--- a/SCAP_1.4/SCAP_1.4_Self_Assertion_Checklist.xlsx
+++ b/SCAP_1.4/SCAP_1.4_Self_Assertion_Checklist.xlsx
@@ -16,7 +16,8 @@
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'OVAL Test Declarations'!$A$1:$C$103</definedName>
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Area" vbProcedure="false">'SCAP 1.4 Self Assertion'!$A:$J</definedName>
-    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'SCAP 1.4 Self Assertion'!$A$1:$J$42</definedName>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'SCAP 1.4 Self Assertion'!$A$1:$J$45</definedName>
+    <definedName function="false" hidden="false" localSheetId="3" name="_xlnm._FilterDatabase_0" vbProcedure="false">'SCAP 1.4 Self Assertion'!$A$1:$J$42</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -51,14 +52,45 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="342">
   <si>
     <t xml:space="preserve">SCAP 1.4 Self Assertion ReadMe</t>
   </si>
   <si>
-    <t xml:space="preserve">This spreadsheet is designed to facilitate the self assertion of SCAP 1.4 Capabilities by a product vendor.   This file supports the NIST SCAP 1.4 specification (NIST Special Publication 800-126 Revision 4) located at: 
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+This spreadsheet is designed to facilitate the self assertion of SCAP 1.4 Capabilities by a product vendor.  
+NIST's SCAPVal application will be required for several of the test case. Version 1.4.3 or later is recommended.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">For more information on Security Content Automation Protocol, and to obtain the SCAPVal application refer to :
 https://csrc.nist.gov/Projects/security-content-automation-protocol/scap-releases/scap-1-4
-Results from this self assertion, along with the SCAP 1.4 Implementation Statement will be published on the OVAL Community Github page, and will be linked from NIST's SCAP 1.4 page.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+Results from this self assertion, along with the SCAP 1.4 Implementation Statement will be published on the OVAL Community SCAP Self Assertion page.
 Definitions:
 ACS - Authenticated Configuration Scanner
 OCIL - Optional support for the Open Checklist Interactive Language
@@ -66,17 +98,18 @@
 1.  Fill out the Vendor Information tab
 2.  Fill out the OVAL Test Declarations tab
 3.  Complete the SCAP 1.4 Self Assertion tab
-	a.  Follow the Test Procedures and Detailed Test Instructions.
-	b.  Fill in the Detailed Results text entry field:  Document the result of the test with a human readable synopsis of the test results.  
-	c.  Select Pass/Fail or Not Applicable for the result.
+   a.  Follow the Test Procedures and Detailed Test Instructions.
+   b.  Fill in the Detailed Results text entry field:  Document the result of the test with a human readable synopsis of the test results.  
+   c.  Select Pass/Fail or Not Applicable for the result.
 4.  Create a SCAP 1.4 Implementation Statement (Saved to a PDF)
 5.  Commit results to github in a new directory based on your Vendor Name
-	a.  https://github.com/OVAL-Community/SCAP-Self-Assertion/tree/main/SCAP_1.4/Completed_Self_Assertions/&lt;Vendor Name&gt;.
-	b.  This completed spreadsheet.
-	c.  SCAP 1.4 Implementation Statement (PDF Format).
-	d.  Vendor or Application Logo (300 x 300 square in PNG Format).
-	e.  Sub-Directory of test results from SCAP and OVAL test content, including ARF, XCCDF and OVAL results.
+    a.  https://github.com/OVAL-Community/SCAP-Self-Assertion/tree/main/SCAP_1.4/Completed_Self_Assertions/&lt;Vendor Name&gt;.
+    b.  This completed spreadsheet.
+    c.  SCAP 1.4 Implementation Statement (PDF Format).
+    d.  Vendor or Application Logo (300 x 300 square in PNG Format).
+    e.  Sub-Directory of test results from SCAP and OVAL test content, including ARF, XCCDF and OVAL results.
 </t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">Requirement</t>
@@ -106,7 +139,10 @@
     <t xml:space="preserve">SCAP 1.4 Self Assertion Checklist/Test Content Version</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0 RC2 (July 2 2026)</t>
+    <t xml:space="preserve">1.0 (September 24, 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCAPVal Version Utilized for testing</t>
   </si>
   <si>
     <t xml:space="preserve">SCAP 1.4 Capabilities  (Answer YES/NO)</t>
@@ -118,13 +154,10 @@
     <t xml:space="preserve">    Open Checklist Interactive Language (OCIL) Option</t>
   </si>
   <si>
-    <t xml:space="preserve"> SCAP 1.3 backward compatibility </t>
+    <t xml:space="preserve">    SCAP 1.3 backward compatibility </t>
   </si>
   <si>
     <t xml:space="preserve">Operating Systems Tested</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enter Operating Systems Tested, one per line.</t>
   </si>
   <si>
     <t xml:space="preserve">Platform</t>
@@ -804,8 +837,8 @@
   <si>
     <t xml:space="preserve">Use content from SCAP_Test_Content\R2100
 questionnaire_results:
-  ocil:validation_program:questionnaire:1" result="FAIL"
-  ocil:validation_program:questionnaire:2" result="PASS"
+  ocil:validation_program:questionnaire:1" result="PASS"
+  ocil:validation_program:questionnaire:2" result="FAIL"
   ocil:validation_program:questionnaire:3" result="PASS"</t>
   </si>
   <si>
@@ -895,29 +928,41 @@
     <t xml:space="preserve">SCAP.V.2940.1: The vendor SHALL provide instruction on where the SCAP Result Data Stream files can be located for inspection.</t>
   </si>
   <si>
-    <t xml:space="preserve">SCAP.T.2940.1: The tester SHALL visually inspect the results to verify that the CPE identifiers are included within the &lt;xccdf:rule-result&gt; element. The SCAP Result Data Streams MUST be processed by the SCAPVal utility without any errors.</t>
+    <t xml:space="preserve">SCAP.T.2940.1: The tester SHALL visually inspect the results to verify that the CPE identifiers are included within the &lt;xccdf:TestResult&gt; element. The SCAP Result Data Streams MUST be processed by the SCAPVal utility without any errors.</t>
   </si>
   <si>
     <t xml:space="preserve">SCAP.R.3005</t>
   </si>
   <si>
-    <t xml:space="preserve">The product SHALL be able to process XCCDF Tailoring component (&lt;xccdf:Tailoring&gt;) that is part of an SCAP source data stream as well as XCCDF Tailoring component that is external to the source datastream and generate XCCDF component results within an SCAP result data stream in accordance with the XCCDF specification for the target platform.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCAP.V.3005.1: The vendor SHALL provide instructions on how to import XCCDF Tailoring component content that is part of or external to the SCAP source data streams for execution and provide instructions on where the XCCDF component results can be located for visual inspection. The purpose of this requirement is to ensure that the product produces valid XCCDF Results and the results match the expected results for all given rules.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCAP.T.3005.1: The tester SHALL import a known valid XCCDF Tailoring component content that is part of SCAP source data streams for the target platform into the vendor product and execute it according to the product operation instructions provided by the vendor. The tester will inspect the product output ensuring XCCDF components are compliant with the XCCDF specification.
-SCAP.T.3005.2: The tester SHALL import a known valid XCCDF Tailoring component content that is external to the SCAP source data streams for the target platform into the vendor product and execute it according to the product operation instructions provided by the vendor. The tester will inspect the product output ensuring XCCDF components are compliant with the XCCDF specification.
-SCAP.T.3005.3: The tester SHALL validate the resulting XCCDF component results within an SCAP result data stream output using the SCAPVal utility. This validation MUST NOT produce any validation errors.
-SCAP.T.3005.4: The tester SHALL compare the product results to the expected results ensuring that all the results match the expected results.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The following scan results are expected: 
-- r3005-datastream-01.xml - selected profile "xccdf_gov.nist.validation_profile_r3005_01"
-- r3005-datastream-01.xml - selected profile "xccdf_gov.nist.validation_profile_r3005_tailoring_01"
-- r3005-datastream-02.xml - selected profile "xccdf_gov.nist.validation_profile_r3005_tailoring_02"
-- r3005-datastream-03.xml - selected profile "xccdf_gov.nist.validation_profile_r3005_tailoring_03"</t>
+    <t xml:space="preserve">The product SHALL support XCCDF Tailoring </t>
+  </si>
+  <si>
+    <t xml:space="preserve">SCAP.V.3005.1: The vendor SHALL provide instructions on how to use XCCDF tailoring within the product.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SCAP.T.3005.1: The tester SHALL follow vendor documentation regarding tailoring usage and ensure that SCAP datastreams can be tailored and that the results from tailoring match end user expectations.
+Tailoring testing should include:
+- Enabling and disabling rules for a SCAP datastream
+- Changing the weight value for individual rules
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">- Selecting different XCCDF Values (only if the source content has Values defined for selection</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">SCAP.R.3010</t>
@@ -934,28 +979,7 @@
 SCAP.T.3010.3: The tester SHALL compare the product results to the expected results ensuring that all the results match the expected results.</t>
   </si>
   <si>
-    <t xml:space="preserve">XCCDF Rule Name	Configuration 1
-xccdf_gov.nist_rule_r3010-1_1	PASS
-xccdf_gov.nist_rule_r3010-1_2	NOTAPPLICABLE
-xccdf_gov.nist_rule_r3010-1_3	NOTSELECTED
-xccdf_gov.nist_rule_r3010-1_4	FAIL
-xccdf_gov.nist_rule_r3010-1_5	NOTAPPLICABLE
-xccdf_gov.nist_rule_r3010-1_6	NOTSELECTED
-xccdf_gov.nist_rule_r3010-1_7	NOTAPPLICABLE
-xccdf_gov.nist_rule_r3010-2_8	NOTAPPLICABLE
-xccdf_gov.nist_rule_r3010-2_9	NOTAPPLICABLE
-xccdf_gov.nist_rule_r3010-2_4	NOTAPPLICABLE
-xccdf_gov.nist_rule_r3010-2_5	NOTAPPLICABLE
-xccdf_gov.nist_rule_r3010-3_1	NOTSELECTED
-xccdf_gov.nist_rule_r3010-3_2	NOTSELECTED
-xccdf_gov.nist_rule_r3010-3_3	NOTSELECTED
-xccdf_gov.nist_rule_r3010-3_4	NOTSELECTED
-xccdf_gov.nist_rule_r3010-0_1	PASS
-xccdf_gov.nist_rule_r3010-0_2	NOTAPPLICABLE
-xccdf_gov.nist_rule_r3010-0_3	NOTSELECTED
-xccdf_gov.nist_rule_r3010-0_4	NOTAPPLICABLE
-xccdf_gov.nist_rule_r3010-0_5	INFORMATIONAL
-xccdf_gov.nist_rule_r3010-0_6	NOTCHECKED</t>
+    <t xml:space="preserve">XCCDF Rule NameConfiguration 1xccdf_gov.nist_rule_r3010-1_1PASSxccdf_gov.nist_rule_r3010-1_2NOTAPPLICABLExccdf_gov.nist_rule_r3010-1_3NOTSELECTEDxccdf_gov.nist_rule_r3010-1_4FAILxccdf_gov.nist_rule_r3010-1_5NOTAPPLICABLExccdf_gov.nist_rule_r3010-1_6NOTSELECTEDxccdf_gov.nist_rule_r3010-1_7NOTAPPLICABLExccdf_gov.nist_rule_r3010-2_8NOTAPPLICABLExccdf_gov.nist_rule_r3010-2_9NOTAPPLICABLExccdf_gov.nist_rule_r3010-2_4NOTAPPLICABLExccdf_gov.nist_rule_r3010-2_5NOTAPPLICABLExccdf_gov.nist_rule_r3010-3_1NOTSELECTEDxccdf_gov.nist_rule_r3010-3_2NOTSELECTEDxccdf_gov.nist_rule_r3010-3_3NOTSELECTEDxccdf_gov.nist_rule_r3010-3_4NOTSELECTEDxccdf_gov.nist_rule_r3010-0_1PASSxccdf_gov.nist_rule_r3010-0_2NOTAPPLICABLExccdf_gov.nist_rule_r3010-0_3NOTSELECTEDxccdf_gov.nist_rule_r3010-0_4NOTAPPLICABLExccdf_gov.nist_rule_r3010-0_5INFORMATIONALxccdf_gov.nist_rule_r3010-0_6NOTCHECKED</t>
   </si>
   <si>
     <t xml:space="preserve">YES</t>
@@ -1084,10 +1108,10 @@
     <t xml:space="preserve">SCAP.V.4901.1: The vendor SHALL provide documentation (printed or electronic) indicating where oval reference information can be obtained</t>
   </si>
   <si>
-    <t xml:space="preserve">SCAP.T.4901.1: The tester SHALL review the OVAL results from a the sample OVAL file and ensure that the results from the product contain the same reference information as the source OVAL XML document.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.  Install the oval_reference_text.xml content. 
+    <t xml:space="preserve">SCAP.T.4901.1: The tester SHALL review the OVAL results from the sample OVAL file found in the SCAP_Test_Content\R4901 directory and ensure that the results from the product contain the same reference information as the source OVAL XML document.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.  Install the oval_reference_text.xml content found in the SCAP_Test_Content\R4901 directory. 
 2.  Execute a scan using the product being tested.
 3.  Review all available reports, including OVAL XML and view resulting CVE, CCE, CCI references.</t>
   </si>
@@ -1267,7 +1291,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1312,6 +1336,12 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
       <i val="true"/>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1340,7 +1370,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1351,6 +1381,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -1399,7 +1435,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="24">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1413,23 +1449,19 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="8" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -1440,7 +1472,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1468,16 +1500,36 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1638,23 +1690,26 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultColWidth="9.12890625" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.12890625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="128.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="125.98"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1024" min="2" style="1" width="9.14"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="409.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="348.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" display="https://csrc.nist.gov/Projects/security-content-automation-protocol/scap-releases/scap-1-4"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1670,8 +1725,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:B36"/>
-  <sheetFormatPr defaultColWidth="9.12890625" defaultRowHeight="12.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:B37"/>
+  <sheetFormatPr defaultColWidth="9.12890625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="76.3"/>
@@ -1749,7 +1804,7 @@
       <c r="B11" s="6"/>
     </row>
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B12" s="6"/>
@@ -1758,12 +1813,12 @@
       <c r="A13" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="6"/>
+    </row>
+    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="5" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6"/>
       <c r="B14" s="6"/>
     </row>
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1853,6 +1908,10 @@
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="6"/>
       <c r="B36" s="6"/>
+    </row>
+    <row r="37" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6"/>
+      <c r="B37" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1871,941 +1930,942 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C103"/>
-  <sheetFormatPr defaultColWidth="13.3828125" defaultRowHeight="13.9" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.22265625" defaultRowHeight="13.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="19.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="41.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="8" width="19.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="19.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="7" width="41.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="7" width="19.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="64" min="4" style="7" width="13.31"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="10"/>
+      <c r="C2" s="9"/>
     </row>
     <row r="3" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="10" t="s">
+      <c r="A3" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="10"/>
+      <c r="C3" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="10"/>
+      <c r="C4" s="9"/>
     </row>
     <row r="5" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="10"/>
+      <c r="C5" s="9"/>
     </row>
     <row r="6" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="10" t="s">
+      <c r="A6" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="10"/>
+      <c r="C6" s="9"/>
     </row>
     <row r="7" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="10"/>
+      <c r="C7" s="9"/>
     </row>
     <row r="8" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="10" t="s">
+      <c r="A8" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C8" s="10"/>
+      <c r="C8" s="9"/>
     </row>
     <row r="9" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="10" t="s">
+      <c r="A9" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C9" s="10"/>
+      <c r="C9" s="9"/>
     </row>
     <row r="10" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="10" t="s">
+      <c r="A10" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="10" t="s">
+      <c r="B10" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="10"/>
+      <c r="C10" s="9"/>
     </row>
     <row r="11" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="10" t="s">
+      <c r="A11" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="10"/>
+      <c r="C11" s="9"/>
     </row>
     <row r="12" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="10" t="s">
+      <c r="A12" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="10"/>
+      <c r="C12" s="9"/>
     </row>
     <row r="13" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C13" s="10"/>
+      <c r="C13" s="9"/>
     </row>
     <row r="14" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="10" t="s">
+      <c r="A14" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="10"/>
+      <c r="C14" s="9"/>
     </row>
     <row r="15" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="10" t="s">
+      <c r="A15" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="10"/>
+      <c r="C15" s="9"/>
     </row>
     <row r="16" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="10" t="s">
+      <c r="A16" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C16" s="10"/>
+      <c r="C16" s="9"/>
     </row>
     <row r="17" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="10" t="s">
+      <c r="A17" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="10"/>
+      <c r="C17" s="9"/>
     </row>
     <row r="18" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="10" t="s">
+      <c r="A18" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="C18" s="10"/>
+      <c r="C18" s="9"/>
     </row>
     <row r="19" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="10" t="s">
+      <c r="B19" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C19" s="10"/>
+      <c r="C19" s="9"/>
     </row>
     <row r="20" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="10" t="s">
+      <c r="B20" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="C20" s="10"/>
+      <c r="C20" s="9"/>
     </row>
     <row r="21" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="C21" s="10"/>
+      <c r="C21" s="9"/>
     </row>
     <row r="22" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="10" t="s">
+      <c r="A22" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="C22" s="10"/>
+      <c r="C22" s="9"/>
     </row>
     <row r="23" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="C23" s="10"/>
+      <c r="C23" s="9"/>
     </row>
     <row r="24" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="10" t="s">
+      <c r="A24" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C24" s="10"/>
+      <c r="C24" s="9"/>
     </row>
     <row r="25" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="10" t="s">
+      <c r="A25" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="10" t="s">
+      <c r="B25" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="C25" s="10"/>
+      <c r="C25" s="9"/>
     </row>
     <row r="26" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="10" t="s">
+      <c r="A26" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C26" s="10"/>
+      <c r="C26" s="9"/>
     </row>
     <row r="27" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="10" t="s">
+      <c r="A27" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="10" t="s">
+      <c r="B27" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C27" s="10"/>
+      <c r="C27" s="9"/>
     </row>
     <row r="28" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="10" t="s">
+      <c r="A28" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C28" s="10"/>
+      <c r="C28" s="9"/>
     </row>
     <row r="29" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="10" t="s">
+      <c r="A29" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="B29" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="C29" s="10"/>
+      <c r="C29" s="9"/>
     </row>
     <row r="30" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="10" t="s">
+      <c r="A30" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="10" t="s">
+      <c r="B30" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="C30" s="10"/>
+      <c r="C30" s="9"/>
     </row>
     <row r="31" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="10" t="s">
+      <c r="A31" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="10" t="s">
+      <c r="B31" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="C31" s="10"/>
+      <c r="C31" s="9"/>
     </row>
     <row r="32" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="10" t="s">
+      <c r="A32" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="10" t="s">
+      <c r="B32" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C32" s="10"/>
+      <c r="C32" s="9"/>
     </row>
     <row r="33" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="10" t="s">
+      <c r="A33" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="10" t="s">
+      <c r="B33" s="9" t="s">
         <v>45</v>
       </c>
-      <c r="C33" s="10"/>
+      <c r="C33" s="9"/>
     </row>
     <row r="34" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="10" t="s">
+      <c r="A34" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="10" t="s">
+      <c r="B34" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="C34" s="10"/>
+      <c r="C34" s="9"/>
     </row>
     <row r="35" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="10" t="s">
+      <c r="A35" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B35" s="10" t="s">
+      <c r="B35" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="C35" s="10"/>
+      <c r="C35" s="9"/>
     </row>
     <row r="36" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="10" t="s">
+      <c r="A36" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B36" s="10" t="s">
+      <c r="B36" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="C36" s="10"/>
+      <c r="C36" s="9"/>
     </row>
     <row r="37" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="10" t="s">
+      <c r="A37" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B37" s="10" t="s">
+      <c r="B37" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="C37" s="10"/>
+      <c r="C37" s="9"/>
     </row>
     <row r="38" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="10" t="s">
+      <c r="A38" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B38" s="10" t="s">
+      <c r="B38" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C38" s="10"/>
+      <c r="C38" s="9"/>
     </row>
     <row r="39" customFormat="false" ht="13.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="10" t="s">
+      <c r="A39" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B39" s="10" t="s">
+      <c r="B39" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="C39" s="10"/>
-    </row>
-    <row r="40" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="10" t="s">
+      <c r="C39" s="9"/>
+    </row>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B40" s="10" t="s">
+      <c r="B40" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C40" s="10"/>
-    </row>
-    <row r="41" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="10" t="s">
+      <c r="C40" s="9"/>
+    </row>
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B41" s="10" t="s">
+      <c r="B41" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="C41" s="10"/>
-    </row>
-    <row r="42" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="10" t="s">
+      <c r="C41" s="9"/>
+    </row>
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B42" s="10" t="s">
+      <c r="B42" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C42" s="10"/>
-    </row>
-    <row r="43" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="10" t="s">
+      <c r="C42" s="9"/>
+    </row>
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B43" s="10" t="s">
+      <c r="B43" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="C43" s="10"/>
-    </row>
-    <row r="44" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="10" t="s">
+      <c r="C43" s="9"/>
+    </row>
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B44" s="10" t="s">
+      <c r="B44" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="C44" s="10"/>
-    </row>
-    <row r="45" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="10" t="s">
+      <c r="C44" s="9"/>
+    </row>
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B45" s="10" t="s">
+      <c r="B45" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C45" s="10"/>
-    </row>
-    <row r="46" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="10" t="s">
+      <c r="C45" s="9"/>
+    </row>
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B46" s="10" t="s">
+      <c r="B46" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C46" s="10"/>
-    </row>
-    <row r="47" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="10" t="s">
+      <c r="C46" s="9"/>
+    </row>
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B47" s="10" t="s">
+      <c r="B47" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="C47" s="10"/>
-    </row>
-    <row r="48" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="10" t="s">
+      <c r="C47" s="9"/>
+    </row>
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B48" s="10" t="s">
+      <c r="B48" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C48" s="10"/>
-    </row>
-    <row r="49" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="10" t="s">
+      <c r="C48" s="9"/>
+    </row>
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B49" s="10" t="s">
+      <c r="B49" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C49" s="10"/>
-    </row>
-    <row r="50" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="10" t="s">
+      <c r="C49" s="9"/>
+    </row>
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B50" s="10" t="s">
+      <c r="B50" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="C50" s="10"/>
-    </row>
-    <row r="51" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="10" t="s">
+      <c r="C50" s="9"/>
+    </row>
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B51" s="10" t="s">
+      <c r="B51" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C51" s="10"/>
-    </row>
-    <row r="52" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="10" t="s">
+      <c r="C51" s="9"/>
+    </row>
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B52" s="10" t="s">
+      <c r="B52" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C52" s="10"/>
-    </row>
-    <row r="53" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="10" t="s">
+      <c r="C52" s="9"/>
+    </row>
+    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B53" s="10" t="s">
+      <c r="B53" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="C53" s="10"/>
-    </row>
-    <row r="54" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="10" t="s">
+      <c r="C53" s="9"/>
+    </row>
+    <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B54" s="10" t="s">
+      <c r="B54" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C54" s="10"/>
-    </row>
-    <row r="55" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="10" t="s">
+      <c r="C54" s="9"/>
+    </row>
+    <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B55" s="10" t="s">
+      <c r="B55" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="C55" s="10"/>
-    </row>
-    <row r="56" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="10" t="s">
+      <c r="C55" s="9"/>
+    </row>
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B56" s="10" t="s">
+      <c r="B56" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C56" s="10"/>
-    </row>
-    <row r="57" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="10" t="s">
+      <c r="C56" s="9"/>
+    </row>
+    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B57" s="10" t="s">
+      <c r="B57" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="C57" s="10"/>
-    </row>
-    <row r="58" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="10" t="s">
+      <c r="C57" s="9"/>
+    </row>
+    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B58" s="10" t="s">
+      <c r="B58" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="C58" s="10"/>
-    </row>
-    <row r="59" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="10" t="s">
+      <c r="C58" s="9"/>
+    </row>
+    <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B59" s="10" t="s">
+      <c r="B59" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="C59" s="10"/>
-    </row>
-    <row r="60" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="10" t="s">
+      <c r="C59" s="9"/>
+    </row>
+    <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B60" s="10" t="s">
+      <c r="B60" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="C60" s="10"/>
-    </row>
-    <row r="61" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="10" t="s">
+      <c r="C60" s="9"/>
+    </row>
+    <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B61" s="10" t="s">
+      <c r="B61" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="C61" s="10"/>
-    </row>
-    <row r="62" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="10" t="s">
+      <c r="C61" s="9"/>
+    </row>
+    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B62" s="10" t="s">
+      <c r="B62" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="C62" s="10"/>
-    </row>
-    <row r="63" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="10" t="s">
+      <c r="C62" s="9"/>
+    </row>
+    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B63" s="10" t="s">
+      <c r="B63" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="C63" s="10"/>
-    </row>
-    <row r="64" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="10" t="s">
+      <c r="C63" s="9"/>
+    </row>
+    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B64" s="10" t="s">
+      <c r="B64" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="C64" s="10"/>
-    </row>
-    <row r="65" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="10" t="s">
+      <c r="C64" s="9"/>
+    </row>
+    <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B65" s="10" t="s">
+      <c r="B65" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="C65" s="10"/>
-    </row>
-    <row r="66" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="10" t="s">
+      <c r="C65" s="9"/>
+    </row>
+    <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B66" s="10" t="s">
+      <c r="B66" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="C66" s="10"/>
-    </row>
-    <row r="67" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="10" t="s">
+      <c r="C66" s="9"/>
+    </row>
+    <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B67" s="10" t="s">
+      <c r="B67" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="C67" s="10"/>
-    </row>
-    <row r="68" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="10" t="s">
+      <c r="C67" s="9"/>
+    </row>
+    <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B68" s="10" t="s">
+      <c r="B68" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="C68" s="10"/>
-    </row>
-    <row r="69" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="10" t="s">
+      <c r="C68" s="9"/>
+    </row>
+    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="B69" s="10" t="s">
+      <c r="B69" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="C69" s="10"/>
-    </row>
-    <row r="70" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="10" t="s">
+      <c r="C69" s="9"/>
+    </row>
+    <row r="70" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="B70" s="10" t="s">
+      <c r="B70" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="C70" s="10"/>
-    </row>
-    <row r="71" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="10" t="s">
+      <c r="C70" s="9"/>
+    </row>
+    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="B71" s="10" t="s">
+      <c r="B71" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="C71" s="10"/>
-    </row>
-    <row r="72" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="10" t="s">
+      <c r="C71" s="9"/>
+    </row>
+    <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="B72" s="10" t="s">
+      <c r="B72" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="C72" s="10"/>
-    </row>
-    <row r="73" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="10" t="s">
+      <c r="C72" s="9"/>
+    </row>
+    <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="B73" s="10" t="s">
+      <c r="B73" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="C73" s="10"/>
-    </row>
-    <row r="74" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="10" t="s">
+      <c r="C73" s="9"/>
+    </row>
+    <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="B74" s="10" t="s">
+      <c r="B74" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="C74" s="10"/>
-    </row>
-    <row r="75" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="10" t="s">
+      <c r="C74" s="9"/>
+    </row>
+    <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="B75" s="10" t="s">
+      <c r="B75" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="C75" s="10"/>
-    </row>
-    <row r="76" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="10" t="s">
+      <c r="C75" s="9"/>
+    </row>
+    <row r="76" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B76" s="10" t="s">
+      <c r="B76" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C76" s="10"/>
-    </row>
-    <row r="77" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="10" t="s">
+      <c r="C76" s="9"/>
+    </row>
+    <row r="77" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B77" s="10" t="s">
+      <c r="B77" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="C77" s="10"/>
-    </row>
-    <row r="78" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="10" t="s">
+      <c r="C77" s="9"/>
+    </row>
+    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B78" s="10" t="s">
+      <c r="B78" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="C78" s="10"/>
-    </row>
-    <row r="79" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="10" t="s">
+      <c r="C78" s="9"/>
+    </row>
+    <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B79" s="10" t="s">
+      <c r="B79" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="C79" s="10"/>
-    </row>
-    <row r="80" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="10" t="s">
+      <c r="C79" s="9"/>
+    </row>
+    <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B80" s="10" t="s">
+      <c r="B80" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="C80" s="10"/>
-    </row>
-    <row r="81" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="10" t="s">
+      <c r="C80" s="9"/>
+    </row>
+    <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B81" s="10" t="s">
+      <c r="B81" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="C81" s="10"/>
-    </row>
-    <row r="82" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="10" t="s">
+      <c r="C81" s="9"/>
+    </row>
+    <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B82" s="10" t="s">
+      <c r="B82" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="C82" s="10"/>
-    </row>
-    <row r="83" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="10" t="s">
+      <c r="C82" s="9"/>
+    </row>
+    <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B83" s="10" t="s">
+      <c r="B83" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="C83" s="10"/>
-    </row>
-    <row r="84" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="10" t="s">
+      <c r="C83" s="9"/>
+    </row>
+    <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="B84" s="10" t="s">
+      <c r="B84" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="C84" s="10"/>
-    </row>
-    <row r="85" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="10" t="s">
+      <c r="C84" s="9"/>
+    </row>
+    <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="B85" s="10" t="s">
+      <c r="B85" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="C85" s="10"/>
-    </row>
-    <row r="86" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="10" t="s">
+      <c r="C85" s="9"/>
+    </row>
+    <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="B86" s="10" t="s">
+      <c r="B86" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="C86" s="10"/>
-    </row>
-    <row r="87" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="10" t="s">
+      <c r="C86" s="9"/>
+    </row>
+    <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="B87" s="10" t="s">
+      <c r="B87" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="C87" s="10"/>
-    </row>
-    <row r="88" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="10" t="s">
+      <c r="C87" s="9"/>
+    </row>
+    <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="B88" s="10" t="s">
+      <c r="B88" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="C88" s="10"/>
-    </row>
-    <row r="89" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="10" t="s">
+      <c r="C88" s="9"/>
+    </row>
+    <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="B89" s="10" t="s">
+      <c r="B89" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="C89" s="10"/>
-    </row>
-    <row r="90" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="10" t="s">
+      <c r="C89" s="9"/>
+    </row>
+    <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="B90" s="10" t="s">
+      <c r="B90" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="C90" s="10"/>
-    </row>
-    <row r="91" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="10" t="s">
+      <c r="C90" s="9"/>
+    </row>
+    <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="B91" s="10" t="s">
+      <c r="B91" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="C91" s="10"/>
-    </row>
-    <row r="92" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="10" t="s">
+      <c r="C91" s="9"/>
+    </row>
+    <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="B92" s="10" t="s">
+      <c r="B92" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="C92" s="10"/>
-    </row>
-    <row r="93" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="10" t="s">
+      <c r="C92" s="9"/>
+    </row>
+    <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="B93" s="10" t="s">
+      <c r="B93" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="C93" s="10"/>
-    </row>
-    <row r="94" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A94" s="10" t="s">
+      <c r="C93" s="9"/>
+    </row>
+    <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="B94" s="10" t="s">
+      <c r="B94" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="C94" s="10"/>
-    </row>
-    <row r="95" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="10" t="s">
+      <c r="C94" s="9"/>
+    </row>
+    <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="B95" s="10" t="s">
+      <c r="B95" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="C95" s="10"/>
-    </row>
-    <row r="96" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="10" t="s">
+      <c r="C95" s="9"/>
+    </row>
+    <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="B96" s="10" t="s">
+      <c r="B96" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="C96" s="10"/>
-    </row>
-    <row r="97" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="10" t="s">
+      <c r="C96" s="9"/>
+    </row>
+    <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="B97" s="10" t="s">
+      <c r="B97" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="C97" s="10"/>
-    </row>
-    <row r="98" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="10" t="s">
+      <c r="C97" s="9"/>
+    </row>
+    <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="B98" s="10" t="s">
+      <c r="B98" s="9" t="s">
         <v>112</v>
       </c>
-      <c r="C98" s="10"/>
-    </row>
-    <row r="99" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="10" t="s">
+      <c r="C98" s="9"/>
+    </row>
+    <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="B99" s="10" t="s">
+      <c r="B99" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="C99" s="10"/>
-    </row>
-    <row r="100" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="10" t="s">
+      <c r="C99" s="9"/>
+    </row>
+    <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="B100" s="10" t="s">
+      <c r="B100" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="C100" s="10"/>
-    </row>
-    <row r="101" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A101" s="10" t="s">
+      <c r="C100" s="9"/>
+    </row>
+    <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="B101" s="10" t="s">
+      <c r="B101" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="C101" s="10"/>
-    </row>
-    <row r="102" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="10" t="s">
+      <c r="C101" s="9"/>
+    </row>
+    <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="B102" s="10" t="s">
+      <c r="B102" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="C102" s="10"/>
-    </row>
-    <row r="103" customFormat="false" ht="13.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A103" s="10" t="s">
+      <c r="C102" s="9"/>
+    </row>
+    <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="B103" s="10" t="s">
+      <c r="B103" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="C103" s="10"/>
+      <c r="C103" s="9"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:C103"/>
@@ -2825,1103 +2885,5166 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:R45"/>
-  <sheetFormatPr defaultColWidth="9.12890625" defaultRowHeight="13.9" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AMJ45"/>
+  <sheetFormatPr defaultColWidth="9.12890625" defaultRowHeight="13.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="11" width="13.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="11" width="17.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="11" width="9.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="12" width="16.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="12" width="30.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="12" width="38.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="12" width="45.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="12" width="55.44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="12" width="11.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="12" width="22.43"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="17" min="11" style="12" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="18" min="18" style="12" width="10.31"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1023" min="19" style="12" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="10" width="13.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="10" width="17.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="10" width="9.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="11" width="16.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="11" width="30.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="11" width="38.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="11" width="45.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="11" width="55.44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="11" width="11.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="11" width="22.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="11" width="27.35"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="17" min="12" style="11" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="true" outlineLevel="0" max="18" min="18" style="11" width="10.31"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1023" min="19" style="11" width="9.14"/>
   </cols>
   <sheetData>
-    <row r="1" s="14" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="9" t="s">
+    <row r="1" s="13" customFormat="true" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="9" t="s">
+      <c r="B1" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="R1" s="14" t="s">
+      <c r="R1" s="13" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="16" t="s">
+      <c r="B2" s="14"/>
+      <c r="C2" s="14"/>
+      <c r="D2" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="F2" s="16" t="s">
+      <c r="F2" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="G2" s="16" t="s">
+      <c r="G2" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="H2" s="16" t="s">
+      <c r="H2" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="R2" s="12" t="s">
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="R2" s="11" t="s">
         <v>134</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="202.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="15"/>
-      <c r="B3" s="15" t="s">
+      <c r="A3" s="14"/>
+      <c r="B3" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="16" t="s">
+      <c r="C3" s="14"/>
+      <c r="D3" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="E3" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="F3" s="16" t="s">
+      <c r="F3" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="G3" s="16" t="s">
+      <c r="G3" s="15" t="s">
         <v>138</v>
       </c>
-      <c r="H3" s="16" t="s">
+      <c r="H3" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-      <c r="R3" s="12" t="s">
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="R3" s="11" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="16" t="s">
+      <c r="B4" s="14"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="E4" s="16" t="s">
+      <c r="E4" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="F4" s="16" t="s">
+      <c r="F4" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="G4" s="16" t="s">
+      <c r="G4" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="H4" s="16" t="s">
+      <c r="H4" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="I4" s="16"/>
-      <c r="J4" s="16"/>
+      <c r="I4" s="15"/>
+      <c r="J4" s="15"/>
     </row>
     <row r="5" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="16" t="s">
+      <c r="B5" s="14"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="15" t="s">
         <v>144</v>
       </c>
-      <c r="E5" s="16" t="s">
+      <c r="E5" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="F5" s="16" t="s">
+      <c r="F5" s="15" t="s">
         <v>146</v>
       </c>
-      <c r="G5" s="16" t="s">
+      <c r="G5" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="H5" s="16" t="s">
+      <c r="H5" s="15" t="s">
         <v>148</v>
       </c>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
     </row>
     <row r="6" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="16" t="s">
+      <c r="B6" s="14"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="F6" s="16" t="s">
+      <c r="F6" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="G6" s="16" t="s">
+      <c r="G6" s="15" t="s">
         <v>152</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="H6" s="15" t="s">
         <v>153</v>
       </c>
-      <c r="I6" s="16"/>
-      <c r="J6" s="16"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
     </row>
     <row r="7" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="B7" s="15"/>
-      <c r="C7" s="15"/>
-      <c r="D7" s="16" t="s">
+      <c r="B7" s="14"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E7" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="G7" s="16" t="s">
+      <c r="G7" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="H7" s="16" t="s">
+      <c r="H7" s="15" t="s">
         <v>158</v>
       </c>
-      <c r="I7" s="16"/>
-      <c r="J7" s="16"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
     </row>
     <row r="8" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="16" t="s">
+      <c r="B8" s="14"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="E8" s="16" t="s">
+      <c r="E8" s="15" t="s">
         <v>160</v>
       </c>
-      <c r="F8" s="16" t="s">
+      <c r="F8" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="G8" s="16" t="s">
+      <c r="G8" s="15" t="s">
         <v>162</v>
       </c>
-      <c r="H8" s="16" t="s">
+      <c r="H8" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
     </row>
     <row r="9" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="16" t="s">
+      <c r="B9" s="14"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="E9" s="16" t="s">
+      <c r="E9" s="15" t="s">
         <v>165</v>
       </c>
-      <c r="F9" s="16" t="s">
+      <c r="F9" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="G9" s="16" t="s">
+      <c r="G9" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="H9" s="16" t="s">
+      <c r="H9" s="15" t="s">
         <v>168</v>
       </c>
-      <c r="I9" s="16"/>
-      <c r="J9" s="16"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
     </row>
     <row r="10" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
-      <c r="D10" s="16" t="s">
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="15" t="s">
         <v>169</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="15" t="s">
         <v>170</v>
       </c>
-      <c r="F10" s="16" t="s">
+      <c r="F10" s="15" t="s">
         <v>171</v>
       </c>
-      <c r="G10" s="16" t="s">
+      <c r="G10" s="15" t="s">
         <v>172</v>
       </c>
-      <c r="H10" s="16" t="s">
+      <c r="H10" s="15" t="s">
         <v>173</v>
       </c>
-      <c r="I10" s="16"/>
-      <c r="J10" s="16"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
     </row>
     <row r="11" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="16" t="s">
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="15" t="s">
         <v>174</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="E11" s="15" t="s">
         <v>175</v>
       </c>
-      <c r="F11" s="16" t="s">
+      <c r="F11" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="G11" s="16" t="s">
+      <c r="G11" s="15" t="s">
         <v>177</v>
       </c>
-      <c r="H11" s="16" t="s">
+      <c r="H11" s="15" t="s">
         <v>178</v>
       </c>
-      <c r="I11" s="16"/>
-      <c r="J11" s="16"/>
-    </row>
-    <row r="12" customFormat="false" ht="102" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="15" t="s">
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+    </row>
+    <row r="12" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="C12" s="15"/>
-      <c r="D12" s="16" t="s">
+      <c r="C12" s="14"/>
+      <c r="D12" s="15" t="s">
         <v>179</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="G12" s="16" t="s">
+      <c r="G12" s="15" t="s">
         <v>182</v>
       </c>
-      <c r="H12" s="16" t="s">
+      <c r="H12" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
+      <c r="I12" s="15"/>
+      <c r="J12" s="15"/>
     </row>
     <row r="13" customFormat="false" ht="292.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="16" t="s">
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="E13" s="15" t="s">
         <v>185</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="F13" s="15" t="s">
         <v>186</v>
       </c>
-      <c r="G13" s="16" t="s">
+      <c r="G13" s="15" t="s">
         <v>187</v>
       </c>
-      <c r="H13" s="16" t="s">
+      <c r="H13" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="I13" s="16"/>
-      <c r="J13" s="16"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
     </row>
     <row r="14" customFormat="false" ht="393.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="16" t="s">
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="15" t="s">
         <v>189</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="15" t="s">
         <v>190</v>
       </c>
-      <c r="F14" s="16" t="s">
+      <c r="F14" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="G14" s="16" t="s">
+      <c r="G14" s="15" t="s">
         <v>192</v>
       </c>
-      <c r="H14" s="16" t="s">
+      <c r="H14" s="15" t="s">
         <v>193</v>
       </c>
-      <c r="I14" s="16"/>
-      <c r="J14" s="16"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
     </row>
     <row r="15" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="15"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="15" t="s">
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="15" t="s">
         <v>194</v>
       </c>
-      <c r="E15" s="16" t="s">
+      <c r="E15" s="15" t="s">
         <v>195</v>
       </c>
-      <c r="F15" s="16" t="s">
+      <c r="F15" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="G15" s="16" t="s">
+      <c r="G15" s="15" t="s">
         <v>197</v>
       </c>
-      <c r="H15" s="16" t="s">
+      <c r="H15" s="15" t="s">
         <v>198</v>
       </c>
-      <c r="I15" s="16"/>
-      <c r="J15" s="16"/>
-    </row>
-    <row r="16" customFormat="false" ht="102" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="15" t="s">
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+    </row>
+    <row r="16" s="16" customFormat="true" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="16" t="s">
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="15" t="s">
         <v>199</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="15" t="s">
         <v>200</v>
       </c>
-      <c r="F16" s="16" t="s">
+      <c r="F16" s="15" t="s">
         <v>201</v>
       </c>
-      <c r="G16" s="16" t="s">
+      <c r="G16" s="15" t="s">
         <v>202</v>
       </c>
-      <c r="H16" s="16" t="s">
+      <c r="H16" s="15" t="s">
         <v>203</v>
       </c>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
-    </row>
-    <row r="17" s="18" customFormat="true" ht="258.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="15" t="s">
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="11"/>
+      <c r="L16" s="11"/>
+      <c r="M16" s="11"/>
+      <c r="N16" s="11"/>
+      <c r="O16" s="11"/>
+      <c r="P16" s="11"/>
+      <c r="Q16" s="11"/>
+      <c r="R16" s="11"/>
+      <c r="S16" s="11"/>
+      <c r="T16" s="11"/>
+      <c r="U16" s="11"/>
+      <c r="V16" s="11"/>
+      <c r="W16" s="11"/>
+      <c r="X16" s="11"/>
+      <c r="Y16" s="11"/>
+      <c r="Z16" s="11"/>
+      <c r="AA16" s="11"/>
+      <c r="AB16" s="11"/>
+      <c r="AC16" s="11"/>
+      <c r="AD16" s="11"/>
+      <c r="AE16" s="11"/>
+      <c r="AF16" s="11"/>
+      <c r="AG16" s="11"/>
+      <c r="AH16" s="11"/>
+      <c r="AI16" s="11"/>
+      <c r="AJ16" s="11"/>
+      <c r="AK16" s="11"/>
+      <c r="AL16" s="11"/>
+      <c r="AM16" s="11"/>
+      <c r="AN16" s="11"/>
+      <c r="AO16" s="11"/>
+      <c r="AP16" s="11"/>
+      <c r="AQ16" s="11"/>
+      <c r="AR16" s="11"/>
+      <c r="AS16" s="11"/>
+      <c r="AT16" s="11"/>
+      <c r="AU16" s="11"/>
+      <c r="AV16" s="11"/>
+      <c r="AW16" s="11"/>
+      <c r="AX16" s="11"/>
+      <c r="AY16" s="11"/>
+      <c r="AZ16" s="11"/>
+      <c r="BA16" s="11"/>
+      <c r="BB16" s="11"/>
+      <c r="BC16" s="11"/>
+      <c r="BD16" s="11"/>
+      <c r="BE16" s="11"/>
+      <c r="BF16" s="11"/>
+      <c r="BG16" s="11"/>
+      <c r="BH16" s="11"/>
+      <c r="BI16" s="11"/>
+      <c r="BJ16" s="11"/>
+      <c r="BK16" s="11"/>
+      <c r="BL16" s="11"/>
+      <c r="BM16" s="11"/>
+      <c r="BN16" s="11"/>
+      <c r="BO16" s="11"/>
+      <c r="BP16" s="11"/>
+      <c r="BQ16" s="11"/>
+      <c r="BR16" s="11"/>
+      <c r="BS16" s="11"/>
+      <c r="BT16" s="11"/>
+      <c r="BU16" s="11"/>
+      <c r="BV16" s="11"/>
+      <c r="BW16" s="11"/>
+      <c r="BX16" s="11"/>
+      <c r="BY16" s="11"/>
+      <c r="BZ16" s="11"/>
+      <c r="CA16" s="11"/>
+      <c r="CB16" s="11"/>
+      <c r="CC16" s="11"/>
+      <c r="CD16" s="11"/>
+      <c r="CE16" s="11"/>
+      <c r="CF16" s="11"/>
+      <c r="CG16" s="11"/>
+      <c r="CH16" s="11"/>
+      <c r="CI16" s="11"/>
+      <c r="CJ16" s="11"/>
+      <c r="CK16" s="11"/>
+      <c r="CL16" s="11"/>
+      <c r="CM16" s="11"/>
+      <c r="CN16" s="11"/>
+      <c r="CO16" s="11"/>
+      <c r="CP16" s="11"/>
+      <c r="CQ16" s="11"/>
+      <c r="CR16" s="11"/>
+      <c r="CS16" s="11"/>
+      <c r="CT16" s="11"/>
+      <c r="CU16" s="11"/>
+      <c r="CV16" s="11"/>
+      <c r="CW16" s="11"/>
+      <c r="CX16" s="11"/>
+      <c r="CY16" s="11"/>
+      <c r="CZ16" s="11"/>
+      <c r="DA16" s="11"/>
+      <c r="DB16" s="11"/>
+      <c r="DC16" s="11"/>
+      <c r="DD16" s="11"/>
+      <c r="DE16" s="11"/>
+      <c r="DF16" s="11"/>
+      <c r="DG16" s="11"/>
+      <c r="DH16" s="11"/>
+      <c r="DI16" s="11"/>
+      <c r="DJ16" s="11"/>
+      <c r="DK16" s="11"/>
+      <c r="DL16" s="11"/>
+      <c r="DM16" s="11"/>
+      <c r="DN16" s="11"/>
+      <c r="DO16" s="11"/>
+      <c r="DP16" s="11"/>
+      <c r="DQ16" s="11"/>
+      <c r="DR16" s="11"/>
+      <c r="DS16" s="11"/>
+      <c r="DT16" s="11"/>
+      <c r="DU16" s="11"/>
+      <c r="DV16" s="11"/>
+      <c r="DW16" s="11"/>
+      <c r="DX16" s="11"/>
+      <c r="DY16" s="11"/>
+      <c r="DZ16" s="11"/>
+      <c r="EA16" s="11"/>
+      <c r="EB16" s="11"/>
+      <c r="EC16" s="11"/>
+      <c r="ED16" s="11"/>
+      <c r="EE16" s="11"/>
+      <c r="EF16" s="11"/>
+      <c r="EG16" s="11"/>
+      <c r="EH16" s="11"/>
+      <c r="EI16" s="11"/>
+      <c r="EJ16" s="11"/>
+      <c r="EK16" s="11"/>
+      <c r="EL16" s="11"/>
+      <c r="EM16" s="11"/>
+      <c r="EN16" s="11"/>
+      <c r="EO16" s="11"/>
+      <c r="EP16" s="11"/>
+      <c r="EQ16" s="11"/>
+      <c r="ER16" s="11"/>
+      <c r="ES16" s="11"/>
+      <c r="ET16" s="11"/>
+      <c r="EU16" s="11"/>
+      <c r="EV16" s="11"/>
+      <c r="EW16" s="11"/>
+      <c r="EX16" s="11"/>
+      <c r="EY16" s="11"/>
+      <c r="EZ16" s="11"/>
+      <c r="FA16" s="11"/>
+      <c r="FB16" s="11"/>
+      <c r="FC16" s="11"/>
+      <c r="FD16" s="11"/>
+      <c r="FE16" s="11"/>
+      <c r="FF16" s="11"/>
+      <c r="FG16" s="11"/>
+      <c r="FH16" s="11"/>
+      <c r="FI16" s="11"/>
+      <c r="FJ16" s="11"/>
+      <c r="FK16" s="11"/>
+      <c r="FL16" s="11"/>
+      <c r="FM16" s="11"/>
+      <c r="FN16" s="11"/>
+      <c r="FO16" s="11"/>
+      <c r="FP16" s="11"/>
+      <c r="FQ16" s="11"/>
+      <c r="FR16" s="11"/>
+      <c r="FS16" s="11"/>
+      <c r="FT16" s="11"/>
+      <c r="FU16" s="11"/>
+      <c r="FV16" s="11"/>
+      <c r="FW16" s="11"/>
+      <c r="FX16" s="11"/>
+      <c r="FY16" s="11"/>
+      <c r="FZ16" s="11"/>
+      <c r="GA16" s="11"/>
+      <c r="GB16" s="11"/>
+      <c r="GC16" s="11"/>
+      <c r="GD16" s="11"/>
+      <c r="GE16" s="11"/>
+      <c r="GF16" s="11"/>
+      <c r="GG16" s="11"/>
+      <c r="GH16" s="11"/>
+      <c r="GI16" s="11"/>
+      <c r="GJ16" s="11"/>
+      <c r="GK16" s="11"/>
+      <c r="GL16" s="11"/>
+      <c r="GM16" s="11"/>
+      <c r="GN16" s="11"/>
+      <c r="GO16" s="11"/>
+      <c r="GP16" s="11"/>
+      <c r="GQ16" s="11"/>
+      <c r="GR16" s="11"/>
+      <c r="GS16" s="11"/>
+      <c r="GT16" s="11"/>
+      <c r="GU16" s="11"/>
+      <c r="GV16" s="11"/>
+      <c r="GW16" s="11"/>
+      <c r="GX16" s="11"/>
+      <c r="GY16" s="11"/>
+      <c r="GZ16" s="11"/>
+      <c r="HA16" s="11"/>
+      <c r="HB16" s="11"/>
+      <c r="HC16" s="11"/>
+      <c r="HD16" s="11"/>
+      <c r="HE16" s="11"/>
+      <c r="HF16" s="11"/>
+      <c r="HG16" s="11"/>
+      <c r="HH16" s="11"/>
+      <c r="HI16" s="11"/>
+      <c r="HJ16" s="11"/>
+      <c r="HK16" s="11"/>
+      <c r="HL16" s="11"/>
+      <c r="HM16" s="11"/>
+      <c r="HN16" s="11"/>
+      <c r="HO16" s="11"/>
+      <c r="HP16" s="11"/>
+      <c r="HQ16" s="11"/>
+      <c r="HR16" s="11"/>
+      <c r="HS16" s="11"/>
+      <c r="HT16" s="11"/>
+      <c r="HU16" s="11"/>
+      <c r="HV16" s="11"/>
+      <c r="HW16" s="11"/>
+      <c r="HX16" s="11"/>
+      <c r="HY16" s="11"/>
+      <c r="HZ16" s="11"/>
+      <c r="IA16" s="11"/>
+      <c r="IB16" s="11"/>
+      <c r="IC16" s="11"/>
+      <c r="ID16" s="11"/>
+      <c r="IE16" s="11"/>
+      <c r="IF16" s="11"/>
+      <c r="IG16" s="11"/>
+      <c r="IH16" s="11"/>
+      <c r="II16" s="11"/>
+      <c r="IJ16" s="11"/>
+      <c r="IK16" s="11"/>
+      <c r="IL16" s="11"/>
+      <c r="IM16" s="11"/>
+      <c r="IN16" s="11"/>
+      <c r="IO16" s="11"/>
+      <c r="IP16" s="11"/>
+      <c r="IQ16" s="11"/>
+      <c r="IR16" s="11"/>
+      <c r="IS16" s="11"/>
+      <c r="IT16" s="11"/>
+      <c r="IU16" s="11"/>
+      <c r="IV16" s="11"/>
+      <c r="IW16" s="11"/>
+      <c r="IX16" s="11"/>
+      <c r="IY16" s="11"/>
+      <c r="IZ16" s="11"/>
+      <c r="JA16" s="11"/>
+      <c r="JB16" s="11"/>
+      <c r="JC16" s="11"/>
+      <c r="JD16" s="11"/>
+      <c r="JE16" s="11"/>
+      <c r="JF16" s="11"/>
+      <c r="JG16" s="11"/>
+      <c r="JH16" s="11"/>
+      <c r="JI16" s="11"/>
+      <c r="JJ16" s="11"/>
+      <c r="JK16" s="11"/>
+      <c r="JL16" s="11"/>
+      <c r="JM16" s="11"/>
+      <c r="JN16" s="11"/>
+      <c r="JO16" s="11"/>
+      <c r="JP16" s="11"/>
+      <c r="JQ16" s="11"/>
+      <c r="JR16" s="11"/>
+      <c r="JS16" s="11"/>
+      <c r="JT16" s="11"/>
+      <c r="JU16" s="11"/>
+      <c r="JV16" s="11"/>
+      <c r="JW16" s="11"/>
+      <c r="JX16" s="11"/>
+      <c r="JY16" s="11"/>
+      <c r="JZ16" s="11"/>
+      <c r="KA16" s="11"/>
+      <c r="KB16" s="11"/>
+      <c r="KC16" s="11"/>
+      <c r="KD16" s="11"/>
+      <c r="KE16" s="11"/>
+      <c r="KF16" s="11"/>
+      <c r="KG16" s="11"/>
+      <c r="KH16" s="11"/>
+      <c r="KI16" s="11"/>
+      <c r="KJ16" s="11"/>
+      <c r="KK16" s="11"/>
+      <c r="KL16" s="11"/>
+      <c r="KM16" s="11"/>
+      <c r="KN16" s="11"/>
+      <c r="KO16" s="11"/>
+      <c r="KP16" s="11"/>
+      <c r="KQ16" s="11"/>
+      <c r="KR16" s="11"/>
+      <c r="KS16" s="11"/>
+      <c r="KT16" s="11"/>
+      <c r="KU16" s="11"/>
+      <c r="KV16" s="11"/>
+      <c r="KW16" s="11"/>
+      <c r="KX16" s="11"/>
+      <c r="KY16" s="11"/>
+      <c r="KZ16" s="11"/>
+      <c r="LA16" s="11"/>
+      <c r="LB16" s="11"/>
+      <c r="LC16" s="11"/>
+      <c r="LD16" s="11"/>
+      <c r="LE16" s="11"/>
+      <c r="LF16" s="11"/>
+      <c r="LG16" s="11"/>
+      <c r="LH16" s="11"/>
+      <c r="LI16" s="11"/>
+      <c r="LJ16" s="11"/>
+      <c r="LK16" s="11"/>
+      <c r="LL16" s="11"/>
+      <c r="LM16" s="11"/>
+      <c r="LN16" s="11"/>
+      <c r="LO16" s="11"/>
+      <c r="LP16" s="11"/>
+      <c r="LQ16" s="11"/>
+      <c r="LR16" s="11"/>
+      <c r="LS16" s="11"/>
+      <c r="LT16" s="11"/>
+      <c r="LU16" s="11"/>
+      <c r="LV16" s="11"/>
+      <c r="LW16" s="11"/>
+      <c r="LX16" s="11"/>
+      <c r="LY16" s="11"/>
+      <c r="LZ16" s="11"/>
+      <c r="MA16" s="11"/>
+      <c r="MB16" s="11"/>
+      <c r="MC16" s="11"/>
+      <c r="MD16" s="11"/>
+      <c r="ME16" s="11"/>
+      <c r="MF16" s="11"/>
+      <c r="MG16" s="11"/>
+      <c r="MH16" s="11"/>
+      <c r="MI16" s="11"/>
+      <c r="MJ16" s="11"/>
+      <c r="MK16" s="11"/>
+      <c r="ML16" s="11"/>
+      <c r="MM16" s="11"/>
+      <c r="MN16" s="11"/>
+      <c r="MO16" s="11"/>
+      <c r="MP16" s="11"/>
+      <c r="MQ16" s="11"/>
+      <c r="MR16" s="11"/>
+      <c r="MS16" s="11"/>
+      <c r="MT16" s="11"/>
+      <c r="MU16" s="11"/>
+      <c r="MV16" s="11"/>
+      <c r="MW16" s="11"/>
+      <c r="MX16" s="11"/>
+      <c r="MY16" s="11"/>
+      <c r="MZ16" s="11"/>
+      <c r="NA16" s="11"/>
+      <c r="NB16" s="11"/>
+      <c r="NC16" s="11"/>
+      <c r="ND16" s="11"/>
+      <c r="NE16" s="11"/>
+      <c r="NF16" s="11"/>
+      <c r="NG16" s="11"/>
+      <c r="NH16" s="11"/>
+      <c r="NI16" s="11"/>
+      <c r="NJ16" s="11"/>
+      <c r="NK16" s="11"/>
+      <c r="NL16" s="11"/>
+      <c r="NM16" s="11"/>
+      <c r="NN16" s="11"/>
+      <c r="NO16" s="11"/>
+      <c r="NP16" s="11"/>
+      <c r="NQ16" s="11"/>
+      <c r="NR16" s="11"/>
+      <c r="NS16" s="11"/>
+      <c r="NT16" s="11"/>
+      <c r="NU16" s="11"/>
+      <c r="NV16" s="11"/>
+      <c r="NW16" s="11"/>
+      <c r="NX16" s="11"/>
+      <c r="NY16" s="11"/>
+      <c r="NZ16" s="11"/>
+      <c r="OA16" s="11"/>
+      <c r="OB16" s="11"/>
+      <c r="OC16" s="11"/>
+      <c r="OD16" s="11"/>
+      <c r="OE16" s="11"/>
+      <c r="OF16" s="11"/>
+      <c r="OG16" s="11"/>
+      <c r="OH16" s="11"/>
+      <c r="OI16" s="11"/>
+      <c r="OJ16" s="11"/>
+      <c r="OK16" s="11"/>
+      <c r="OL16" s="11"/>
+      <c r="OM16" s="11"/>
+      <c r="ON16" s="11"/>
+      <c r="OO16" s="11"/>
+      <c r="OP16" s="11"/>
+      <c r="OQ16" s="11"/>
+      <c r="OR16" s="11"/>
+      <c r="OS16" s="11"/>
+      <c r="OT16" s="11"/>
+      <c r="OU16" s="11"/>
+      <c r="OV16" s="11"/>
+      <c r="OW16" s="11"/>
+      <c r="OX16" s="11"/>
+      <c r="OY16" s="11"/>
+      <c r="OZ16" s="11"/>
+      <c r="PA16" s="11"/>
+      <c r="PB16" s="11"/>
+      <c r="PC16" s="11"/>
+      <c r="PD16" s="11"/>
+      <c r="PE16" s="11"/>
+      <c r="PF16" s="11"/>
+      <c r="PG16" s="11"/>
+      <c r="PH16" s="11"/>
+      <c r="PI16" s="11"/>
+      <c r="PJ16" s="11"/>
+      <c r="PK16" s="11"/>
+      <c r="PL16" s="11"/>
+      <c r="PM16" s="11"/>
+      <c r="PN16" s="11"/>
+      <c r="PO16" s="11"/>
+      <c r="PP16" s="11"/>
+      <c r="PQ16" s="11"/>
+      <c r="PR16" s="11"/>
+      <c r="PS16" s="11"/>
+      <c r="PT16" s="11"/>
+      <c r="PU16" s="11"/>
+      <c r="PV16" s="11"/>
+      <c r="PW16" s="11"/>
+      <c r="PX16" s="11"/>
+      <c r="PY16" s="11"/>
+      <c r="PZ16" s="11"/>
+      <c r="QA16" s="11"/>
+      <c r="QB16" s="11"/>
+      <c r="QC16" s="11"/>
+      <c r="QD16" s="11"/>
+      <c r="QE16" s="11"/>
+      <c r="QF16" s="11"/>
+      <c r="QG16" s="11"/>
+      <c r="QH16" s="11"/>
+      <c r="QI16" s="11"/>
+      <c r="QJ16" s="11"/>
+      <c r="QK16" s="11"/>
+      <c r="QL16" s="11"/>
+      <c r="QM16" s="11"/>
+      <c r="QN16" s="11"/>
+      <c r="QO16" s="11"/>
+      <c r="QP16" s="11"/>
+      <c r="QQ16" s="11"/>
+      <c r="QR16" s="11"/>
+      <c r="QS16" s="11"/>
+      <c r="QT16" s="11"/>
+      <c r="QU16" s="11"/>
+      <c r="QV16" s="11"/>
+      <c r="QW16" s="11"/>
+      <c r="QX16" s="11"/>
+      <c r="QY16" s="11"/>
+      <c r="QZ16" s="11"/>
+      <c r="RA16" s="11"/>
+      <c r="RB16" s="11"/>
+      <c r="RC16" s="11"/>
+      <c r="RD16" s="11"/>
+      <c r="RE16" s="11"/>
+      <c r="RF16" s="11"/>
+      <c r="RG16" s="11"/>
+      <c r="RH16" s="11"/>
+      <c r="RI16" s="11"/>
+      <c r="RJ16" s="11"/>
+      <c r="RK16" s="11"/>
+      <c r="RL16" s="11"/>
+      <c r="RM16" s="11"/>
+      <c r="RN16" s="11"/>
+      <c r="RO16" s="11"/>
+      <c r="RP16" s="11"/>
+      <c r="RQ16" s="11"/>
+      <c r="RR16" s="11"/>
+      <c r="RS16" s="11"/>
+      <c r="RT16" s="11"/>
+      <c r="RU16" s="11"/>
+      <c r="RV16" s="11"/>
+      <c r="RW16" s="11"/>
+      <c r="RX16" s="11"/>
+      <c r="RY16" s="11"/>
+      <c r="RZ16" s="11"/>
+      <c r="SA16" s="11"/>
+      <c r="SB16" s="11"/>
+      <c r="SC16" s="11"/>
+      <c r="SD16" s="11"/>
+      <c r="SE16" s="11"/>
+      <c r="SF16" s="11"/>
+      <c r="SG16" s="11"/>
+      <c r="SH16" s="11"/>
+      <c r="SI16" s="11"/>
+      <c r="SJ16" s="11"/>
+      <c r="SK16" s="11"/>
+      <c r="SL16" s="11"/>
+      <c r="SM16" s="11"/>
+      <c r="SN16" s="11"/>
+      <c r="SO16" s="11"/>
+      <c r="SP16" s="11"/>
+      <c r="SQ16" s="11"/>
+      <c r="SR16" s="11"/>
+      <c r="SS16" s="11"/>
+      <c r="ST16" s="11"/>
+      <c r="SU16" s="11"/>
+      <c r="SV16" s="11"/>
+      <c r="SW16" s="11"/>
+      <c r="SX16" s="11"/>
+      <c r="SY16" s="11"/>
+      <c r="SZ16" s="11"/>
+      <c r="TA16" s="11"/>
+      <c r="TB16" s="11"/>
+      <c r="TC16" s="11"/>
+      <c r="TD16" s="11"/>
+      <c r="TE16" s="11"/>
+      <c r="TF16" s="11"/>
+      <c r="TG16" s="11"/>
+      <c r="TH16" s="11"/>
+      <c r="TI16" s="11"/>
+      <c r="TJ16" s="11"/>
+      <c r="TK16" s="11"/>
+      <c r="TL16" s="11"/>
+      <c r="TM16" s="11"/>
+      <c r="TN16" s="11"/>
+      <c r="TO16" s="11"/>
+      <c r="TP16" s="11"/>
+      <c r="TQ16" s="11"/>
+      <c r="TR16" s="11"/>
+      <c r="TS16" s="11"/>
+      <c r="TT16" s="11"/>
+      <c r="TU16" s="11"/>
+      <c r="TV16" s="11"/>
+      <c r="TW16" s="11"/>
+      <c r="TX16" s="11"/>
+      <c r="TY16" s="11"/>
+      <c r="TZ16" s="11"/>
+      <c r="UA16" s="11"/>
+      <c r="UB16" s="11"/>
+      <c r="UC16" s="11"/>
+      <c r="UD16" s="11"/>
+      <c r="UE16" s="11"/>
+      <c r="UF16" s="11"/>
+      <c r="UG16" s="11"/>
+      <c r="UH16" s="11"/>
+      <c r="UI16" s="11"/>
+      <c r="UJ16" s="11"/>
+      <c r="UK16" s="11"/>
+      <c r="UL16" s="11"/>
+      <c r="UM16" s="11"/>
+      <c r="UN16" s="11"/>
+      <c r="UO16" s="11"/>
+      <c r="UP16" s="11"/>
+      <c r="UQ16" s="11"/>
+      <c r="UR16" s="11"/>
+      <c r="US16" s="11"/>
+      <c r="UT16" s="11"/>
+      <c r="UU16" s="11"/>
+      <c r="UV16" s="11"/>
+      <c r="UW16" s="11"/>
+      <c r="UX16" s="11"/>
+      <c r="UY16" s="11"/>
+      <c r="UZ16" s="11"/>
+      <c r="VA16" s="11"/>
+      <c r="VB16" s="11"/>
+      <c r="VC16" s="11"/>
+      <c r="VD16" s="11"/>
+      <c r="VE16" s="11"/>
+      <c r="VF16" s="11"/>
+      <c r="VG16" s="11"/>
+      <c r="VH16" s="11"/>
+      <c r="VI16" s="11"/>
+      <c r="VJ16" s="11"/>
+      <c r="VK16" s="11"/>
+      <c r="VL16" s="11"/>
+      <c r="VM16" s="11"/>
+      <c r="VN16" s="11"/>
+      <c r="VO16" s="11"/>
+      <c r="VP16" s="11"/>
+      <c r="VQ16" s="11"/>
+      <c r="VR16" s="11"/>
+      <c r="VS16" s="11"/>
+      <c r="VT16" s="11"/>
+      <c r="VU16" s="11"/>
+      <c r="VV16" s="11"/>
+      <c r="VW16" s="11"/>
+      <c r="VX16" s="11"/>
+      <c r="VY16" s="11"/>
+      <c r="VZ16" s="11"/>
+      <c r="WA16" s="11"/>
+      <c r="WB16" s="11"/>
+      <c r="WC16" s="11"/>
+      <c r="WD16" s="11"/>
+      <c r="WE16" s="11"/>
+      <c r="WF16" s="11"/>
+      <c r="WG16" s="11"/>
+      <c r="WH16" s="11"/>
+      <c r="WI16" s="11"/>
+      <c r="WJ16" s="11"/>
+      <c r="WK16" s="11"/>
+      <c r="WL16" s="11"/>
+      <c r="WM16" s="11"/>
+      <c r="WN16" s="11"/>
+      <c r="WO16" s="11"/>
+      <c r="WP16" s="11"/>
+      <c r="WQ16" s="11"/>
+      <c r="WR16" s="11"/>
+      <c r="WS16" s="11"/>
+      <c r="WT16" s="11"/>
+      <c r="WU16" s="11"/>
+      <c r="WV16" s="11"/>
+      <c r="WW16" s="11"/>
+      <c r="WX16" s="11"/>
+      <c r="WY16" s="11"/>
+      <c r="WZ16" s="11"/>
+      <c r="XA16" s="11"/>
+      <c r="XB16" s="11"/>
+      <c r="XC16" s="11"/>
+      <c r="XD16" s="11"/>
+      <c r="XE16" s="11"/>
+      <c r="XF16" s="11"/>
+      <c r="XG16" s="11"/>
+      <c r="XH16" s="11"/>
+      <c r="XI16" s="11"/>
+      <c r="XJ16" s="11"/>
+      <c r="XK16" s="11"/>
+      <c r="XL16" s="11"/>
+      <c r="XM16" s="11"/>
+      <c r="XN16" s="11"/>
+      <c r="XO16" s="11"/>
+      <c r="XP16" s="11"/>
+      <c r="XQ16" s="11"/>
+      <c r="XR16" s="11"/>
+      <c r="XS16" s="11"/>
+      <c r="XT16" s="11"/>
+      <c r="XU16" s="11"/>
+      <c r="XV16" s="11"/>
+      <c r="XW16" s="11"/>
+      <c r="XX16" s="11"/>
+      <c r="XY16" s="11"/>
+      <c r="XZ16" s="11"/>
+      <c r="YA16" s="11"/>
+      <c r="YB16" s="11"/>
+      <c r="YC16" s="11"/>
+      <c r="YD16" s="11"/>
+      <c r="YE16" s="11"/>
+      <c r="YF16" s="11"/>
+      <c r="YG16" s="11"/>
+      <c r="YH16" s="11"/>
+      <c r="YI16" s="11"/>
+      <c r="YJ16" s="11"/>
+      <c r="YK16" s="11"/>
+      <c r="YL16" s="11"/>
+      <c r="YM16" s="11"/>
+      <c r="YN16" s="11"/>
+      <c r="YO16" s="11"/>
+      <c r="YP16" s="11"/>
+      <c r="YQ16" s="11"/>
+      <c r="YR16" s="11"/>
+      <c r="YS16" s="11"/>
+      <c r="YT16" s="11"/>
+      <c r="YU16" s="11"/>
+      <c r="YV16" s="11"/>
+      <c r="YW16" s="11"/>
+      <c r="YX16" s="11"/>
+      <c r="YY16" s="11"/>
+      <c r="YZ16" s="11"/>
+      <c r="ZA16" s="11"/>
+      <c r="ZB16" s="11"/>
+      <c r="ZC16" s="11"/>
+      <c r="ZD16" s="11"/>
+      <c r="ZE16" s="11"/>
+      <c r="ZF16" s="11"/>
+      <c r="ZG16" s="11"/>
+      <c r="ZH16" s="11"/>
+      <c r="ZI16" s="11"/>
+      <c r="ZJ16" s="11"/>
+      <c r="ZK16" s="11"/>
+      <c r="ZL16" s="11"/>
+      <c r="ZM16" s="11"/>
+      <c r="ZN16" s="11"/>
+      <c r="ZO16" s="11"/>
+      <c r="ZP16" s="11"/>
+      <c r="ZQ16" s="11"/>
+      <c r="ZR16" s="11"/>
+      <c r="ZS16" s="11"/>
+      <c r="ZT16" s="11"/>
+      <c r="ZU16" s="11"/>
+      <c r="ZV16" s="11"/>
+      <c r="ZW16" s="11"/>
+      <c r="ZX16" s="11"/>
+      <c r="ZY16" s="11"/>
+      <c r="ZZ16" s="11"/>
+      <c r="AAA16" s="11"/>
+      <c r="AAB16" s="11"/>
+      <c r="AAC16" s="11"/>
+      <c r="AAD16" s="11"/>
+      <c r="AAE16" s="11"/>
+      <c r="AAF16" s="11"/>
+      <c r="AAG16" s="11"/>
+      <c r="AAH16" s="11"/>
+      <c r="AAI16" s="11"/>
+      <c r="AAJ16" s="11"/>
+      <c r="AAK16" s="11"/>
+      <c r="AAL16" s="11"/>
+      <c r="AAM16" s="11"/>
+      <c r="AAN16" s="11"/>
+      <c r="AAO16" s="11"/>
+      <c r="AAP16" s="11"/>
+      <c r="AAQ16" s="11"/>
+      <c r="AAR16" s="11"/>
+      <c r="AAS16" s="11"/>
+      <c r="AAT16" s="11"/>
+      <c r="AAU16" s="11"/>
+      <c r="AAV16" s="11"/>
+      <c r="AAW16" s="11"/>
+      <c r="AAX16" s="11"/>
+      <c r="AAY16" s="11"/>
+      <c r="AAZ16" s="11"/>
+      <c r="ABA16" s="11"/>
+      <c r="ABB16" s="11"/>
+      <c r="ABC16" s="11"/>
+      <c r="ABD16" s="11"/>
+      <c r="ABE16" s="11"/>
+      <c r="ABF16" s="11"/>
+      <c r="ABG16" s="11"/>
+      <c r="ABH16" s="11"/>
+      <c r="ABI16" s="11"/>
+      <c r="ABJ16" s="11"/>
+      <c r="ABK16" s="11"/>
+      <c r="ABL16" s="11"/>
+      <c r="ABM16" s="11"/>
+      <c r="ABN16" s="11"/>
+      <c r="ABO16" s="11"/>
+      <c r="ABP16" s="11"/>
+      <c r="ABQ16" s="11"/>
+      <c r="ABR16" s="11"/>
+      <c r="ABS16" s="11"/>
+      <c r="ABT16" s="11"/>
+      <c r="ABU16" s="11"/>
+      <c r="ABV16" s="11"/>
+      <c r="ABW16" s="11"/>
+      <c r="ABX16" s="11"/>
+      <c r="ABY16" s="11"/>
+      <c r="ABZ16" s="11"/>
+      <c r="ACA16" s="11"/>
+      <c r="ACB16" s="11"/>
+      <c r="ACC16" s="11"/>
+      <c r="ACD16" s="11"/>
+      <c r="ACE16" s="11"/>
+      <c r="ACF16" s="11"/>
+      <c r="ACG16" s="11"/>
+      <c r="ACH16" s="11"/>
+      <c r="ACI16" s="11"/>
+      <c r="ACJ16" s="11"/>
+      <c r="ACK16" s="11"/>
+      <c r="ACL16" s="11"/>
+      <c r="ACM16" s="11"/>
+      <c r="ACN16" s="11"/>
+      <c r="ACO16" s="11"/>
+      <c r="ACP16" s="11"/>
+      <c r="ACQ16" s="11"/>
+      <c r="ACR16" s="11"/>
+      <c r="ACS16" s="11"/>
+      <c r="ACT16" s="11"/>
+      <c r="ACU16" s="11"/>
+      <c r="ACV16" s="11"/>
+      <c r="ACW16" s="11"/>
+      <c r="ACX16" s="11"/>
+      <c r="ACY16" s="11"/>
+      <c r="ACZ16" s="11"/>
+      <c r="ADA16" s="11"/>
+      <c r="ADB16" s="11"/>
+      <c r="ADC16" s="11"/>
+      <c r="ADD16" s="11"/>
+      <c r="ADE16" s="11"/>
+      <c r="ADF16" s="11"/>
+      <c r="ADG16" s="11"/>
+      <c r="ADH16" s="11"/>
+      <c r="ADI16" s="11"/>
+      <c r="ADJ16" s="11"/>
+      <c r="ADK16" s="11"/>
+      <c r="ADL16" s="11"/>
+      <c r="ADM16" s="11"/>
+      <c r="ADN16" s="11"/>
+      <c r="ADO16" s="11"/>
+      <c r="ADP16" s="11"/>
+      <c r="ADQ16" s="11"/>
+      <c r="ADR16" s="11"/>
+      <c r="ADS16" s="11"/>
+      <c r="ADT16" s="11"/>
+      <c r="ADU16" s="11"/>
+      <c r="ADV16" s="11"/>
+      <c r="ADW16" s="11"/>
+      <c r="ADX16" s="11"/>
+      <c r="ADY16" s="11"/>
+      <c r="ADZ16" s="11"/>
+      <c r="AEA16" s="11"/>
+      <c r="AEB16" s="11"/>
+      <c r="AEC16" s="11"/>
+      <c r="AED16" s="11"/>
+      <c r="AEE16" s="11"/>
+      <c r="AEF16" s="11"/>
+      <c r="AEG16" s="11"/>
+      <c r="AEH16" s="11"/>
+      <c r="AEI16" s="11"/>
+      <c r="AEJ16" s="11"/>
+      <c r="AEK16" s="11"/>
+      <c r="AEL16" s="11"/>
+      <c r="AEM16" s="11"/>
+      <c r="AEN16" s="11"/>
+      <c r="AEO16" s="11"/>
+      <c r="AEP16" s="11"/>
+      <c r="AEQ16" s="11"/>
+      <c r="AER16" s="11"/>
+      <c r="AES16" s="11"/>
+      <c r="AET16" s="11"/>
+      <c r="AEU16" s="11"/>
+      <c r="AEV16" s="11"/>
+      <c r="AEW16" s="11"/>
+      <c r="AEX16" s="11"/>
+      <c r="AEY16" s="11"/>
+      <c r="AEZ16" s="11"/>
+      <c r="AFA16" s="11"/>
+      <c r="AFB16" s="11"/>
+      <c r="AFC16" s="11"/>
+      <c r="AFD16" s="11"/>
+      <c r="AFE16" s="11"/>
+      <c r="AFF16" s="11"/>
+      <c r="AFG16" s="11"/>
+      <c r="AFH16" s="11"/>
+      <c r="AFI16" s="11"/>
+      <c r="AFJ16" s="11"/>
+      <c r="AFK16" s="11"/>
+      <c r="AFL16" s="11"/>
+      <c r="AFM16" s="11"/>
+      <c r="AFN16" s="11"/>
+      <c r="AFO16" s="11"/>
+      <c r="AFP16" s="11"/>
+      <c r="AFQ16" s="11"/>
+      <c r="AFR16" s="11"/>
+      <c r="AFS16" s="11"/>
+      <c r="AFT16" s="11"/>
+      <c r="AFU16" s="11"/>
+      <c r="AFV16" s="11"/>
+      <c r="AFW16" s="11"/>
+      <c r="AFX16" s="11"/>
+      <c r="AFY16" s="11"/>
+      <c r="AFZ16" s="11"/>
+      <c r="AGA16" s="11"/>
+      <c r="AGB16" s="11"/>
+      <c r="AGC16" s="11"/>
+      <c r="AGD16" s="11"/>
+      <c r="AGE16" s="11"/>
+      <c r="AGF16" s="11"/>
+      <c r="AGG16" s="11"/>
+      <c r="AGH16" s="11"/>
+      <c r="AGI16" s="11"/>
+      <c r="AGJ16" s="11"/>
+      <c r="AGK16" s="11"/>
+      <c r="AGL16" s="11"/>
+      <c r="AGM16" s="11"/>
+      <c r="AGN16" s="11"/>
+      <c r="AGO16" s="11"/>
+      <c r="AGP16" s="11"/>
+      <c r="AGQ16" s="11"/>
+      <c r="AGR16" s="11"/>
+      <c r="AGS16" s="11"/>
+      <c r="AGT16" s="11"/>
+      <c r="AGU16" s="11"/>
+      <c r="AGV16" s="11"/>
+      <c r="AGW16" s="11"/>
+      <c r="AGX16" s="11"/>
+      <c r="AGY16" s="11"/>
+      <c r="AGZ16" s="11"/>
+      <c r="AHA16" s="11"/>
+      <c r="AHB16" s="11"/>
+      <c r="AHC16" s="11"/>
+      <c r="AHD16" s="11"/>
+      <c r="AHE16" s="11"/>
+      <c r="AHF16" s="11"/>
+      <c r="AHG16" s="11"/>
+      <c r="AHH16" s="11"/>
+      <c r="AHI16" s="11"/>
+      <c r="AHJ16" s="11"/>
+      <c r="AHK16" s="11"/>
+      <c r="AHL16" s="11"/>
+      <c r="AHM16" s="11"/>
+      <c r="AHN16" s="11"/>
+      <c r="AHO16" s="11"/>
+      <c r="AHP16" s="11"/>
+      <c r="AHQ16" s="11"/>
+      <c r="AHR16" s="11"/>
+      <c r="AHS16" s="11"/>
+      <c r="AHT16" s="11"/>
+      <c r="AHU16" s="11"/>
+      <c r="AHV16" s="11"/>
+      <c r="AHW16" s="11"/>
+      <c r="AHX16" s="11"/>
+      <c r="AHY16" s="11"/>
+      <c r="AHZ16" s="11"/>
+      <c r="AIA16" s="11"/>
+      <c r="AIB16" s="11"/>
+      <c r="AIC16" s="11"/>
+      <c r="AID16" s="11"/>
+      <c r="AIE16" s="11"/>
+      <c r="AIF16" s="11"/>
+      <c r="AIG16" s="11"/>
+      <c r="AIH16" s="11"/>
+      <c r="AII16" s="11"/>
+      <c r="AIJ16" s="11"/>
+      <c r="AIK16" s="11"/>
+      <c r="AIL16" s="11"/>
+      <c r="AIM16" s="11"/>
+      <c r="AIN16" s="11"/>
+      <c r="AIO16" s="11"/>
+      <c r="AIP16" s="11"/>
+      <c r="AIQ16" s="11"/>
+      <c r="AIR16" s="11"/>
+      <c r="AIS16" s="11"/>
+      <c r="AIT16" s="11"/>
+      <c r="AIU16" s="11"/>
+      <c r="AIV16" s="11"/>
+      <c r="AIW16" s="11"/>
+      <c r="AIX16" s="11"/>
+      <c r="AIY16" s="11"/>
+      <c r="AIZ16" s="11"/>
+      <c r="AJA16" s="11"/>
+      <c r="AJB16" s="11"/>
+      <c r="AJC16" s="11"/>
+      <c r="AJD16" s="11"/>
+      <c r="AJE16" s="11"/>
+      <c r="AJF16" s="11"/>
+      <c r="AJG16" s="11"/>
+      <c r="AJH16" s="11"/>
+      <c r="AJI16" s="11"/>
+      <c r="AJJ16" s="11"/>
+      <c r="AJK16" s="11"/>
+      <c r="AJL16" s="11"/>
+      <c r="AJM16" s="11"/>
+      <c r="AJN16" s="11"/>
+      <c r="AJO16" s="11"/>
+      <c r="AJP16" s="11"/>
+      <c r="AJQ16" s="11"/>
+      <c r="AJR16" s="11"/>
+      <c r="AJS16" s="11"/>
+      <c r="AJT16" s="11"/>
+      <c r="AJU16" s="11"/>
+      <c r="AJV16" s="11"/>
+      <c r="AJW16" s="11"/>
+      <c r="AJX16" s="11"/>
+      <c r="AJY16" s="11"/>
+      <c r="AJZ16" s="11"/>
+      <c r="AKA16" s="11"/>
+      <c r="AKB16" s="11"/>
+      <c r="AKC16" s="11"/>
+      <c r="AKD16" s="11"/>
+      <c r="AKE16" s="11"/>
+      <c r="AKF16" s="11"/>
+      <c r="AKG16" s="11"/>
+      <c r="AKH16" s="11"/>
+      <c r="AKI16" s="11"/>
+      <c r="AKJ16" s="11"/>
+      <c r="AKK16" s="11"/>
+      <c r="AKL16" s="11"/>
+      <c r="AKM16" s="11"/>
+      <c r="AKN16" s="11"/>
+      <c r="AKO16" s="11"/>
+      <c r="AKP16" s="11"/>
+      <c r="AKQ16" s="11"/>
+      <c r="AKR16" s="11"/>
+      <c r="AKS16" s="11"/>
+      <c r="AKT16" s="11"/>
+      <c r="AKU16" s="11"/>
+      <c r="AKV16" s="11"/>
+      <c r="AKW16" s="11"/>
+      <c r="AKX16" s="11"/>
+      <c r="AKY16" s="11"/>
+      <c r="AKZ16" s="11"/>
+      <c r="ALA16" s="11"/>
+      <c r="ALB16" s="11"/>
+      <c r="ALC16" s="11"/>
+      <c r="ALD16" s="11"/>
+      <c r="ALE16" s="11"/>
+      <c r="ALF16" s="11"/>
+      <c r="ALG16" s="11"/>
+      <c r="ALH16" s="11"/>
+      <c r="ALI16" s="11"/>
+      <c r="ALJ16" s="11"/>
+      <c r="ALK16" s="11"/>
+      <c r="ALL16" s="11"/>
+      <c r="ALM16" s="11"/>
+      <c r="ALN16" s="11"/>
+      <c r="ALO16" s="11"/>
+      <c r="ALP16" s="11"/>
+      <c r="ALQ16" s="11"/>
+      <c r="ALR16" s="11"/>
+      <c r="ALS16" s="11"/>
+      <c r="ALT16" s="11"/>
+      <c r="ALU16" s="11"/>
+      <c r="ALV16" s="11"/>
+      <c r="ALW16" s="11"/>
+      <c r="ALX16" s="11"/>
+      <c r="ALY16" s="11"/>
+      <c r="ALZ16" s="11"/>
+      <c r="AMA16" s="11"/>
+      <c r="AMB16" s="11"/>
+      <c r="AMC16" s="11"/>
+      <c r="AMD16" s="11"/>
+      <c r="AME16" s="11"/>
+      <c r="AMF16" s="11"/>
+      <c r="AMG16" s="11"/>
+      <c r="AMH16" s="11"/>
+      <c r="AMI16" s="11"/>
+      <c r="AMJ16" s="0"/>
+    </row>
+    <row r="17" customFormat="false" ht="258.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="14" t="s">
         <v>128</v>
       </c>
       <c r="B17" s="17"/>
       <c r="C17" s="17"/>
-      <c r="D17" s="16" t="s">
+      <c r="D17" s="15" t="s">
         <v>204</v>
       </c>
-      <c r="E17" s="16" t="s">
+      <c r="E17" s="15" t="s">
         <v>205</v>
       </c>
-      <c r="F17" s="16" t="s">
+      <c r="F17" s="15" t="s">
         <v>206</v>
       </c>
-      <c r="G17" s="16" t="s">
+      <c r="G17" s="15" t="s">
         <v>207</v>
       </c>
-      <c r="H17" s="16" t="s">
+      <c r="H17" s="15" t="s">
         <v>208</v>
       </c>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="16"/>
+      <c r="L17" s="16"/>
+      <c r="M17" s="16"/>
+      <c r="N17" s="16"/>
+      <c r="O17" s="16"/>
+      <c r="P17" s="16"/>
+      <c r="Q17" s="16"/>
+      <c r="R17" s="16"/>
+      <c r="S17" s="16"/>
+      <c r="T17" s="16"/>
+      <c r="U17" s="16"/>
+      <c r="V17" s="16"/>
+      <c r="W17" s="16"/>
+      <c r="X17" s="16"/>
+      <c r="Y17" s="16"/>
+      <c r="Z17" s="16"/>
+      <c r="AA17" s="16"/>
+      <c r="AB17" s="16"/>
+      <c r="AC17" s="16"/>
+      <c r="AD17" s="16"/>
+      <c r="AE17" s="16"/>
+      <c r="AF17" s="16"/>
+      <c r="AG17" s="16"/>
+      <c r="AH17" s="16"/>
+      <c r="AI17" s="16"/>
+      <c r="AJ17" s="16"/>
+      <c r="AK17" s="16"/>
+      <c r="AL17" s="16"/>
+      <c r="AM17" s="16"/>
+      <c r="AN17" s="16"/>
+      <c r="AO17" s="16"/>
+      <c r="AP17" s="16"/>
+      <c r="AQ17" s="16"/>
+      <c r="AR17" s="16"/>
+      <c r="AS17" s="16"/>
+      <c r="AT17" s="16"/>
+      <c r="AU17" s="16"/>
+      <c r="AV17" s="16"/>
+      <c r="AW17" s="16"/>
+      <c r="AX17" s="16"/>
+      <c r="AY17" s="16"/>
+      <c r="AZ17" s="16"/>
+      <c r="BA17" s="16"/>
+      <c r="BB17" s="16"/>
+      <c r="BC17" s="16"/>
+      <c r="BD17" s="16"/>
+      <c r="BE17" s="16"/>
+      <c r="BF17" s="16"/>
+      <c r="BG17" s="16"/>
+      <c r="BH17" s="16"/>
+      <c r="BI17" s="16"/>
+      <c r="BJ17" s="16"/>
+      <c r="BK17" s="16"/>
+      <c r="BL17" s="16"/>
+      <c r="BM17" s="16"/>
+      <c r="BN17" s="16"/>
+      <c r="BO17" s="16"/>
+      <c r="BP17" s="16"/>
+      <c r="BQ17" s="16"/>
+      <c r="BR17" s="16"/>
+      <c r="BS17" s="16"/>
+      <c r="BT17" s="16"/>
+      <c r="BU17" s="16"/>
+      <c r="BV17" s="16"/>
+      <c r="BW17" s="16"/>
+      <c r="BX17" s="16"/>
+      <c r="BY17" s="16"/>
+      <c r="BZ17" s="16"/>
+      <c r="CA17" s="16"/>
+      <c r="CB17" s="16"/>
+      <c r="CC17" s="16"/>
+      <c r="CD17" s="16"/>
+      <c r="CE17" s="16"/>
+      <c r="CF17" s="16"/>
+      <c r="CG17" s="16"/>
+      <c r="CH17" s="16"/>
+      <c r="CI17" s="16"/>
+      <c r="CJ17" s="16"/>
+      <c r="CK17" s="16"/>
+      <c r="CL17" s="16"/>
+      <c r="CM17" s="16"/>
+      <c r="CN17" s="16"/>
+      <c r="CO17" s="16"/>
+      <c r="CP17" s="16"/>
+      <c r="CQ17" s="16"/>
+      <c r="CR17" s="16"/>
+      <c r="CS17" s="16"/>
+      <c r="CT17" s="16"/>
+      <c r="CU17" s="16"/>
+      <c r="CV17" s="16"/>
+      <c r="CW17" s="16"/>
+      <c r="CX17" s="16"/>
+      <c r="CY17" s="16"/>
+      <c r="CZ17" s="16"/>
+      <c r="DA17" s="16"/>
+      <c r="DB17" s="16"/>
+      <c r="DC17" s="16"/>
+      <c r="DD17" s="16"/>
+      <c r="DE17" s="16"/>
+      <c r="DF17" s="16"/>
+      <c r="DG17" s="16"/>
+      <c r="DH17" s="16"/>
+      <c r="DI17" s="16"/>
+      <c r="DJ17" s="16"/>
+      <c r="DK17" s="16"/>
+      <c r="DL17" s="16"/>
+      <c r="DM17" s="16"/>
+      <c r="DN17" s="16"/>
+      <c r="DO17" s="16"/>
+      <c r="DP17" s="16"/>
+      <c r="DQ17" s="16"/>
+      <c r="DR17" s="16"/>
+      <c r="DS17" s="16"/>
+      <c r="DT17" s="16"/>
+      <c r="DU17" s="16"/>
+      <c r="DV17" s="16"/>
+      <c r="DW17" s="16"/>
+      <c r="DX17" s="16"/>
+      <c r="DY17" s="16"/>
+      <c r="DZ17" s="16"/>
+      <c r="EA17" s="16"/>
+      <c r="EB17" s="16"/>
+      <c r="EC17" s="16"/>
+      <c r="ED17" s="16"/>
+      <c r="EE17" s="16"/>
+      <c r="EF17" s="16"/>
+      <c r="EG17" s="16"/>
+      <c r="EH17" s="16"/>
+      <c r="EI17" s="16"/>
+      <c r="EJ17" s="16"/>
+      <c r="EK17" s="16"/>
+      <c r="EL17" s="16"/>
+      <c r="EM17" s="16"/>
+      <c r="EN17" s="16"/>
+      <c r="EO17" s="16"/>
+      <c r="EP17" s="16"/>
+      <c r="EQ17" s="16"/>
+      <c r="ER17" s="16"/>
+      <c r="ES17" s="16"/>
+      <c r="ET17" s="16"/>
+      <c r="EU17" s="16"/>
+      <c r="EV17" s="16"/>
+      <c r="EW17" s="16"/>
+      <c r="EX17" s="16"/>
+      <c r="EY17" s="16"/>
+      <c r="EZ17" s="16"/>
+      <c r="FA17" s="16"/>
+      <c r="FB17" s="16"/>
+      <c r="FC17" s="16"/>
+      <c r="FD17" s="16"/>
+      <c r="FE17" s="16"/>
+      <c r="FF17" s="16"/>
+      <c r="FG17" s="16"/>
+      <c r="FH17" s="16"/>
+      <c r="FI17" s="16"/>
+      <c r="FJ17" s="16"/>
+      <c r="FK17" s="16"/>
+      <c r="FL17" s="16"/>
+      <c r="FM17" s="16"/>
+      <c r="FN17" s="16"/>
+      <c r="FO17" s="16"/>
+      <c r="FP17" s="16"/>
+      <c r="FQ17" s="16"/>
+      <c r="FR17" s="16"/>
+      <c r="FS17" s="16"/>
+      <c r="FT17" s="16"/>
+      <c r="FU17" s="16"/>
+      <c r="FV17" s="16"/>
+      <c r="FW17" s="16"/>
+      <c r="FX17" s="16"/>
+      <c r="FY17" s="16"/>
+      <c r="FZ17" s="16"/>
+      <c r="GA17" s="16"/>
+      <c r="GB17" s="16"/>
+      <c r="GC17" s="16"/>
+      <c r="GD17" s="16"/>
+      <c r="GE17" s="16"/>
+      <c r="GF17" s="16"/>
+      <c r="GG17" s="16"/>
+      <c r="GH17" s="16"/>
+      <c r="GI17" s="16"/>
+      <c r="GJ17" s="16"/>
+      <c r="GK17" s="16"/>
+      <c r="GL17" s="16"/>
+      <c r="GM17" s="16"/>
+      <c r="GN17" s="16"/>
+      <c r="GO17" s="16"/>
+      <c r="GP17" s="16"/>
+      <c r="GQ17" s="16"/>
+      <c r="GR17" s="16"/>
+      <c r="GS17" s="16"/>
+      <c r="GT17" s="16"/>
+      <c r="GU17" s="16"/>
+      <c r="GV17" s="16"/>
+      <c r="GW17" s="16"/>
+      <c r="GX17" s="16"/>
+      <c r="GY17" s="16"/>
+      <c r="GZ17" s="16"/>
+      <c r="HA17" s="16"/>
+      <c r="HB17" s="16"/>
+      <c r="HC17" s="16"/>
+      <c r="HD17" s="16"/>
+      <c r="HE17" s="16"/>
+      <c r="HF17" s="16"/>
+      <c r="HG17" s="16"/>
+      <c r="HH17" s="16"/>
+      <c r="HI17" s="16"/>
+      <c r="HJ17" s="16"/>
+      <c r="HK17" s="16"/>
+      <c r="HL17" s="16"/>
+      <c r="HM17" s="16"/>
+      <c r="HN17" s="16"/>
+      <c r="HO17" s="16"/>
+      <c r="HP17" s="16"/>
+      <c r="HQ17" s="16"/>
+      <c r="HR17" s="16"/>
+      <c r="HS17" s="16"/>
+      <c r="HT17" s="16"/>
+      <c r="HU17" s="16"/>
+      <c r="HV17" s="16"/>
+      <c r="HW17" s="16"/>
+      <c r="HX17" s="16"/>
+      <c r="HY17" s="16"/>
+      <c r="HZ17" s="16"/>
+      <c r="IA17" s="16"/>
+      <c r="IB17" s="16"/>
+      <c r="IC17" s="16"/>
+      <c r="ID17" s="16"/>
+      <c r="IE17" s="16"/>
+      <c r="IF17" s="16"/>
+      <c r="IG17" s="16"/>
+      <c r="IH17" s="16"/>
+      <c r="II17" s="16"/>
+      <c r="IJ17" s="16"/>
+      <c r="IK17" s="16"/>
+      <c r="IL17" s="16"/>
+      <c r="IM17" s="16"/>
+      <c r="IN17" s="16"/>
+      <c r="IO17" s="16"/>
+      <c r="IP17" s="16"/>
+      <c r="IQ17" s="16"/>
+      <c r="IR17" s="16"/>
+      <c r="IS17" s="16"/>
+      <c r="IT17" s="16"/>
+      <c r="IU17" s="16"/>
+      <c r="IV17" s="16"/>
+      <c r="IW17" s="16"/>
+      <c r="IX17" s="16"/>
+      <c r="IY17" s="16"/>
+      <c r="IZ17" s="16"/>
+      <c r="JA17" s="16"/>
+      <c r="JB17" s="16"/>
+      <c r="JC17" s="16"/>
+      <c r="JD17" s="16"/>
+      <c r="JE17" s="16"/>
+      <c r="JF17" s="16"/>
+      <c r="JG17" s="16"/>
+      <c r="JH17" s="16"/>
+      <c r="JI17" s="16"/>
+      <c r="JJ17" s="16"/>
+      <c r="JK17" s="16"/>
+      <c r="JL17" s="16"/>
+      <c r="JM17" s="16"/>
+      <c r="JN17" s="16"/>
+      <c r="JO17" s="16"/>
+      <c r="JP17" s="16"/>
+      <c r="JQ17" s="16"/>
+      <c r="JR17" s="16"/>
+      <c r="JS17" s="16"/>
+      <c r="JT17" s="16"/>
+      <c r="JU17" s="16"/>
+      <c r="JV17" s="16"/>
+      <c r="JW17" s="16"/>
+      <c r="JX17" s="16"/>
+      <c r="JY17" s="16"/>
+      <c r="JZ17" s="16"/>
+      <c r="KA17" s="16"/>
+      <c r="KB17" s="16"/>
+      <c r="KC17" s="16"/>
+      <c r="KD17" s="16"/>
+      <c r="KE17" s="16"/>
+      <c r="KF17" s="16"/>
+      <c r="KG17" s="16"/>
+      <c r="KH17" s="16"/>
+      <c r="KI17" s="16"/>
+      <c r="KJ17" s="16"/>
+      <c r="KK17" s="16"/>
+      <c r="KL17" s="16"/>
+      <c r="KM17" s="16"/>
+      <c r="KN17" s="16"/>
+      <c r="KO17" s="16"/>
+      <c r="KP17" s="16"/>
+      <c r="KQ17" s="16"/>
+      <c r="KR17" s="16"/>
+      <c r="KS17" s="16"/>
+      <c r="KT17" s="16"/>
+      <c r="KU17" s="16"/>
+      <c r="KV17" s="16"/>
+      <c r="KW17" s="16"/>
+      <c r="KX17" s="16"/>
+      <c r="KY17" s="16"/>
+      <c r="KZ17" s="16"/>
+      <c r="LA17" s="16"/>
+      <c r="LB17" s="16"/>
+      <c r="LC17" s="16"/>
+      <c r="LD17" s="16"/>
+      <c r="LE17" s="16"/>
+      <c r="LF17" s="16"/>
+      <c r="LG17" s="16"/>
+      <c r="LH17" s="16"/>
+      <c r="LI17" s="16"/>
+      <c r="LJ17" s="16"/>
+      <c r="LK17" s="16"/>
+      <c r="LL17" s="16"/>
+      <c r="LM17" s="16"/>
+      <c r="LN17" s="16"/>
+      <c r="LO17" s="16"/>
+      <c r="LP17" s="16"/>
+      <c r="LQ17" s="16"/>
+      <c r="LR17" s="16"/>
+      <c r="LS17" s="16"/>
+      <c r="LT17" s="16"/>
+      <c r="LU17" s="16"/>
+      <c r="LV17" s="16"/>
+      <c r="LW17" s="16"/>
+      <c r="LX17" s="16"/>
+      <c r="LY17" s="16"/>
+      <c r="LZ17" s="16"/>
+      <c r="MA17" s="16"/>
+      <c r="MB17" s="16"/>
+      <c r="MC17" s="16"/>
+      <c r="MD17" s="16"/>
+      <c r="ME17" s="16"/>
+      <c r="MF17" s="16"/>
+      <c r="MG17" s="16"/>
+      <c r="MH17" s="16"/>
+      <c r="MI17" s="16"/>
+      <c r="MJ17" s="16"/>
+      <c r="MK17" s="16"/>
+      <c r="ML17" s="16"/>
+      <c r="MM17" s="16"/>
+      <c r="MN17" s="16"/>
+      <c r="MO17" s="16"/>
+      <c r="MP17" s="16"/>
+      <c r="MQ17" s="16"/>
+      <c r="MR17" s="16"/>
+      <c r="MS17" s="16"/>
+      <c r="MT17" s="16"/>
+      <c r="MU17" s="16"/>
+      <c r="MV17" s="16"/>
+      <c r="MW17" s="16"/>
+      <c r="MX17" s="16"/>
+      <c r="MY17" s="16"/>
+      <c r="MZ17" s="16"/>
+      <c r="NA17" s="16"/>
+      <c r="NB17" s="16"/>
+      <c r="NC17" s="16"/>
+      <c r="ND17" s="16"/>
+      <c r="NE17" s="16"/>
+      <c r="NF17" s="16"/>
+      <c r="NG17" s="16"/>
+      <c r="NH17" s="16"/>
+      <c r="NI17" s="16"/>
+      <c r="NJ17" s="16"/>
+      <c r="NK17" s="16"/>
+      <c r="NL17" s="16"/>
+      <c r="NM17" s="16"/>
+      <c r="NN17" s="16"/>
+      <c r="NO17" s="16"/>
+      <c r="NP17" s="16"/>
+      <c r="NQ17" s="16"/>
+      <c r="NR17" s="16"/>
+      <c r="NS17" s="16"/>
+      <c r="NT17" s="16"/>
+      <c r="NU17" s="16"/>
+      <c r="NV17" s="16"/>
+      <c r="NW17" s="16"/>
+      <c r="NX17" s="16"/>
+      <c r="NY17" s="16"/>
+      <c r="NZ17" s="16"/>
+      <c r="OA17" s="16"/>
+      <c r="OB17" s="16"/>
+      <c r="OC17" s="16"/>
+      <c r="OD17" s="16"/>
+      <c r="OE17" s="16"/>
+      <c r="OF17" s="16"/>
+      <c r="OG17" s="16"/>
+      <c r="OH17" s="16"/>
+      <c r="OI17" s="16"/>
+      <c r="OJ17" s="16"/>
+      <c r="OK17" s="16"/>
+      <c r="OL17" s="16"/>
+      <c r="OM17" s="16"/>
+      <c r="ON17" s="16"/>
+      <c r="OO17" s="16"/>
+      <c r="OP17" s="16"/>
+      <c r="OQ17" s="16"/>
+      <c r="OR17" s="16"/>
+      <c r="OS17" s="16"/>
+      <c r="OT17" s="16"/>
+      <c r="OU17" s="16"/>
+      <c r="OV17" s="16"/>
+      <c r="OW17" s="16"/>
+      <c r="OX17" s="16"/>
+      <c r="OY17" s="16"/>
+      <c r="OZ17" s="16"/>
+      <c r="PA17" s="16"/>
+      <c r="PB17" s="16"/>
+      <c r="PC17" s="16"/>
+      <c r="PD17" s="16"/>
+      <c r="PE17" s="16"/>
+      <c r="PF17" s="16"/>
+      <c r="PG17" s="16"/>
+      <c r="PH17" s="16"/>
+      <c r="PI17" s="16"/>
+      <c r="PJ17" s="16"/>
+      <c r="PK17" s="16"/>
+      <c r="PL17" s="16"/>
+      <c r="PM17" s="16"/>
+      <c r="PN17" s="16"/>
+      <c r="PO17" s="16"/>
+      <c r="PP17" s="16"/>
+      <c r="PQ17" s="16"/>
+      <c r="PR17" s="16"/>
+      <c r="PS17" s="16"/>
+      <c r="PT17" s="16"/>
+      <c r="PU17" s="16"/>
+      <c r="PV17" s="16"/>
+      <c r="PW17" s="16"/>
+      <c r="PX17" s="16"/>
+      <c r="PY17" s="16"/>
+      <c r="PZ17" s="16"/>
+      <c r="QA17" s="16"/>
+      <c r="QB17" s="16"/>
+      <c r="QC17" s="16"/>
+      <c r="QD17" s="16"/>
+      <c r="QE17" s="16"/>
+      <c r="QF17" s="16"/>
+      <c r="QG17" s="16"/>
+      <c r="QH17" s="16"/>
+      <c r="QI17" s="16"/>
+      <c r="QJ17" s="16"/>
+      <c r="QK17" s="16"/>
+      <c r="QL17" s="16"/>
+      <c r="QM17" s="16"/>
+      <c r="QN17" s="16"/>
+      <c r="QO17" s="16"/>
+      <c r="QP17" s="16"/>
+      <c r="QQ17" s="16"/>
+      <c r="QR17" s="16"/>
+      <c r="QS17" s="16"/>
+      <c r="QT17" s="16"/>
+      <c r="QU17" s="16"/>
+      <c r="QV17" s="16"/>
+      <c r="QW17" s="16"/>
+      <c r="QX17" s="16"/>
+      <c r="QY17" s="16"/>
+      <c r="QZ17" s="16"/>
+      <c r="RA17" s="16"/>
+      <c r="RB17" s="16"/>
+      <c r="RC17" s="16"/>
+      <c r="RD17" s="16"/>
+      <c r="RE17" s="16"/>
+      <c r="RF17" s="16"/>
+      <c r="RG17" s="16"/>
+      <c r="RH17" s="16"/>
+      <c r="RI17" s="16"/>
+      <c r="RJ17" s="16"/>
+      <c r="RK17" s="16"/>
+      <c r="RL17" s="16"/>
+      <c r="RM17" s="16"/>
+      <c r="RN17" s="16"/>
+      <c r="RO17" s="16"/>
+      <c r="RP17" s="16"/>
+      <c r="RQ17" s="16"/>
+      <c r="RR17" s="16"/>
+      <c r="RS17" s="16"/>
+      <c r="RT17" s="16"/>
+      <c r="RU17" s="16"/>
+      <c r="RV17" s="16"/>
+      <c r="RW17" s="16"/>
+      <c r="RX17" s="16"/>
+      <c r="RY17" s="16"/>
+      <c r="RZ17" s="16"/>
+      <c r="SA17" s="16"/>
+      <c r="SB17" s="16"/>
+      <c r="SC17" s="16"/>
+      <c r="SD17" s="16"/>
+      <c r="SE17" s="16"/>
+      <c r="SF17" s="16"/>
+      <c r="SG17" s="16"/>
+      <c r="SH17" s="16"/>
+      <c r="SI17" s="16"/>
+      <c r="SJ17" s="16"/>
+      <c r="SK17" s="16"/>
+      <c r="SL17" s="16"/>
+      <c r="SM17" s="16"/>
+      <c r="SN17" s="16"/>
+      <c r="SO17" s="16"/>
+      <c r="SP17" s="16"/>
+      <c r="SQ17" s="16"/>
+      <c r="SR17" s="16"/>
+      <c r="SS17" s="16"/>
+      <c r="ST17" s="16"/>
+      <c r="SU17" s="16"/>
+      <c r="SV17" s="16"/>
+      <c r="SW17" s="16"/>
+      <c r="SX17" s="16"/>
+      <c r="SY17" s="16"/>
+      <c r="SZ17" s="16"/>
+      <c r="TA17" s="16"/>
+      <c r="TB17" s="16"/>
+      <c r="TC17" s="16"/>
+      <c r="TD17" s="16"/>
+      <c r="TE17" s="16"/>
+      <c r="TF17" s="16"/>
+      <c r="TG17" s="16"/>
+      <c r="TH17" s="16"/>
+      <c r="TI17" s="16"/>
+      <c r="TJ17" s="16"/>
+      <c r="TK17" s="16"/>
+      <c r="TL17" s="16"/>
+      <c r="TM17" s="16"/>
+      <c r="TN17" s="16"/>
+      <c r="TO17" s="16"/>
+      <c r="TP17" s="16"/>
+      <c r="TQ17" s="16"/>
+      <c r="TR17" s="16"/>
+      <c r="TS17" s="16"/>
+      <c r="TT17" s="16"/>
+      <c r="TU17" s="16"/>
+      <c r="TV17" s="16"/>
+      <c r="TW17" s="16"/>
+      <c r="TX17" s="16"/>
+      <c r="TY17" s="16"/>
+      <c r="TZ17" s="16"/>
+      <c r="UA17" s="16"/>
+      <c r="UB17" s="16"/>
+      <c r="UC17" s="16"/>
+      <c r="UD17" s="16"/>
+      <c r="UE17" s="16"/>
+      <c r="UF17" s="16"/>
+      <c r="UG17" s="16"/>
+      <c r="UH17" s="16"/>
+      <c r="UI17" s="16"/>
+      <c r="UJ17" s="16"/>
+      <c r="UK17" s="16"/>
+      <c r="UL17" s="16"/>
+      <c r="UM17" s="16"/>
+      <c r="UN17" s="16"/>
+      <c r="UO17" s="16"/>
+      <c r="UP17" s="16"/>
+      <c r="UQ17" s="16"/>
+      <c r="UR17" s="16"/>
+      <c r="US17" s="16"/>
+      <c r="UT17" s="16"/>
+      <c r="UU17" s="16"/>
+      <c r="UV17" s="16"/>
+      <c r="UW17" s="16"/>
+      <c r="UX17" s="16"/>
+      <c r="UY17" s="16"/>
+      <c r="UZ17" s="16"/>
+      <c r="VA17" s="16"/>
+      <c r="VB17" s="16"/>
+      <c r="VC17" s="16"/>
+      <c r="VD17" s="16"/>
+      <c r="VE17" s="16"/>
+      <c r="VF17" s="16"/>
+      <c r="VG17" s="16"/>
+      <c r="VH17" s="16"/>
+      <c r="VI17" s="16"/>
+      <c r="VJ17" s="16"/>
+      <c r="VK17" s="16"/>
+      <c r="VL17" s="16"/>
+      <c r="VM17" s="16"/>
+      <c r="VN17" s="16"/>
+      <c r="VO17" s="16"/>
+      <c r="VP17" s="16"/>
+      <c r="VQ17" s="16"/>
+      <c r="VR17" s="16"/>
+      <c r="VS17" s="16"/>
+      <c r="VT17" s="16"/>
+      <c r="VU17" s="16"/>
+      <c r="VV17" s="16"/>
+      <c r="VW17" s="16"/>
+      <c r="VX17" s="16"/>
+      <c r="VY17" s="16"/>
+      <c r="VZ17" s="16"/>
+      <c r="WA17" s="16"/>
+      <c r="WB17" s="16"/>
+      <c r="WC17" s="16"/>
+      <c r="WD17" s="16"/>
+      <c r="WE17" s="16"/>
+      <c r="WF17" s="16"/>
+      <c r="WG17" s="16"/>
+      <c r="WH17" s="16"/>
+      <c r="WI17" s="16"/>
+      <c r="WJ17" s="16"/>
+      <c r="WK17" s="16"/>
+      <c r="WL17" s="16"/>
+      <c r="WM17" s="16"/>
+      <c r="WN17" s="16"/>
+      <c r="WO17" s="16"/>
+      <c r="WP17" s="16"/>
+      <c r="WQ17" s="16"/>
+      <c r="WR17" s="16"/>
+      <c r="WS17" s="16"/>
+      <c r="WT17" s="16"/>
+      <c r="WU17" s="16"/>
+      <c r="WV17" s="16"/>
+      <c r="WW17" s="16"/>
+      <c r="WX17" s="16"/>
+      <c r="WY17" s="16"/>
+      <c r="WZ17" s="16"/>
+      <c r="XA17" s="16"/>
+      <c r="XB17" s="16"/>
+      <c r="XC17" s="16"/>
+      <c r="XD17" s="16"/>
+      <c r="XE17" s="16"/>
+      <c r="XF17" s="16"/>
+      <c r="XG17" s="16"/>
+      <c r="XH17" s="16"/>
+      <c r="XI17" s="16"/>
+      <c r="XJ17" s="16"/>
+      <c r="XK17" s="16"/>
+      <c r="XL17" s="16"/>
+      <c r="XM17" s="16"/>
+      <c r="XN17" s="16"/>
+      <c r="XO17" s="16"/>
+      <c r="XP17" s="16"/>
+      <c r="XQ17" s="16"/>
+      <c r="XR17" s="16"/>
+      <c r="XS17" s="16"/>
+      <c r="XT17" s="16"/>
+      <c r="XU17" s="16"/>
+      <c r="XV17" s="16"/>
+      <c r="XW17" s="16"/>
+      <c r="XX17" s="16"/>
+      <c r="XY17" s="16"/>
+      <c r="XZ17" s="16"/>
+      <c r="YA17" s="16"/>
+      <c r="YB17" s="16"/>
+      <c r="YC17" s="16"/>
+      <c r="YD17" s="16"/>
+      <c r="YE17" s="16"/>
+      <c r="YF17" s="16"/>
+      <c r="YG17" s="16"/>
+      <c r="YH17" s="16"/>
+      <c r="YI17" s="16"/>
+      <c r="YJ17" s="16"/>
+      <c r="YK17" s="16"/>
+      <c r="YL17" s="16"/>
+      <c r="YM17" s="16"/>
+      <c r="YN17" s="16"/>
+      <c r="YO17" s="16"/>
+      <c r="YP17" s="16"/>
+      <c r="YQ17" s="16"/>
+      <c r="YR17" s="16"/>
+      <c r="YS17" s="16"/>
+      <c r="YT17" s="16"/>
+      <c r="YU17" s="16"/>
+      <c r="YV17" s="16"/>
+      <c r="YW17" s="16"/>
+      <c r="YX17" s="16"/>
+      <c r="YY17" s="16"/>
+      <c r="YZ17" s="16"/>
+      <c r="ZA17" s="16"/>
+      <c r="ZB17" s="16"/>
+      <c r="ZC17" s="16"/>
+      <c r="ZD17" s="16"/>
+      <c r="ZE17" s="16"/>
+      <c r="ZF17" s="16"/>
+      <c r="ZG17" s="16"/>
+      <c r="ZH17" s="16"/>
+      <c r="ZI17" s="16"/>
+      <c r="ZJ17" s="16"/>
+      <c r="ZK17" s="16"/>
+      <c r="ZL17" s="16"/>
+      <c r="ZM17" s="16"/>
+      <c r="ZN17" s="16"/>
+      <c r="ZO17" s="16"/>
+      <c r="ZP17" s="16"/>
+      <c r="ZQ17" s="16"/>
+      <c r="ZR17" s="16"/>
+      <c r="ZS17" s="16"/>
+      <c r="ZT17" s="16"/>
+      <c r="ZU17" s="16"/>
+      <c r="ZV17" s="16"/>
+      <c r="ZW17" s="16"/>
+      <c r="ZX17" s="16"/>
+      <c r="ZY17" s="16"/>
+      <c r="ZZ17" s="16"/>
+      <c r="AAA17" s="16"/>
+      <c r="AAB17" s="16"/>
+      <c r="AAC17" s="16"/>
+      <c r="AAD17" s="16"/>
+      <c r="AAE17" s="16"/>
+      <c r="AAF17" s="16"/>
+      <c r="AAG17" s="16"/>
+      <c r="AAH17" s="16"/>
+      <c r="AAI17" s="16"/>
+      <c r="AAJ17" s="16"/>
+      <c r="AAK17" s="16"/>
+      <c r="AAL17" s="16"/>
+      <c r="AAM17" s="16"/>
+      <c r="AAN17" s="16"/>
+      <c r="AAO17" s="16"/>
+      <c r="AAP17" s="16"/>
+      <c r="AAQ17" s="16"/>
+      <c r="AAR17" s="16"/>
+      <c r="AAS17" s="16"/>
+      <c r="AAT17" s="16"/>
+      <c r="AAU17" s="16"/>
+      <c r="AAV17" s="16"/>
+      <c r="AAW17" s="16"/>
+      <c r="AAX17" s="16"/>
+      <c r="AAY17" s="16"/>
+      <c r="AAZ17" s="16"/>
+      <c r="ABA17" s="16"/>
+      <c r="ABB17" s="16"/>
+      <c r="ABC17" s="16"/>
+      <c r="ABD17" s="16"/>
+      <c r="ABE17" s="16"/>
+      <c r="ABF17" s="16"/>
+      <c r="ABG17" s="16"/>
+      <c r="ABH17" s="16"/>
+      <c r="ABI17" s="16"/>
+      <c r="ABJ17" s="16"/>
+      <c r="ABK17" s="16"/>
+      <c r="ABL17" s="16"/>
+      <c r="ABM17" s="16"/>
+      <c r="ABN17" s="16"/>
+      <c r="ABO17" s="16"/>
+      <c r="ABP17" s="16"/>
+      <c r="ABQ17" s="16"/>
+      <c r="ABR17" s="16"/>
+      <c r="ABS17" s="16"/>
+      <c r="ABT17" s="16"/>
+      <c r="ABU17" s="16"/>
+      <c r="ABV17" s="16"/>
+      <c r="ABW17" s="16"/>
+      <c r="ABX17" s="16"/>
+      <c r="ABY17" s="16"/>
+      <c r="ABZ17" s="16"/>
+      <c r="ACA17" s="16"/>
+      <c r="ACB17" s="16"/>
+      <c r="ACC17" s="16"/>
+      <c r="ACD17" s="16"/>
+      <c r="ACE17" s="16"/>
+      <c r="ACF17" s="16"/>
+      <c r="ACG17" s="16"/>
+      <c r="ACH17" s="16"/>
+      <c r="ACI17" s="16"/>
+      <c r="ACJ17" s="16"/>
+      <c r="ACK17" s="16"/>
+      <c r="ACL17" s="16"/>
+      <c r="ACM17" s="16"/>
+      <c r="ACN17" s="16"/>
+      <c r="ACO17" s="16"/>
+      <c r="ACP17" s="16"/>
+      <c r="ACQ17" s="16"/>
+      <c r="ACR17" s="16"/>
+      <c r="ACS17" s="16"/>
+      <c r="ACT17" s="16"/>
+      <c r="ACU17" s="16"/>
+      <c r="ACV17" s="16"/>
+      <c r="ACW17" s="16"/>
+      <c r="ACX17" s="16"/>
+      <c r="ACY17" s="16"/>
+      <c r="ACZ17" s="16"/>
+      <c r="ADA17" s="16"/>
+      <c r="ADB17" s="16"/>
+      <c r="ADC17" s="16"/>
+      <c r="ADD17" s="16"/>
+      <c r="ADE17" s="16"/>
+      <c r="ADF17" s="16"/>
+      <c r="ADG17" s="16"/>
+      <c r="ADH17" s="16"/>
+      <c r="ADI17" s="16"/>
+      <c r="ADJ17" s="16"/>
+      <c r="ADK17" s="16"/>
+      <c r="ADL17" s="16"/>
+      <c r="ADM17" s="16"/>
+      <c r="ADN17" s="16"/>
+      <c r="ADO17" s="16"/>
+      <c r="ADP17" s="16"/>
+      <c r="ADQ17" s="16"/>
+      <c r="ADR17" s="16"/>
+      <c r="ADS17" s="16"/>
+      <c r="ADT17" s="16"/>
+      <c r="ADU17" s="16"/>
+      <c r="ADV17" s="16"/>
+      <c r="ADW17" s="16"/>
+      <c r="ADX17" s="16"/>
+      <c r="ADY17" s="16"/>
+      <c r="ADZ17" s="16"/>
+      <c r="AEA17" s="16"/>
+      <c r="AEB17" s="16"/>
+      <c r="AEC17" s="16"/>
+      <c r="AED17" s="16"/>
+      <c r="AEE17" s="16"/>
+      <c r="AEF17" s="16"/>
+      <c r="AEG17" s="16"/>
+      <c r="AEH17" s="16"/>
+      <c r="AEI17" s="16"/>
+      <c r="AEJ17" s="16"/>
+      <c r="AEK17" s="16"/>
+      <c r="AEL17" s="16"/>
+      <c r="AEM17" s="16"/>
+      <c r="AEN17" s="16"/>
+      <c r="AEO17" s="16"/>
+      <c r="AEP17" s="16"/>
+      <c r="AEQ17" s="16"/>
+      <c r="AER17" s="16"/>
+      <c r="AES17" s="16"/>
+      <c r="AET17" s="16"/>
+      <c r="AEU17" s="16"/>
+      <c r="AEV17" s="16"/>
+      <c r="AEW17" s="16"/>
+      <c r="AEX17" s="16"/>
+      <c r="AEY17" s="16"/>
+      <c r="AEZ17" s="16"/>
+      <c r="AFA17" s="16"/>
+      <c r="AFB17" s="16"/>
+      <c r="AFC17" s="16"/>
+      <c r="AFD17" s="16"/>
+      <c r="AFE17" s="16"/>
+      <c r="AFF17" s="16"/>
+      <c r="AFG17" s="16"/>
+      <c r="AFH17" s="16"/>
+      <c r="AFI17" s="16"/>
+      <c r="AFJ17" s="16"/>
+      <c r="AFK17" s="16"/>
+      <c r="AFL17" s="16"/>
+      <c r="AFM17" s="16"/>
+      <c r="AFN17" s="16"/>
+      <c r="AFO17" s="16"/>
+      <c r="AFP17" s="16"/>
+      <c r="AFQ17" s="16"/>
+      <c r="AFR17" s="16"/>
+      <c r="AFS17" s="16"/>
+      <c r="AFT17" s="16"/>
+      <c r="AFU17" s="16"/>
+      <c r="AFV17" s="16"/>
+      <c r="AFW17" s="16"/>
+      <c r="AFX17" s="16"/>
+      <c r="AFY17" s="16"/>
+      <c r="AFZ17" s="16"/>
+      <c r="AGA17" s="16"/>
+      <c r="AGB17" s="16"/>
+      <c r="AGC17" s="16"/>
+      <c r="AGD17" s="16"/>
+      <c r="AGE17" s="16"/>
+      <c r="AGF17" s="16"/>
+      <c r="AGG17" s="16"/>
+      <c r="AGH17" s="16"/>
+      <c r="AGI17" s="16"/>
+      <c r="AGJ17" s="16"/>
+      <c r="AGK17" s="16"/>
+      <c r="AGL17" s="16"/>
+      <c r="AGM17" s="16"/>
+      <c r="AGN17" s="16"/>
+      <c r="AGO17" s="16"/>
+      <c r="AGP17" s="16"/>
+      <c r="AGQ17" s="16"/>
+      <c r="AGR17" s="16"/>
+      <c r="AGS17" s="16"/>
+      <c r="AGT17" s="16"/>
+      <c r="AGU17" s="16"/>
+      <c r="AGV17" s="16"/>
+      <c r="AGW17" s="16"/>
+      <c r="AGX17" s="16"/>
+      <c r="AGY17" s="16"/>
+      <c r="AGZ17" s="16"/>
+      <c r="AHA17" s="16"/>
+      <c r="AHB17" s="16"/>
+      <c r="AHC17" s="16"/>
+      <c r="AHD17" s="16"/>
+      <c r="AHE17" s="16"/>
+      <c r="AHF17" s="16"/>
+      <c r="AHG17" s="16"/>
+      <c r="AHH17" s="16"/>
+      <c r="AHI17" s="16"/>
+      <c r="AHJ17" s="16"/>
+      <c r="AHK17" s="16"/>
+      <c r="AHL17" s="16"/>
+      <c r="AHM17" s="16"/>
+      <c r="AHN17" s="16"/>
+      <c r="AHO17" s="16"/>
+      <c r="AHP17" s="16"/>
+      <c r="AHQ17" s="16"/>
+      <c r="AHR17" s="16"/>
+      <c r="AHS17" s="16"/>
+      <c r="AHT17" s="16"/>
+      <c r="AHU17" s="16"/>
+      <c r="AHV17" s="16"/>
+      <c r="AHW17" s="16"/>
+      <c r="AHX17" s="16"/>
+      <c r="AHY17" s="16"/>
+      <c r="AHZ17" s="16"/>
+      <c r="AIA17" s="16"/>
+      <c r="AIB17" s="16"/>
+      <c r="AIC17" s="16"/>
+      <c r="AID17" s="16"/>
+      <c r="AIE17" s="16"/>
+      <c r="AIF17" s="16"/>
+      <c r="AIG17" s="16"/>
+      <c r="AIH17" s="16"/>
+      <c r="AII17" s="16"/>
+      <c r="AIJ17" s="16"/>
+      <c r="AIK17" s="16"/>
+      <c r="AIL17" s="16"/>
+      <c r="AIM17" s="16"/>
+      <c r="AIN17" s="16"/>
+      <c r="AIO17" s="16"/>
+      <c r="AIP17" s="16"/>
+      <c r="AIQ17" s="16"/>
+      <c r="AIR17" s="16"/>
+      <c r="AIS17" s="16"/>
+      <c r="AIT17" s="16"/>
+      <c r="AIU17" s="16"/>
+      <c r="AIV17" s="16"/>
+      <c r="AIW17" s="16"/>
+      <c r="AIX17" s="16"/>
+      <c r="AIY17" s="16"/>
+      <c r="AIZ17" s="16"/>
+      <c r="AJA17" s="16"/>
+      <c r="AJB17" s="16"/>
+      <c r="AJC17" s="16"/>
+      <c r="AJD17" s="16"/>
+      <c r="AJE17" s="16"/>
+      <c r="AJF17" s="16"/>
+      <c r="AJG17" s="16"/>
+      <c r="AJH17" s="16"/>
+      <c r="AJI17" s="16"/>
+      <c r="AJJ17" s="16"/>
+      <c r="AJK17" s="16"/>
+      <c r="AJL17" s="16"/>
+      <c r="AJM17" s="16"/>
+      <c r="AJN17" s="16"/>
+      <c r="AJO17" s="16"/>
+      <c r="AJP17" s="16"/>
+      <c r="AJQ17" s="16"/>
+      <c r="AJR17" s="16"/>
+      <c r="AJS17" s="16"/>
+      <c r="AJT17" s="16"/>
+      <c r="AJU17" s="16"/>
+      <c r="AJV17" s="16"/>
+      <c r="AJW17" s="16"/>
+      <c r="AJX17" s="16"/>
+      <c r="AJY17" s="16"/>
+      <c r="AJZ17" s="16"/>
+      <c r="AKA17" s="16"/>
+      <c r="AKB17" s="16"/>
+      <c r="AKC17" s="16"/>
+      <c r="AKD17" s="16"/>
+      <c r="AKE17" s="16"/>
+      <c r="AKF17" s="16"/>
+      <c r="AKG17" s="16"/>
+      <c r="AKH17" s="16"/>
+      <c r="AKI17" s="16"/>
+      <c r="AKJ17" s="16"/>
+      <c r="AKK17" s="16"/>
+      <c r="AKL17" s="16"/>
+      <c r="AKM17" s="16"/>
+      <c r="AKN17" s="16"/>
+      <c r="AKO17" s="16"/>
+      <c r="AKP17" s="16"/>
+      <c r="AKQ17" s="16"/>
+      <c r="AKR17" s="16"/>
+      <c r="AKS17" s="16"/>
+      <c r="AKT17" s="16"/>
+      <c r="AKU17" s="16"/>
+      <c r="AKV17" s="16"/>
+      <c r="AKW17" s="16"/>
+      <c r="AKX17" s="16"/>
+      <c r="AKY17" s="16"/>
+      <c r="AKZ17" s="16"/>
+      <c r="ALA17" s="16"/>
+      <c r="ALB17" s="16"/>
+      <c r="ALC17" s="16"/>
+      <c r="ALD17" s="16"/>
+      <c r="ALE17" s="16"/>
+      <c r="ALF17" s="16"/>
+      <c r="ALG17" s="16"/>
+      <c r="ALH17" s="16"/>
+      <c r="ALI17" s="16"/>
+      <c r="ALJ17" s="16"/>
+      <c r="ALK17" s="16"/>
+      <c r="ALL17" s="16"/>
+      <c r="ALM17" s="16"/>
+      <c r="ALN17" s="16"/>
+      <c r="ALO17" s="16"/>
+      <c r="ALP17" s="16"/>
+      <c r="ALQ17" s="16"/>
+      <c r="ALR17" s="16"/>
+      <c r="ALS17" s="16"/>
+      <c r="ALT17" s="16"/>
+      <c r="ALU17" s="16"/>
+      <c r="ALV17" s="16"/>
+      <c r="ALW17" s="16"/>
+      <c r="ALX17" s="16"/>
+      <c r="ALY17" s="16"/>
+      <c r="ALZ17" s="16"/>
+      <c r="AMA17" s="16"/>
+      <c r="AMB17" s="16"/>
+      <c r="AMC17" s="16"/>
+      <c r="AMD17" s="16"/>
+      <c r="AME17" s="16"/>
+      <c r="AMF17" s="16"/>
+      <c r="AMG17" s="16"/>
+      <c r="AMH17" s="16"/>
+      <c r="AMI17" s="16"/>
+      <c r="AMJ17" s="16"/>
     </row>
     <row r="18" customFormat="false" ht="214.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="16" t="s">
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="15" t="s">
         <v>209</v>
       </c>
-      <c r="E18" s="16" t="s">
+      <c r="E18" s="15" t="s">
         <v>210</v>
       </c>
-      <c r="F18" s="16" t="s">
+      <c r="F18" s="15" t="s">
         <v>211</v>
       </c>
-      <c r="G18" s="16" t="s">
+      <c r="G18" s="15" t="s">
         <v>212</v>
       </c>
-      <c r="H18" s="16" t="s">
+      <c r="H18" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="I18" s="19"/>
-      <c r="J18" s="19"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="16"/>
     </row>
     <row r="19" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="15"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15" t="s">
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="D19" s="16" t="s">
+      <c r="D19" s="15" t="s">
         <v>214</v>
       </c>
-      <c r="E19" s="16" t="s">
+      <c r="E19" s="15" t="s">
         <v>215</v>
       </c>
-      <c r="F19" s="16" t="s">
+      <c r="F19" s="15" t="s">
         <v>216</v>
       </c>
-      <c r="G19" s="16" t="s">
+      <c r="G19" s="15" t="s">
         <v>217</v>
       </c>
-      <c r="H19" s="16" t="s">
+      <c r="H19" s="15" t="s">
         <v>218</v>
       </c>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="16"/>
     </row>
     <row r="20" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="15"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15" t="s">
+      <c r="A20" s="14"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="E20" s="16" t="s">
+      <c r="E20" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="F20" s="16" t="s">
+      <c r="F20" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="G20" s="16" t="s">
+      <c r="G20" s="15" t="s">
         <v>222</v>
       </c>
-      <c r="H20" s="16" t="s">
+      <c r="H20" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="I20" s="16"/>
-      <c r="J20" s="16"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
     </row>
     <row r="21" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="15"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="16" t="s">
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="15" t="s">
         <v>224</v>
       </c>
-      <c r="E21" s="16" t="s">
+      <c r="E21" s="15" t="s">
         <v>225</v>
       </c>
-      <c r="F21" s="16" t="s">
+      <c r="F21" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="G21" s="16" t="s">
+      <c r="G21" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="H21" s="16" t="s">
+      <c r="H21" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="I21" s="16"/>
-      <c r="J21" s="16"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
     </row>
     <row r="22" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="15" t="s">
+      <c r="A22" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="16" t="s">
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="15" t="s">
         <v>228</v>
       </c>
-      <c r="E22" s="16" t="s">
+      <c r="E22" s="15" t="s">
         <v>229</v>
       </c>
-      <c r="F22" s="16" t="s">
+      <c r="F22" s="15" t="s">
         <v>230</v>
       </c>
-      <c r="G22" s="16" t="s">
+      <c r="G22" s="15" t="s">
         <v>231</v>
       </c>
-      <c r="H22" s="16" t="s">
+      <c r="H22" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="I22" s="16"/>
-      <c r="J22" s="16"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
     </row>
     <row r="23" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="16" t="s">
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="15" t="s">
         <v>232</v>
       </c>
-      <c r="E23" s="16" t="s">
+      <c r="E23" s="15" t="s">
         <v>233</v>
       </c>
-      <c r="F23" s="16" t="s">
+      <c r="F23" s="15" t="s">
         <v>234</v>
       </c>
-      <c r="G23" s="16" t="s">
+      <c r="G23" s="15" t="s">
         <v>235</v>
       </c>
-      <c r="H23" s="16" t="s">
+      <c r="H23" s="15" t="s">
         <v>236</v>
       </c>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
     </row>
     <row r="24" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="15" t="s">
+      <c r="A24" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="B24" s="15"/>
-      <c r="C24" s="15"/>
-      <c r="D24" s="16" t="s">
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="15" t="s">
         <v>237</v>
       </c>
-      <c r="E24" s="16" t="s">
+      <c r="E24" s="15" t="s">
         <v>238</v>
       </c>
-      <c r="F24" s="16" t="s">
+      <c r="F24" s="15" t="s">
         <v>239</v>
       </c>
-      <c r="G24" s="16" t="s">
+      <c r="G24" s="15" t="s">
         <v>240</v>
       </c>
-      <c r="H24" s="16" t="s">
+      <c r="H24" s="15" t="s">
         <v>241</v>
       </c>
-      <c r="I24" s="16"/>
-      <c r="J24" s="16"/>
-    </row>
-    <row r="25" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="15" t="s">
+      <c r="I24" s="15"/>
+      <c r="J24" s="15"/>
+    </row>
+    <row r="25" s="18" customFormat="true" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="16" t="s">
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="15" t="s">
         <v>242</v>
       </c>
-      <c r="E25" s="16" t="s">
+      <c r="E25" s="15" t="s">
         <v>243</v>
       </c>
-      <c r="F25" s="16" t="s">
+      <c r="F25" s="15" t="s">
         <v>244</v>
       </c>
-      <c r="G25" s="16" t="s">
+      <c r="G25" s="15" t="s">
         <v>245</v>
       </c>
-      <c r="H25" s="16" t="s">
+      <c r="H25" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
-    </row>
-    <row r="26" customFormat="false" ht="326.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="15" t="s">
+      <c r="I25" s="15"/>
+      <c r="J25" s="15"/>
+      <c r="K25" s="11"/>
+      <c r="L25" s="11"/>
+      <c r="M25" s="11"/>
+      <c r="N25" s="11"/>
+      <c r="O25" s="11"/>
+      <c r="P25" s="11"/>
+      <c r="Q25" s="11"/>
+      <c r="R25" s="11"/>
+      <c r="S25" s="11"/>
+      <c r="T25" s="11"/>
+      <c r="U25" s="11"/>
+      <c r="V25" s="11"/>
+      <c r="W25" s="11"/>
+      <c r="X25" s="11"/>
+      <c r="Y25" s="11"/>
+      <c r="Z25" s="11"/>
+      <c r="AA25" s="11"/>
+      <c r="AB25" s="11"/>
+      <c r="AC25" s="11"/>
+      <c r="AD25" s="11"/>
+      <c r="AE25" s="11"/>
+      <c r="AF25" s="11"/>
+      <c r="AG25" s="11"/>
+      <c r="AH25" s="11"/>
+      <c r="AI25" s="11"/>
+      <c r="AJ25" s="11"/>
+      <c r="AK25" s="11"/>
+      <c r="AL25" s="11"/>
+      <c r="AM25" s="11"/>
+      <c r="AN25" s="11"/>
+      <c r="AO25" s="11"/>
+      <c r="AP25" s="11"/>
+      <c r="AQ25" s="11"/>
+      <c r="AR25" s="11"/>
+      <c r="AS25" s="11"/>
+      <c r="AT25" s="11"/>
+      <c r="AU25" s="11"/>
+      <c r="AV25" s="11"/>
+      <c r="AW25" s="11"/>
+      <c r="AX25" s="11"/>
+      <c r="AY25" s="11"/>
+      <c r="AZ25" s="11"/>
+      <c r="BA25" s="11"/>
+      <c r="BB25" s="11"/>
+      <c r="BC25" s="11"/>
+      <c r="BD25" s="11"/>
+      <c r="BE25" s="11"/>
+      <c r="BF25" s="11"/>
+      <c r="BG25" s="11"/>
+      <c r="BH25" s="11"/>
+      <c r="BI25" s="11"/>
+      <c r="BJ25" s="11"/>
+      <c r="BK25" s="11"/>
+      <c r="BL25" s="11"/>
+      <c r="BM25" s="11"/>
+      <c r="BN25" s="11"/>
+      <c r="BO25" s="11"/>
+      <c r="BP25" s="11"/>
+      <c r="BQ25" s="11"/>
+      <c r="BR25" s="11"/>
+      <c r="BS25" s="11"/>
+      <c r="BT25" s="11"/>
+      <c r="BU25" s="11"/>
+      <c r="BV25" s="11"/>
+      <c r="BW25" s="11"/>
+      <c r="BX25" s="11"/>
+      <c r="BY25" s="11"/>
+      <c r="BZ25" s="11"/>
+      <c r="CA25" s="11"/>
+      <c r="CB25" s="11"/>
+      <c r="CC25" s="11"/>
+      <c r="CD25" s="11"/>
+      <c r="CE25" s="11"/>
+      <c r="CF25" s="11"/>
+      <c r="CG25" s="11"/>
+      <c r="CH25" s="11"/>
+      <c r="CI25" s="11"/>
+      <c r="CJ25" s="11"/>
+      <c r="CK25" s="11"/>
+      <c r="CL25" s="11"/>
+      <c r="CM25" s="11"/>
+      <c r="CN25" s="11"/>
+      <c r="CO25" s="11"/>
+      <c r="CP25" s="11"/>
+      <c r="CQ25" s="11"/>
+      <c r="CR25" s="11"/>
+      <c r="CS25" s="11"/>
+      <c r="CT25" s="11"/>
+      <c r="CU25" s="11"/>
+      <c r="CV25" s="11"/>
+      <c r="CW25" s="11"/>
+      <c r="CX25" s="11"/>
+      <c r="CY25" s="11"/>
+      <c r="CZ25" s="11"/>
+      <c r="DA25" s="11"/>
+      <c r="DB25" s="11"/>
+      <c r="DC25" s="11"/>
+      <c r="DD25" s="11"/>
+      <c r="DE25" s="11"/>
+      <c r="DF25" s="11"/>
+      <c r="DG25" s="11"/>
+      <c r="DH25" s="11"/>
+      <c r="DI25" s="11"/>
+      <c r="DJ25" s="11"/>
+      <c r="DK25" s="11"/>
+      <c r="DL25" s="11"/>
+      <c r="DM25" s="11"/>
+      <c r="DN25" s="11"/>
+      <c r="DO25" s="11"/>
+      <c r="DP25" s="11"/>
+      <c r="DQ25" s="11"/>
+      <c r="DR25" s="11"/>
+      <c r="DS25" s="11"/>
+      <c r="DT25" s="11"/>
+      <c r="DU25" s="11"/>
+      <c r="DV25" s="11"/>
+      <c r="DW25" s="11"/>
+      <c r="DX25" s="11"/>
+      <c r="DY25" s="11"/>
+      <c r="DZ25" s="11"/>
+      <c r="EA25" s="11"/>
+      <c r="EB25" s="11"/>
+      <c r="EC25" s="11"/>
+      <c r="ED25" s="11"/>
+      <c r="EE25" s="11"/>
+      <c r="EF25" s="11"/>
+      <c r="EG25" s="11"/>
+      <c r="EH25" s="11"/>
+      <c r="EI25" s="11"/>
+      <c r="EJ25" s="11"/>
+      <c r="EK25" s="11"/>
+      <c r="EL25" s="11"/>
+      <c r="EM25" s="11"/>
+      <c r="EN25" s="11"/>
+      <c r="EO25" s="11"/>
+      <c r="EP25" s="11"/>
+      <c r="EQ25" s="11"/>
+      <c r="ER25" s="11"/>
+      <c r="ES25" s="11"/>
+      <c r="ET25" s="11"/>
+      <c r="EU25" s="11"/>
+      <c r="EV25" s="11"/>
+      <c r="EW25" s="11"/>
+      <c r="EX25" s="11"/>
+      <c r="EY25" s="11"/>
+      <c r="EZ25" s="11"/>
+      <c r="FA25" s="11"/>
+      <c r="FB25" s="11"/>
+      <c r="FC25" s="11"/>
+      <c r="FD25" s="11"/>
+      <c r="FE25" s="11"/>
+      <c r="FF25" s="11"/>
+      <c r="FG25" s="11"/>
+      <c r="FH25" s="11"/>
+      <c r="FI25" s="11"/>
+      <c r="FJ25" s="11"/>
+      <c r="FK25" s="11"/>
+      <c r="FL25" s="11"/>
+      <c r="FM25" s="11"/>
+      <c r="FN25" s="11"/>
+      <c r="FO25" s="11"/>
+      <c r="FP25" s="11"/>
+      <c r="FQ25" s="11"/>
+      <c r="FR25" s="11"/>
+      <c r="FS25" s="11"/>
+      <c r="FT25" s="11"/>
+      <c r="FU25" s="11"/>
+      <c r="FV25" s="11"/>
+      <c r="FW25" s="11"/>
+      <c r="FX25" s="11"/>
+      <c r="FY25" s="11"/>
+      <c r="FZ25" s="11"/>
+      <c r="GA25" s="11"/>
+      <c r="GB25" s="11"/>
+      <c r="GC25" s="11"/>
+      <c r="GD25" s="11"/>
+      <c r="GE25" s="11"/>
+      <c r="GF25" s="11"/>
+      <c r="GG25" s="11"/>
+      <c r="GH25" s="11"/>
+      <c r="GI25" s="11"/>
+      <c r="GJ25" s="11"/>
+      <c r="GK25" s="11"/>
+      <c r="GL25" s="11"/>
+      <c r="GM25" s="11"/>
+      <c r="GN25" s="11"/>
+      <c r="GO25" s="11"/>
+      <c r="GP25" s="11"/>
+      <c r="GQ25" s="11"/>
+      <c r="GR25" s="11"/>
+      <c r="GS25" s="11"/>
+      <c r="GT25" s="11"/>
+      <c r="GU25" s="11"/>
+      <c r="GV25" s="11"/>
+      <c r="GW25" s="11"/>
+      <c r="GX25" s="11"/>
+      <c r="GY25" s="11"/>
+      <c r="GZ25" s="11"/>
+      <c r="HA25" s="11"/>
+      <c r="HB25" s="11"/>
+      <c r="HC25" s="11"/>
+      <c r="HD25" s="11"/>
+      <c r="HE25" s="11"/>
+      <c r="HF25" s="11"/>
+      <c r="HG25" s="11"/>
+      <c r="HH25" s="11"/>
+      <c r="HI25" s="11"/>
+      <c r="HJ25" s="11"/>
+      <c r="HK25" s="11"/>
+      <c r="HL25" s="11"/>
+      <c r="HM25" s="11"/>
+      <c r="HN25" s="11"/>
+      <c r="HO25" s="11"/>
+      <c r="HP25" s="11"/>
+      <c r="HQ25" s="11"/>
+      <c r="HR25" s="11"/>
+      <c r="HS25" s="11"/>
+      <c r="HT25" s="11"/>
+      <c r="HU25" s="11"/>
+      <c r="HV25" s="11"/>
+      <c r="HW25" s="11"/>
+      <c r="HX25" s="11"/>
+      <c r="HY25" s="11"/>
+      <c r="HZ25" s="11"/>
+      <c r="IA25" s="11"/>
+      <c r="IB25" s="11"/>
+      <c r="IC25" s="11"/>
+      <c r="ID25" s="11"/>
+      <c r="IE25" s="11"/>
+      <c r="IF25" s="11"/>
+      <c r="IG25" s="11"/>
+      <c r="IH25" s="11"/>
+      <c r="II25" s="11"/>
+      <c r="IJ25" s="11"/>
+      <c r="IK25" s="11"/>
+      <c r="IL25" s="11"/>
+      <c r="IM25" s="11"/>
+      <c r="IN25" s="11"/>
+      <c r="IO25" s="11"/>
+      <c r="IP25" s="11"/>
+      <c r="IQ25" s="11"/>
+      <c r="IR25" s="11"/>
+      <c r="IS25" s="11"/>
+      <c r="IT25" s="11"/>
+      <c r="IU25" s="11"/>
+      <c r="IV25" s="11"/>
+      <c r="IW25" s="11"/>
+      <c r="IX25" s="11"/>
+      <c r="IY25" s="11"/>
+      <c r="IZ25" s="11"/>
+      <c r="JA25" s="11"/>
+      <c r="JB25" s="11"/>
+      <c r="JC25" s="11"/>
+      <c r="JD25" s="11"/>
+      <c r="JE25" s="11"/>
+      <c r="JF25" s="11"/>
+      <c r="JG25" s="11"/>
+      <c r="JH25" s="11"/>
+      <c r="JI25" s="11"/>
+      <c r="JJ25" s="11"/>
+      <c r="JK25" s="11"/>
+      <c r="JL25" s="11"/>
+      <c r="JM25" s="11"/>
+      <c r="JN25" s="11"/>
+      <c r="JO25" s="11"/>
+      <c r="JP25" s="11"/>
+      <c r="JQ25" s="11"/>
+      <c r="JR25" s="11"/>
+      <c r="JS25" s="11"/>
+      <c r="JT25" s="11"/>
+      <c r="JU25" s="11"/>
+      <c r="JV25" s="11"/>
+      <c r="JW25" s="11"/>
+      <c r="JX25" s="11"/>
+      <c r="JY25" s="11"/>
+      <c r="JZ25" s="11"/>
+      <c r="KA25" s="11"/>
+      <c r="KB25" s="11"/>
+      <c r="KC25" s="11"/>
+      <c r="KD25" s="11"/>
+      <c r="KE25" s="11"/>
+      <c r="KF25" s="11"/>
+      <c r="KG25" s="11"/>
+      <c r="KH25" s="11"/>
+      <c r="KI25" s="11"/>
+      <c r="KJ25" s="11"/>
+      <c r="KK25" s="11"/>
+      <c r="KL25" s="11"/>
+      <c r="KM25" s="11"/>
+      <c r="KN25" s="11"/>
+      <c r="KO25" s="11"/>
+      <c r="KP25" s="11"/>
+      <c r="KQ25" s="11"/>
+      <c r="KR25" s="11"/>
+      <c r="KS25" s="11"/>
+      <c r="KT25" s="11"/>
+      <c r="KU25" s="11"/>
+      <c r="KV25" s="11"/>
+      <c r="KW25" s="11"/>
+      <c r="KX25" s="11"/>
+      <c r="KY25" s="11"/>
+      <c r="KZ25" s="11"/>
+      <c r="LA25" s="11"/>
+      <c r="LB25" s="11"/>
+      <c r="LC25" s="11"/>
+      <c r="LD25" s="11"/>
+      <c r="LE25" s="11"/>
+      <c r="LF25" s="11"/>
+      <c r="LG25" s="11"/>
+      <c r="LH25" s="11"/>
+      <c r="LI25" s="11"/>
+      <c r="LJ25" s="11"/>
+      <c r="LK25" s="11"/>
+      <c r="LL25" s="11"/>
+      <c r="LM25" s="11"/>
+      <c r="LN25" s="11"/>
+      <c r="LO25" s="11"/>
+      <c r="LP25" s="11"/>
+      <c r="LQ25" s="11"/>
+      <c r="LR25" s="11"/>
+      <c r="LS25" s="11"/>
+      <c r="LT25" s="11"/>
+      <c r="LU25" s="11"/>
+      <c r="LV25" s="11"/>
+      <c r="LW25" s="11"/>
+      <c r="LX25" s="11"/>
+      <c r="LY25" s="11"/>
+      <c r="LZ25" s="11"/>
+      <c r="MA25" s="11"/>
+      <c r="MB25" s="11"/>
+      <c r="MC25" s="11"/>
+      <c r="MD25" s="11"/>
+      <c r="ME25" s="11"/>
+      <c r="MF25" s="11"/>
+      <c r="MG25" s="11"/>
+      <c r="MH25" s="11"/>
+      <c r="MI25" s="11"/>
+      <c r="MJ25" s="11"/>
+      <c r="MK25" s="11"/>
+      <c r="ML25" s="11"/>
+      <c r="MM25" s="11"/>
+      <c r="MN25" s="11"/>
+      <c r="MO25" s="11"/>
+      <c r="MP25" s="11"/>
+      <c r="MQ25" s="11"/>
+      <c r="MR25" s="11"/>
+      <c r="MS25" s="11"/>
+      <c r="MT25" s="11"/>
+      <c r="MU25" s="11"/>
+      <c r="MV25" s="11"/>
+      <c r="MW25" s="11"/>
+      <c r="MX25" s="11"/>
+      <c r="MY25" s="11"/>
+      <c r="MZ25" s="11"/>
+      <c r="NA25" s="11"/>
+      <c r="NB25" s="11"/>
+      <c r="NC25" s="11"/>
+      <c r="ND25" s="11"/>
+      <c r="NE25" s="11"/>
+      <c r="NF25" s="11"/>
+      <c r="NG25" s="11"/>
+      <c r="NH25" s="11"/>
+      <c r="NI25" s="11"/>
+      <c r="NJ25" s="11"/>
+      <c r="NK25" s="11"/>
+      <c r="NL25" s="11"/>
+      <c r="NM25" s="11"/>
+      <c r="NN25" s="11"/>
+      <c r="NO25" s="11"/>
+      <c r="NP25" s="11"/>
+      <c r="NQ25" s="11"/>
+      <c r="NR25" s="11"/>
+      <c r="NS25" s="11"/>
+      <c r="NT25" s="11"/>
+      <c r="NU25" s="11"/>
+      <c r="NV25" s="11"/>
+      <c r="NW25" s="11"/>
+      <c r="NX25" s="11"/>
+      <c r="NY25" s="11"/>
+      <c r="NZ25" s="11"/>
+      <c r="OA25" s="11"/>
+      <c r="OB25" s="11"/>
+      <c r="OC25" s="11"/>
+      <c r="OD25" s="11"/>
+      <c r="OE25" s="11"/>
+      <c r="OF25" s="11"/>
+      <c r="OG25" s="11"/>
+      <c r="OH25" s="11"/>
+      <c r="OI25" s="11"/>
+      <c r="OJ25" s="11"/>
+      <c r="OK25" s="11"/>
+      <c r="OL25" s="11"/>
+      <c r="OM25" s="11"/>
+      <c r="ON25" s="11"/>
+      <c r="OO25" s="11"/>
+      <c r="OP25" s="11"/>
+      <c r="OQ25" s="11"/>
+      <c r="OR25" s="11"/>
+      <c r="OS25" s="11"/>
+      <c r="OT25" s="11"/>
+      <c r="OU25" s="11"/>
+      <c r="OV25" s="11"/>
+      <c r="OW25" s="11"/>
+      <c r="OX25" s="11"/>
+      <c r="OY25" s="11"/>
+      <c r="OZ25" s="11"/>
+      <c r="PA25" s="11"/>
+      <c r="PB25" s="11"/>
+      <c r="PC25" s="11"/>
+      <c r="PD25" s="11"/>
+      <c r="PE25" s="11"/>
+      <c r="PF25" s="11"/>
+      <c r="PG25" s="11"/>
+      <c r="PH25" s="11"/>
+      <c r="PI25" s="11"/>
+      <c r="PJ25" s="11"/>
+      <c r="PK25" s="11"/>
+      <c r="PL25" s="11"/>
+      <c r="PM25" s="11"/>
+      <c r="PN25" s="11"/>
+      <c r="PO25" s="11"/>
+      <c r="PP25" s="11"/>
+      <c r="PQ25" s="11"/>
+      <c r="PR25" s="11"/>
+      <c r="PS25" s="11"/>
+      <c r="PT25" s="11"/>
+      <c r="PU25" s="11"/>
+      <c r="PV25" s="11"/>
+      <c r="PW25" s="11"/>
+      <c r="PX25" s="11"/>
+      <c r="PY25" s="11"/>
+      <c r="PZ25" s="11"/>
+      <c r="QA25" s="11"/>
+      <c r="QB25" s="11"/>
+      <c r="QC25" s="11"/>
+      <c r="QD25" s="11"/>
+      <c r="QE25" s="11"/>
+      <c r="QF25" s="11"/>
+      <c r="QG25" s="11"/>
+      <c r="QH25" s="11"/>
+      <c r="QI25" s="11"/>
+      <c r="QJ25" s="11"/>
+      <c r="QK25" s="11"/>
+      <c r="QL25" s="11"/>
+      <c r="QM25" s="11"/>
+      <c r="QN25" s="11"/>
+      <c r="QO25" s="11"/>
+      <c r="QP25" s="11"/>
+      <c r="QQ25" s="11"/>
+      <c r="QR25" s="11"/>
+      <c r="QS25" s="11"/>
+      <c r="QT25" s="11"/>
+      <c r="QU25" s="11"/>
+      <c r="QV25" s="11"/>
+      <c r="QW25" s="11"/>
+      <c r="QX25" s="11"/>
+      <c r="QY25" s="11"/>
+      <c r="QZ25" s="11"/>
+      <c r="RA25" s="11"/>
+      <c r="RB25" s="11"/>
+      <c r="RC25" s="11"/>
+      <c r="RD25" s="11"/>
+      <c r="RE25" s="11"/>
+      <c r="RF25" s="11"/>
+      <c r="RG25" s="11"/>
+      <c r="RH25" s="11"/>
+      <c r="RI25" s="11"/>
+      <c r="RJ25" s="11"/>
+      <c r="RK25" s="11"/>
+      <c r="RL25" s="11"/>
+      <c r="RM25" s="11"/>
+      <c r="RN25" s="11"/>
+      <c r="RO25" s="11"/>
+      <c r="RP25" s="11"/>
+      <c r="RQ25" s="11"/>
+      <c r="RR25" s="11"/>
+      <c r="RS25" s="11"/>
+      <c r="RT25" s="11"/>
+      <c r="RU25" s="11"/>
+      <c r="RV25" s="11"/>
+      <c r="RW25" s="11"/>
+      <c r="RX25" s="11"/>
+      <c r="RY25" s="11"/>
+      <c r="RZ25" s="11"/>
+      <c r="SA25" s="11"/>
+      <c r="SB25" s="11"/>
+      <c r="SC25" s="11"/>
+      <c r="SD25" s="11"/>
+      <c r="SE25" s="11"/>
+      <c r="SF25" s="11"/>
+      <c r="SG25" s="11"/>
+      <c r="SH25" s="11"/>
+      <c r="SI25" s="11"/>
+      <c r="SJ25" s="11"/>
+      <c r="SK25" s="11"/>
+      <c r="SL25" s="11"/>
+      <c r="SM25" s="11"/>
+      <c r="SN25" s="11"/>
+      <c r="SO25" s="11"/>
+      <c r="SP25" s="11"/>
+      <c r="SQ25" s="11"/>
+      <c r="SR25" s="11"/>
+      <c r="SS25" s="11"/>
+      <c r="ST25" s="11"/>
+      <c r="SU25" s="11"/>
+      <c r="SV25" s="11"/>
+      <c r="SW25" s="11"/>
+      <c r="SX25" s="11"/>
+      <c r="SY25" s="11"/>
+      <c r="SZ25" s="11"/>
+      <c r="TA25" s="11"/>
+      <c r="TB25" s="11"/>
+      <c r="TC25" s="11"/>
+      <c r="TD25" s="11"/>
+      <c r="TE25" s="11"/>
+      <c r="TF25" s="11"/>
+      <c r="TG25" s="11"/>
+      <c r="TH25" s="11"/>
+      <c r="TI25" s="11"/>
+      <c r="TJ25" s="11"/>
+      <c r="TK25" s="11"/>
+      <c r="TL25" s="11"/>
+      <c r="TM25" s="11"/>
+      <c r="TN25" s="11"/>
+      <c r="TO25" s="11"/>
+      <c r="TP25" s="11"/>
+      <c r="TQ25" s="11"/>
+      <c r="TR25" s="11"/>
+      <c r="TS25" s="11"/>
+      <c r="TT25" s="11"/>
+      <c r="TU25" s="11"/>
+      <c r="TV25" s="11"/>
+      <c r="TW25" s="11"/>
+      <c r="TX25" s="11"/>
+      <c r="TY25" s="11"/>
+      <c r="TZ25" s="11"/>
+      <c r="UA25" s="11"/>
+      <c r="UB25" s="11"/>
+      <c r="UC25" s="11"/>
+      <c r="UD25" s="11"/>
+      <c r="UE25" s="11"/>
+      <c r="UF25" s="11"/>
+      <c r="UG25" s="11"/>
+      <c r="UH25" s="11"/>
+      <c r="UI25" s="11"/>
+      <c r="UJ25" s="11"/>
+      <c r="UK25" s="11"/>
+      <c r="UL25" s="11"/>
+      <c r="UM25" s="11"/>
+      <c r="UN25" s="11"/>
+      <c r="UO25" s="11"/>
+      <c r="UP25" s="11"/>
+      <c r="UQ25" s="11"/>
+      <c r="UR25" s="11"/>
+      <c r="US25" s="11"/>
+      <c r="UT25" s="11"/>
+      <c r="UU25" s="11"/>
+      <c r="UV25" s="11"/>
+      <c r="UW25" s="11"/>
+      <c r="UX25" s="11"/>
+      <c r="UY25" s="11"/>
+      <c r="UZ25" s="11"/>
+      <c r="VA25" s="11"/>
+      <c r="VB25" s="11"/>
+      <c r="VC25" s="11"/>
+      <c r="VD25" s="11"/>
+      <c r="VE25" s="11"/>
+      <c r="VF25" s="11"/>
+      <c r="VG25" s="11"/>
+      <c r="VH25" s="11"/>
+      <c r="VI25" s="11"/>
+      <c r="VJ25" s="11"/>
+      <c r="VK25" s="11"/>
+      <c r="VL25" s="11"/>
+      <c r="VM25" s="11"/>
+      <c r="VN25" s="11"/>
+      <c r="VO25" s="11"/>
+      <c r="VP25" s="11"/>
+      <c r="VQ25" s="11"/>
+      <c r="VR25" s="11"/>
+      <c r="VS25" s="11"/>
+      <c r="VT25" s="11"/>
+      <c r="VU25" s="11"/>
+      <c r="VV25" s="11"/>
+      <c r="VW25" s="11"/>
+      <c r="VX25" s="11"/>
+      <c r="VY25" s="11"/>
+      <c r="VZ25" s="11"/>
+      <c r="WA25" s="11"/>
+      <c r="WB25" s="11"/>
+      <c r="WC25" s="11"/>
+      <c r="WD25" s="11"/>
+      <c r="WE25" s="11"/>
+      <c r="WF25" s="11"/>
+      <c r="WG25" s="11"/>
+      <c r="WH25" s="11"/>
+      <c r="WI25" s="11"/>
+      <c r="WJ25" s="11"/>
+      <c r="WK25" s="11"/>
+      <c r="WL25" s="11"/>
+      <c r="WM25" s="11"/>
+      <c r="WN25" s="11"/>
+      <c r="WO25" s="11"/>
+      <c r="WP25" s="11"/>
+      <c r="WQ25" s="11"/>
+      <c r="WR25" s="11"/>
+      <c r="WS25" s="11"/>
+      <c r="WT25" s="11"/>
+      <c r="WU25" s="11"/>
+      <c r="WV25" s="11"/>
+      <c r="WW25" s="11"/>
+      <c r="WX25" s="11"/>
+      <c r="WY25" s="11"/>
+      <c r="WZ25" s="11"/>
+      <c r="XA25" s="11"/>
+      <c r="XB25" s="11"/>
+      <c r="XC25" s="11"/>
+      <c r="XD25" s="11"/>
+      <c r="XE25" s="11"/>
+      <c r="XF25" s="11"/>
+      <c r="XG25" s="11"/>
+      <c r="XH25" s="11"/>
+      <c r="XI25" s="11"/>
+      <c r="XJ25" s="11"/>
+      <c r="XK25" s="11"/>
+      <c r="XL25" s="11"/>
+      <c r="XM25" s="11"/>
+      <c r="XN25" s="11"/>
+      <c r="XO25" s="11"/>
+      <c r="XP25" s="11"/>
+      <c r="XQ25" s="11"/>
+      <c r="XR25" s="11"/>
+      <c r="XS25" s="11"/>
+      <c r="XT25" s="11"/>
+      <c r="XU25" s="11"/>
+      <c r="XV25" s="11"/>
+      <c r="XW25" s="11"/>
+      <c r="XX25" s="11"/>
+      <c r="XY25" s="11"/>
+      <c r="XZ25" s="11"/>
+      <c r="YA25" s="11"/>
+      <c r="YB25" s="11"/>
+      <c r="YC25" s="11"/>
+      <c r="YD25" s="11"/>
+      <c r="YE25" s="11"/>
+      <c r="YF25" s="11"/>
+      <c r="YG25" s="11"/>
+      <c r="YH25" s="11"/>
+      <c r="YI25" s="11"/>
+      <c r="YJ25" s="11"/>
+      <c r="YK25" s="11"/>
+      <c r="YL25" s="11"/>
+      <c r="YM25" s="11"/>
+      <c r="YN25" s="11"/>
+      <c r="YO25" s="11"/>
+      <c r="YP25" s="11"/>
+      <c r="YQ25" s="11"/>
+      <c r="YR25" s="11"/>
+      <c r="YS25" s="11"/>
+      <c r="YT25" s="11"/>
+      <c r="YU25" s="11"/>
+      <c r="YV25" s="11"/>
+      <c r="YW25" s="11"/>
+      <c r="YX25" s="11"/>
+      <c r="YY25" s="11"/>
+      <c r="YZ25" s="11"/>
+      <c r="ZA25" s="11"/>
+      <c r="ZB25" s="11"/>
+      <c r="ZC25" s="11"/>
+      <c r="ZD25" s="11"/>
+      <c r="ZE25" s="11"/>
+      <c r="ZF25" s="11"/>
+      <c r="ZG25" s="11"/>
+      <c r="ZH25" s="11"/>
+      <c r="ZI25" s="11"/>
+      <c r="ZJ25" s="11"/>
+      <c r="ZK25" s="11"/>
+      <c r="ZL25" s="11"/>
+      <c r="ZM25" s="11"/>
+      <c r="ZN25" s="11"/>
+      <c r="ZO25" s="11"/>
+      <c r="ZP25" s="11"/>
+      <c r="ZQ25" s="11"/>
+      <c r="ZR25" s="11"/>
+      <c r="ZS25" s="11"/>
+      <c r="ZT25" s="11"/>
+      <c r="ZU25" s="11"/>
+      <c r="ZV25" s="11"/>
+      <c r="ZW25" s="11"/>
+      <c r="ZX25" s="11"/>
+      <c r="ZY25" s="11"/>
+      <c r="ZZ25" s="11"/>
+      <c r="AAA25" s="11"/>
+      <c r="AAB25" s="11"/>
+      <c r="AAC25" s="11"/>
+      <c r="AAD25" s="11"/>
+      <c r="AAE25" s="11"/>
+      <c r="AAF25" s="11"/>
+      <c r="AAG25" s="11"/>
+      <c r="AAH25" s="11"/>
+      <c r="AAI25" s="11"/>
+      <c r="AAJ25" s="11"/>
+      <c r="AAK25" s="11"/>
+      <c r="AAL25" s="11"/>
+      <c r="AAM25" s="11"/>
+      <c r="AAN25" s="11"/>
+      <c r="AAO25" s="11"/>
+      <c r="AAP25" s="11"/>
+      <c r="AAQ25" s="11"/>
+      <c r="AAR25" s="11"/>
+      <c r="AAS25" s="11"/>
+      <c r="AAT25" s="11"/>
+      <c r="AAU25" s="11"/>
+      <c r="AAV25" s="11"/>
+      <c r="AAW25" s="11"/>
+      <c r="AAX25" s="11"/>
+      <c r="AAY25" s="11"/>
+      <c r="AAZ25" s="11"/>
+      <c r="ABA25" s="11"/>
+      <c r="ABB25" s="11"/>
+      <c r="ABC25" s="11"/>
+      <c r="ABD25" s="11"/>
+      <c r="ABE25" s="11"/>
+      <c r="ABF25" s="11"/>
+      <c r="ABG25" s="11"/>
+      <c r="ABH25" s="11"/>
+      <c r="ABI25" s="11"/>
+      <c r="ABJ25" s="11"/>
+      <c r="ABK25" s="11"/>
+      <c r="ABL25" s="11"/>
+      <c r="ABM25" s="11"/>
+      <c r="ABN25" s="11"/>
+      <c r="ABO25" s="11"/>
+      <c r="ABP25" s="11"/>
+      <c r="ABQ25" s="11"/>
+      <c r="ABR25" s="11"/>
+      <c r="ABS25" s="11"/>
+      <c r="ABT25" s="11"/>
+      <c r="ABU25" s="11"/>
+      <c r="ABV25" s="11"/>
+      <c r="ABW25" s="11"/>
+      <c r="ABX25" s="11"/>
+      <c r="ABY25" s="11"/>
+      <c r="ABZ25" s="11"/>
+      <c r="ACA25" s="11"/>
+      <c r="ACB25" s="11"/>
+      <c r="ACC25" s="11"/>
+      <c r="ACD25" s="11"/>
+      <c r="ACE25" s="11"/>
+      <c r="ACF25" s="11"/>
+      <c r="ACG25" s="11"/>
+      <c r="ACH25" s="11"/>
+      <c r="ACI25" s="11"/>
+      <c r="ACJ25" s="11"/>
+      <c r="ACK25" s="11"/>
+      <c r="ACL25" s="11"/>
+      <c r="ACM25" s="11"/>
+      <c r="ACN25" s="11"/>
+      <c r="ACO25" s="11"/>
+      <c r="ACP25" s="11"/>
+      <c r="ACQ25" s="11"/>
+      <c r="ACR25" s="11"/>
+      <c r="ACS25" s="11"/>
+      <c r="ACT25" s="11"/>
+      <c r="ACU25" s="11"/>
+      <c r="ACV25" s="11"/>
+      <c r="ACW25" s="11"/>
+      <c r="ACX25" s="11"/>
+      <c r="ACY25" s="11"/>
+      <c r="ACZ25" s="11"/>
+      <c r="ADA25" s="11"/>
+      <c r="ADB25" s="11"/>
+      <c r="ADC25" s="11"/>
+      <c r="ADD25" s="11"/>
+      <c r="ADE25" s="11"/>
+      <c r="ADF25" s="11"/>
+      <c r="ADG25" s="11"/>
+      <c r="ADH25" s="11"/>
+      <c r="ADI25" s="11"/>
+      <c r="ADJ25" s="11"/>
+      <c r="ADK25" s="11"/>
+      <c r="ADL25" s="11"/>
+      <c r="ADM25" s="11"/>
+      <c r="ADN25" s="11"/>
+      <c r="ADO25" s="11"/>
+      <c r="ADP25" s="11"/>
+      <c r="ADQ25" s="11"/>
+      <c r="ADR25" s="11"/>
+      <c r="ADS25" s="11"/>
+      <c r="ADT25" s="11"/>
+      <c r="ADU25" s="11"/>
+      <c r="ADV25" s="11"/>
+      <c r="ADW25" s="11"/>
+      <c r="ADX25" s="11"/>
+      <c r="ADY25" s="11"/>
+      <c r="ADZ25" s="11"/>
+      <c r="AEA25" s="11"/>
+      <c r="AEB25" s="11"/>
+      <c r="AEC25" s="11"/>
+      <c r="AED25" s="11"/>
+      <c r="AEE25" s="11"/>
+      <c r="AEF25" s="11"/>
+      <c r="AEG25" s="11"/>
+      <c r="AEH25" s="11"/>
+      <c r="AEI25" s="11"/>
+      <c r="AEJ25" s="11"/>
+      <c r="AEK25" s="11"/>
+      <c r="AEL25" s="11"/>
+      <c r="AEM25" s="11"/>
+      <c r="AEN25" s="11"/>
+      <c r="AEO25" s="11"/>
+      <c r="AEP25" s="11"/>
+      <c r="AEQ25" s="11"/>
+      <c r="AER25" s="11"/>
+      <c r="AES25" s="11"/>
+      <c r="AET25" s="11"/>
+      <c r="AEU25" s="11"/>
+      <c r="AEV25" s="11"/>
+      <c r="AEW25" s="11"/>
+      <c r="AEX25" s="11"/>
+      <c r="AEY25" s="11"/>
+      <c r="AEZ25" s="11"/>
+      <c r="AFA25" s="11"/>
+      <c r="AFB25" s="11"/>
+      <c r="AFC25" s="11"/>
+      <c r="AFD25" s="11"/>
+      <c r="AFE25" s="11"/>
+      <c r="AFF25" s="11"/>
+      <c r="AFG25" s="11"/>
+      <c r="AFH25" s="11"/>
+      <c r="AFI25" s="11"/>
+      <c r="AFJ25" s="11"/>
+      <c r="AFK25" s="11"/>
+      <c r="AFL25" s="11"/>
+      <c r="AFM25" s="11"/>
+      <c r="AFN25" s="11"/>
+      <c r="AFO25" s="11"/>
+      <c r="AFP25" s="11"/>
+      <c r="AFQ25" s="11"/>
+      <c r="AFR25" s="11"/>
+      <c r="AFS25" s="11"/>
+      <c r="AFT25" s="11"/>
+      <c r="AFU25" s="11"/>
+      <c r="AFV25" s="11"/>
+      <c r="AFW25" s="11"/>
+      <c r="AFX25" s="11"/>
+      <c r="AFY25" s="11"/>
+      <c r="AFZ25" s="11"/>
+      <c r="AGA25" s="11"/>
+      <c r="AGB25" s="11"/>
+      <c r="AGC25" s="11"/>
+      <c r="AGD25" s="11"/>
+      <c r="AGE25" s="11"/>
+      <c r="AGF25" s="11"/>
+      <c r="AGG25" s="11"/>
+      <c r="AGH25" s="11"/>
+      <c r="AGI25" s="11"/>
+      <c r="AGJ25" s="11"/>
+      <c r="AGK25" s="11"/>
+      <c r="AGL25" s="11"/>
+      <c r="AGM25" s="11"/>
+      <c r="AGN25" s="11"/>
+      <c r="AGO25" s="11"/>
+      <c r="AGP25" s="11"/>
+      <c r="AGQ25" s="11"/>
+      <c r="AGR25" s="11"/>
+      <c r="AGS25" s="11"/>
+      <c r="AGT25" s="11"/>
+      <c r="AGU25" s="11"/>
+      <c r="AGV25" s="11"/>
+      <c r="AGW25" s="11"/>
+      <c r="AGX25" s="11"/>
+      <c r="AGY25" s="11"/>
+      <c r="AGZ25" s="11"/>
+      <c r="AHA25" s="11"/>
+      <c r="AHB25" s="11"/>
+      <c r="AHC25" s="11"/>
+      <c r="AHD25" s="11"/>
+      <c r="AHE25" s="11"/>
+      <c r="AHF25" s="11"/>
+      <c r="AHG25" s="11"/>
+      <c r="AHH25" s="11"/>
+      <c r="AHI25" s="11"/>
+      <c r="AHJ25" s="11"/>
+      <c r="AHK25" s="11"/>
+      <c r="AHL25" s="11"/>
+      <c r="AHM25" s="11"/>
+      <c r="AHN25" s="11"/>
+      <c r="AHO25" s="11"/>
+      <c r="AHP25" s="11"/>
+      <c r="AHQ25" s="11"/>
+      <c r="AHR25" s="11"/>
+      <c r="AHS25" s="11"/>
+      <c r="AHT25" s="11"/>
+      <c r="AHU25" s="11"/>
+      <c r="AHV25" s="11"/>
+      <c r="AHW25" s="11"/>
+      <c r="AHX25" s="11"/>
+      <c r="AHY25" s="11"/>
+      <c r="AHZ25" s="11"/>
+      <c r="AIA25" s="11"/>
+      <c r="AIB25" s="11"/>
+      <c r="AIC25" s="11"/>
+      <c r="AID25" s="11"/>
+      <c r="AIE25" s="11"/>
+      <c r="AIF25" s="11"/>
+      <c r="AIG25" s="11"/>
+      <c r="AIH25" s="11"/>
+      <c r="AII25" s="11"/>
+      <c r="AIJ25" s="11"/>
+      <c r="AIK25" s="11"/>
+      <c r="AIL25" s="11"/>
+      <c r="AIM25" s="11"/>
+      <c r="AIN25" s="11"/>
+      <c r="AIO25" s="11"/>
+      <c r="AIP25" s="11"/>
+      <c r="AIQ25" s="11"/>
+      <c r="AIR25" s="11"/>
+      <c r="AIS25" s="11"/>
+      <c r="AIT25" s="11"/>
+      <c r="AIU25" s="11"/>
+      <c r="AIV25" s="11"/>
+      <c r="AIW25" s="11"/>
+      <c r="AIX25" s="11"/>
+      <c r="AIY25" s="11"/>
+      <c r="AIZ25" s="11"/>
+      <c r="AJA25" s="11"/>
+      <c r="AJB25" s="11"/>
+      <c r="AJC25" s="11"/>
+      <c r="AJD25" s="11"/>
+      <c r="AJE25" s="11"/>
+      <c r="AJF25" s="11"/>
+      <c r="AJG25" s="11"/>
+      <c r="AJH25" s="11"/>
+      <c r="AJI25" s="11"/>
+      <c r="AJJ25" s="11"/>
+      <c r="AJK25" s="11"/>
+      <c r="AJL25" s="11"/>
+      <c r="AJM25" s="11"/>
+      <c r="AJN25" s="11"/>
+      <c r="AJO25" s="11"/>
+      <c r="AJP25" s="11"/>
+      <c r="AJQ25" s="11"/>
+      <c r="AJR25" s="11"/>
+      <c r="AJS25" s="11"/>
+      <c r="AJT25" s="11"/>
+      <c r="AJU25" s="11"/>
+      <c r="AJV25" s="11"/>
+      <c r="AJW25" s="11"/>
+      <c r="AJX25" s="11"/>
+      <c r="AJY25" s="11"/>
+      <c r="AJZ25" s="11"/>
+      <c r="AKA25" s="11"/>
+      <c r="AKB25" s="11"/>
+      <c r="AKC25" s="11"/>
+      <c r="AKD25" s="11"/>
+      <c r="AKE25" s="11"/>
+      <c r="AKF25" s="11"/>
+      <c r="AKG25" s="11"/>
+      <c r="AKH25" s="11"/>
+      <c r="AKI25" s="11"/>
+      <c r="AKJ25" s="11"/>
+      <c r="AKK25" s="11"/>
+      <c r="AKL25" s="11"/>
+      <c r="AKM25" s="11"/>
+      <c r="AKN25" s="11"/>
+      <c r="AKO25" s="11"/>
+      <c r="AKP25" s="11"/>
+      <c r="AKQ25" s="11"/>
+      <c r="AKR25" s="11"/>
+      <c r="AKS25" s="11"/>
+      <c r="AKT25" s="11"/>
+      <c r="AKU25" s="11"/>
+      <c r="AKV25" s="11"/>
+      <c r="AKW25" s="11"/>
+      <c r="AKX25" s="11"/>
+      <c r="AKY25" s="11"/>
+      <c r="AKZ25" s="11"/>
+      <c r="ALA25" s="11"/>
+      <c r="ALB25" s="11"/>
+      <c r="ALC25" s="11"/>
+      <c r="ALD25" s="11"/>
+      <c r="ALE25" s="11"/>
+      <c r="ALF25" s="11"/>
+      <c r="ALG25" s="11"/>
+      <c r="ALH25" s="11"/>
+      <c r="ALI25" s="11"/>
+      <c r="ALJ25" s="11"/>
+      <c r="ALK25" s="11"/>
+      <c r="ALL25" s="11"/>
+      <c r="ALM25" s="11"/>
+      <c r="ALN25" s="11"/>
+      <c r="ALO25" s="11"/>
+      <c r="ALP25" s="11"/>
+      <c r="ALQ25" s="11"/>
+      <c r="ALR25" s="11"/>
+      <c r="ALS25" s="11"/>
+      <c r="ALT25" s="11"/>
+      <c r="ALU25" s="11"/>
+      <c r="ALV25" s="11"/>
+      <c r="ALW25" s="11"/>
+      <c r="ALX25" s="11"/>
+      <c r="ALY25" s="11"/>
+      <c r="ALZ25" s="11"/>
+      <c r="AMA25" s="11"/>
+      <c r="AMB25" s="11"/>
+      <c r="AMC25" s="11"/>
+      <c r="AMD25" s="11"/>
+      <c r="AME25" s="11"/>
+      <c r="AMF25" s="11"/>
+      <c r="AMG25" s="11"/>
+      <c r="AMH25" s="11"/>
+      <c r="AMI25" s="11"/>
+      <c r="AMJ25" s="0"/>
+    </row>
+    <row r="26" s="23" customFormat="true" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="B26" s="15"/>
-      <c r="C26" s="15"/>
-      <c r="D26" s="16" t="s">
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="20" t="s">
         <v>246</v>
       </c>
-      <c r="E26" s="16" t="s">
+      <c r="E26" s="20" t="s">
         <v>247</v>
       </c>
-      <c r="F26" s="16" t="s">
+      <c r="F26" s="20" t="s">
         <v>248</v>
       </c>
-      <c r="G26" s="16" t="s">
+      <c r="G26" s="20" t="s">
         <v>249</v>
       </c>
-      <c r="H26" s="16" t="s">
+      <c r="H26" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
+      <c r="K26" s="21"/>
+      <c r="L26" s="21"/>
+      <c r="M26" s="21"/>
+      <c r="N26" s="21"/>
+      <c r="O26" s="21"/>
+      <c r="P26" s="21"/>
+      <c r="Q26" s="21"/>
+      <c r="R26" s="21"/>
+      <c r="S26" s="21"/>
+      <c r="T26" s="21"/>
+      <c r="U26" s="21"/>
+      <c r="V26" s="21"/>
+      <c r="W26" s="21"/>
+      <c r="X26" s="21"/>
+      <c r="Y26" s="21"/>
+      <c r="Z26" s="21"/>
+      <c r="AA26" s="21"/>
+      <c r="AB26" s="21"/>
+      <c r="AC26" s="21"/>
+      <c r="AD26" s="21"/>
+      <c r="AE26" s="21"/>
+      <c r="AF26" s="21"/>
+      <c r="AG26" s="21"/>
+      <c r="AH26" s="21"/>
+      <c r="AI26" s="21"/>
+      <c r="AJ26" s="21"/>
+      <c r="AK26" s="21"/>
+      <c r="AL26" s="21"/>
+      <c r="AM26" s="21"/>
+      <c r="AN26" s="21"/>
+      <c r="AO26" s="21"/>
+      <c r="AP26" s="21"/>
+      <c r="AQ26" s="21"/>
+      <c r="AR26" s="21"/>
+      <c r="AS26" s="21"/>
+      <c r="AT26" s="21"/>
+      <c r="AU26" s="21"/>
+      <c r="AV26" s="21"/>
+      <c r="AW26" s="21"/>
+      <c r="AX26" s="21"/>
+      <c r="AY26" s="21"/>
+      <c r="AZ26" s="21"/>
+      <c r="BA26" s="21"/>
+      <c r="BB26" s="21"/>
+      <c r="BC26" s="21"/>
+      <c r="BD26" s="21"/>
+      <c r="BE26" s="21"/>
+      <c r="BF26" s="21"/>
+      <c r="BG26" s="21"/>
+      <c r="BH26" s="21"/>
+      <c r="BI26" s="21"/>
+      <c r="BJ26" s="21"/>
+      <c r="BK26" s="21"/>
+      <c r="BL26" s="21"/>
+      <c r="BM26" s="21"/>
+      <c r="BN26" s="21"/>
+      <c r="BO26" s="21"/>
+      <c r="BP26" s="21"/>
+      <c r="BQ26" s="21"/>
+      <c r="BR26" s="21"/>
+      <c r="BS26" s="21"/>
+      <c r="BT26" s="21"/>
+      <c r="BU26" s="21"/>
+      <c r="BV26" s="21"/>
+      <c r="BW26" s="21"/>
+      <c r="BX26" s="21"/>
+      <c r="BY26" s="21"/>
+      <c r="BZ26" s="21"/>
+      <c r="CA26" s="21"/>
+      <c r="CB26" s="21"/>
+      <c r="CC26" s="21"/>
+      <c r="CD26" s="21"/>
+      <c r="CE26" s="21"/>
+      <c r="CF26" s="21"/>
+      <c r="CG26" s="21"/>
+      <c r="CH26" s="21"/>
+      <c r="CI26" s="21"/>
+      <c r="CJ26" s="21"/>
+      <c r="CK26" s="21"/>
+      <c r="CL26" s="21"/>
+      <c r="CM26" s="21"/>
+      <c r="CN26" s="21"/>
+      <c r="CO26" s="21"/>
+      <c r="CP26" s="21"/>
+      <c r="CQ26" s="21"/>
+      <c r="CR26" s="21"/>
+      <c r="CS26" s="21"/>
+      <c r="CT26" s="21"/>
+      <c r="CU26" s="21"/>
+      <c r="CV26" s="21"/>
+      <c r="CW26" s="21"/>
+      <c r="CX26" s="21"/>
+      <c r="CY26" s="21"/>
+      <c r="CZ26" s="21"/>
+      <c r="DA26" s="21"/>
+      <c r="DB26" s="21"/>
+      <c r="DC26" s="21"/>
+      <c r="DD26" s="21"/>
+      <c r="DE26" s="21"/>
+      <c r="DF26" s="21"/>
+      <c r="DG26" s="21"/>
+      <c r="DH26" s="21"/>
+      <c r="DI26" s="21"/>
+      <c r="DJ26" s="21"/>
+      <c r="DK26" s="21"/>
+      <c r="DL26" s="21"/>
+      <c r="DM26" s="21"/>
+      <c r="DN26" s="21"/>
+      <c r="DO26" s="21"/>
+      <c r="DP26" s="21"/>
+      <c r="DQ26" s="21"/>
+      <c r="DR26" s="21"/>
+      <c r="DS26" s="21"/>
+      <c r="DT26" s="21"/>
+      <c r="DU26" s="21"/>
+      <c r="DV26" s="21"/>
+      <c r="DW26" s="21"/>
+      <c r="DX26" s="21"/>
+      <c r="DY26" s="21"/>
+      <c r="DZ26" s="21"/>
+      <c r="EA26" s="21"/>
+      <c r="EB26" s="21"/>
+      <c r="EC26" s="21"/>
+      <c r="ED26" s="21"/>
+      <c r="EE26" s="21"/>
+      <c r="EF26" s="21"/>
+      <c r="EG26" s="21"/>
+      <c r="EH26" s="21"/>
+      <c r="EI26" s="21"/>
+      <c r="EJ26" s="21"/>
+      <c r="EK26" s="21"/>
+      <c r="EL26" s="21"/>
+      <c r="EM26" s="21"/>
+      <c r="EN26" s="21"/>
+      <c r="EO26" s="21"/>
+      <c r="EP26" s="21"/>
+      <c r="EQ26" s="21"/>
+      <c r="ER26" s="21"/>
+      <c r="ES26" s="21"/>
+      <c r="ET26" s="21"/>
+      <c r="EU26" s="21"/>
+      <c r="EV26" s="21"/>
+      <c r="EW26" s="21"/>
+      <c r="EX26" s="21"/>
+      <c r="EY26" s="21"/>
+      <c r="EZ26" s="21"/>
+      <c r="FA26" s="21"/>
+      <c r="FB26" s="21"/>
+      <c r="FC26" s="21"/>
+      <c r="FD26" s="21"/>
+      <c r="FE26" s="21"/>
+      <c r="FF26" s="21"/>
+      <c r="FG26" s="21"/>
+      <c r="FH26" s="21"/>
+      <c r="FI26" s="21"/>
+      <c r="FJ26" s="21"/>
+      <c r="FK26" s="21"/>
+      <c r="FL26" s="21"/>
+      <c r="FM26" s="21"/>
+      <c r="FN26" s="21"/>
+      <c r="FO26" s="21"/>
+      <c r="FP26" s="21"/>
+      <c r="FQ26" s="21"/>
+      <c r="FR26" s="21"/>
+      <c r="FS26" s="21"/>
+      <c r="FT26" s="21"/>
+      <c r="FU26" s="21"/>
+      <c r="FV26" s="21"/>
+      <c r="FW26" s="21"/>
+      <c r="FX26" s="21"/>
+      <c r="FY26" s="21"/>
+      <c r="FZ26" s="21"/>
+      <c r="GA26" s="21"/>
+      <c r="GB26" s="21"/>
+      <c r="GC26" s="21"/>
+      <c r="GD26" s="21"/>
+      <c r="GE26" s="21"/>
+      <c r="GF26" s="21"/>
+      <c r="GG26" s="21"/>
+      <c r="GH26" s="21"/>
+      <c r="GI26" s="21"/>
+      <c r="GJ26" s="21"/>
+      <c r="GK26" s="21"/>
+      <c r="GL26" s="21"/>
+      <c r="GM26" s="21"/>
+      <c r="GN26" s="21"/>
+      <c r="GO26" s="21"/>
+      <c r="GP26" s="21"/>
+      <c r="GQ26" s="21"/>
+      <c r="GR26" s="21"/>
+      <c r="GS26" s="21"/>
+      <c r="GT26" s="21"/>
+      <c r="GU26" s="21"/>
+      <c r="GV26" s="21"/>
+      <c r="GW26" s="21"/>
+      <c r="GX26" s="21"/>
+      <c r="GY26" s="21"/>
+      <c r="GZ26" s="21"/>
+      <c r="HA26" s="21"/>
+      <c r="HB26" s="21"/>
+      <c r="HC26" s="21"/>
+      <c r="HD26" s="21"/>
+      <c r="HE26" s="21"/>
+      <c r="HF26" s="21"/>
+      <c r="HG26" s="21"/>
+      <c r="HH26" s="21"/>
+      <c r="HI26" s="21"/>
+      <c r="HJ26" s="21"/>
+      <c r="HK26" s="21"/>
+      <c r="HL26" s="21"/>
+      <c r="HM26" s="21"/>
+      <c r="HN26" s="21"/>
+      <c r="HO26" s="21"/>
+      <c r="HP26" s="21"/>
+      <c r="HQ26" s="21"/>
+      <c r="HR26" s="21"/>
+      <c r="HS26" s="21"/>
+      <c r="HT26" s="21"/>
+      <c r="HU26" s="21"/>
+      <c r="HV26" s="21"/>
+      <c r="HW26" s="21"/>
+      <c r="HX26" s="21"/>
+      <c r="HY26" s="21"/>
+      <c r="HZ26" s="21"/>
+      <c r="IA26" s="21"/>
+      <c r="IB26" s="21"/>
+      <c r="IC26" s="21"/>
+      <c r="ID26" s="21"/>
+      <c r="IE26" s="21"/>
+      <c r="IF26" s="21"/>
+      <c r="IG26" s="21"/>
+      <c r="IH26" s="21"/>
+      <c r="II26" s="21"/>
+      <c r="IJ26" s="21"/>
+      <c r="IK26" s="21"/>
+      <c r="IL26" s="21"/>
+      <c r="IM26" s="21"/>
+      <c r="IN26" s="21"/>
+      <c r="IO26" s="21"/>
+      <c r="IP26" s="21"/>
+      <c r="IQ26" s="21"/>
+      <c r="IR26" s="21"/>
+      <c r="IS26" s="21"/>
+      <c r="IT26" s="21"/>
+      <c r="IU26" s="21"/>
+      <c r="IV26" s="21"/>
+      <c r="IW26" s="21"/>
+      <c r="IX26" s="21"/>
+      <c r="IY26" s="21"/>
+      <c r="IZ26" s="21"/>
+      <c r="JA26" s="21"/>
+      <c r="JB26" s="21"/>
+      <c r="JC26" s="21"/>
+      <c r="JD26" s="21"/>
+      <c r="JE26" s="21"/>
+      <c r="JF26" s="21"/>
+      <c r="JG26" s="21"/>
+      <c r="JH26" s="21"/>
+      <c r="JI26" s="21"/>
+      <c r="JJ26" s="21"/>
+      <c r="JK26" s="21"/>
+      <c r="JL26" s="21"/>
+      <c r="JM26" s="21"/>
+      <c r="JN26" s="21"/>
+      <c r="JO26" s="21"/>
+      <c r="JP26" s="21"/>
+      <c r="JQ26" s="21"/>
+      <c r="JR26" s="21"/>
+      <c r="JS26" s="21"/>
+      <c r="JT26" s="21"/>
+      <c r="JU26" s="21"/>
+      <c r="JV26" s="21"/>
+      <c r="JW26" s="21"/>
+      <c r="JX26" s="21"/>
+      <c r="JY26" s="21"/>
+      <c r="JZ26" s="21"/>
+      <c r="KA26" s="21"/>
+      <c r="KB26" s="21"/>
+      <c r="KC26" s="21"/>
+      <c r="KD26" s="21"/>
+      <c r="KE26" s="21"/>
+      <c r="KF26" s="21"/>
+      <c r="KG26" s="21"/>
+      <c r="KH26" s="21"/>
+      <c r="KI26" s="21"/>
+      <c r="KJ26" s="21"/>
+      <c r="KK26" s="21"/>
+      <c r="KL26" s="21"/>
+      <c r="KM26" s="21"/>
+      <c r="KN26" s="21"/>
+      <c r="KO26" s="21"/>
+      <c r="KP26" s="21"/>
+      <c r="KQ26" s="21"/>
+      <c r="KR26" s="21"/>
+      <c r="KS26" s="21"/>
+      <c r="KT26" s="21"/>
+      <c r="KU26" s="21"/>
+      <c r="KV26" s="21"/>
+      <c r="KW26" s="21"/>
+      <c r="KX26" s="21"/>
+      <c r="KY26" s="21"/>
+      <c r="KZ26" s="21"/>
+      <c r="LA26" s="21"/>
+      <c r="LB26" s="21"/>
+      <c r="LC26" s="21"/>
+      <c r="LD26" s="21"/>
+      <c r="LE26" s="21"/>
+      <c r="LF26" s="21"/>
+      <c r="LG26" s="21"/>
+      <c r="LH26" s="21"/>
+      <c r="LI26" s="21"/>
+      <c r="LJ26" s="21"/>
+      <c r="LK26" s="21"/>
+      <c r="LL26" s="21"/>
+      <c r="LM26" s="21"/>
+      <c r="LN26" s="21"/>
+      <c r="LO26" s="21"/>
+      <c r="LP26" s="21"/>
+      <c r="LQ26" s="21"/>
+      <c r="LR26" s="21"/>
+      <c r="LS26" s="21"/>
+      <c r="LT26" s="21"/>
+      <c r="LU26" s="21"/>
+      <c r="LV26" s="21"/>
+      <c r="LW26" s="21"/>
+      <c r="LX26" s="21"/>
+      <c r="LY26" s="21"/>
+      <c r="LZ26" s="21"/>
+      <c r="MA26" s="21"/>
+      <c r="MB26" s="21"/>
+      <c r="MC26" s="21"/>
+      <c r="MD26" s="21"/>
+      <c r="ME26" s="21"/>
+      <c r="MF26" s="21"/>
+      <c r="MG26" s="21"/>
+      <c r="MH26" s="21"/>
+      <c r="MI26" s="21"/>
+      <c r="MJ26" s="21"/>
+      <c r="MK26" s="21"/>
+      <c r="ML26" s="21"/>
+      <c r="MM26" s="21"/>
+      <c r="MN26" s="21"/>
+      <c r="MO26" s="21"/>
+      <c r="MP26" s="21"/>
+      <c r="MQ26" s="21"/>
+      <c r="MR26" s="21"/>
+      <c r="MS26" s="21"/>
+      <c r="MT26" s="21"/>
+      <c r="MU26" s="21"/>
+      <c r="MV26" s="21"/>
+      <c r="MW26" s="21"/>
+      <c r="MX26" s="21"/>
+      <c r="MY26" s="21"/>
+      <c r="MZ26" s="21"/>
+      <c r="NA26" s="21"/>
+      <c r="NB26" s="21"/>
+      <c r="NC26" s="21"/>
+      <c r="ND26" s="21"/>
+      <c r="NE26" s="21"/>
+      <c r="NF26" s="21"/>
+      <c r="NG26" s="21"/>
+      <c r="NH26" s="21"/>
+      <c r="NI26" s="21"/>
+      <c r="NJ26" s="21"/>
+      <c r="NK26" s="21"/>
+      <c r="NL26" s="21"/>
+      <c r="NM26" s="21"/>
+      <c r="NN26" s="21"/>
+      <c r="NO26" s="21"/>
+      <c r="NP26" s="21"/>
+      <c r="NQ26" s="21"/>
+      <c r="NR26" s="21"/>
+      <c r="NS26" s="21"/>
+      <c r="NT26" s="21"/>
+      <c r="NU26" s="21"/>
+      <c r="NV26" s="21"/>
+      <c r="NW26" s="21"/>
+      <c r="NX26" s="21"/>
+      <c r="NY26" s="21"/>
+      <c r="NZ26" s="21"/>
+      <c r="OA26" s="21"/>
+      <c r="OB26" s="21"/>
+      <c r="OC26" s="21"/>
+      <c r="OD26" s="21"/>
+      <c r="OE26" s="21"/>
+      <c r="OF26" s="21"/>
+      <c r="OG26" s="21"/>
+      <c r="OH26" s="21"/>
+      <c r="OI26" s="21"/>
+      <c r="OJ26" s="21"/>
+      <c r="OK26" s="21"/>
+      <c r="OL26" s="21"/>
+      <c r="OM26" s="21"/>
+      <c r="ON26" s="21"/>
+      <c r="OO26" s="21"/>
+      <c r="OP26" s="21"/>
+      <c r="OQ26" s="21"/>
+      <c r="OR26" s="21"/>
+      <c r="OS26" s="21"/>
+      <c r="OT26" s="21"/>
+      <c r="OU26" s="21"/>
+      <c r="OV26" s="21"/>
+      <c r="OW26" s="21"/>
+      <c r="OX26" s="21"/>
+      <c r="OY26" s="21"/>
+      <c r="OZ26" s="21"/>
+      <c r="PA26" s="21"/>
+      <c r="PB26" s="21"/>
+      <c r="PC26" s="21"/>
+      <c r="PD26" s="21"/>
+      <c r="PE26" s="21"/>
+      <c r="PF26" s="21"/>
+      <c r="PG26" s="21"/>
+      <c r="PH26" s="21"/>
+      <c r="PI26" s="21"/>
+      <c r="PJ26" s="21"/>
+      <c r="PK26" s="21"/>
+      <c r="PL26" s="21"/>
+      <c r="PM26" s="21"/>
+      <c r="PN26" s="21"/>
+      <c r="PO26" s="21"/>
+      <c r="PP26" s="21"/>
+      <c r="PQ26" s="21"/>
+      <c r="PR26" s="21"/>
+      <c r="PS26" s="21"/>
+      <c r="PT26" s="21"/>
+      <c r="PU26" s="21"/>
+      <c r="PV26" s="21"/>
+      <c r="PW26" s="21"/>
+      <c r="PX26" s="21"/>
+      <c r="PY26" s="21"/>
+      <c r="PZ26" s="21"/>
+      <c r="QA26" s="21"/>
+      <c r="QB26" s="21"/>
+      <c r="QC26" s="21"/>
+      <c r="QD26" s="21"/>
+      <c r="QE26" s="21"/>
+      <c r="QF26" s="21"/>
+      <c r="QG26" s="21"/>
+      <c r="QH26" s="21"/>
+      <c r="QI26" s="21"/>
+      <c r="QJ26" s="21"/>
+      <c r="QK26" s="21"/>
+      <c r="QL26" s="21"/>
+      <c r="QM26" s="21"/>
+      <c r="QN26" s="21"/>
+      <c r="QO26" s="21"/>
+      <c r="QP26" s="21"/>
+      <c r="QQ26" s="21"/>
+      <c r="QR26" s="21"/>
+      <c r="QS26" s="21"/>
+      <c r="QT26" s="21"/>
+      <c r="QU26" s="21"/>
+      <c r="QV26" s="21"/>
+      <c r="QW26" s="21"/>
+      <c r="QX26" s="21"/>
+      <c r="QY26" s="21"/>
+      <c r="QZ26" s="21"/>
+      <c r="RA26" s="21"/>
+      <c r="RB26" s="21"/>
+      <c r="RC26" s="21"/>
+      <c r="RD26" s="21"/>
+      <c r="RE26" s="21"/>
+      <c r="RF26" s="21"/>
+      <c r="RG26" s="21"/>
+      <c r="RH26" s="21"/>
+      <c r="RI26" s="21"/>
+      <c r="RJ26" s="21"/>
+      <c r="RK26" s="21"/>
+      <c r="RL26" s="21"/>
+      <c r="RM26" s="21"/>
+      <c r="RN26" s="21"/>
+      <c r="RO26" s="21"/>
+      <c r="RP26" s="21"/>
+      <c r="RQ26" s="21"/>
+      <c r="RR26" s="21"/>
+      <c r="RS26" s="21"/>
+      <c r="RT26" s="21"/>
+      <c r="RU26" s="21"/>
+      <c r="RV26" s="21"/>
+      <c r="RW26" s="21"/>
+      <c r="RX26" s="21"/>
+      <c r="RY26" s="21"/>
+      <c r="RZ26" s="21"/>
+      <c r="SA26" s="21"/>
+      <c r="SB26" s="21"/>
+      <c r="SC26" s="21"/>
+      <c r="SD26" s="21"/>
+      <c r="SE26" s="21"/>
+      <c r="SF26" s="21"/>
+      <c r="SG26" s="21"/>
+      <c r="SH26" s="21"/>
+      <c r="SI26" s="21"/>
+      <c r="SJ26" s="21"/>
+      <c r="SK26" s="21"/>
+      <c r="SL26" s="21"/>
+      <c r="SM26" s="21"/>
+      <c r="SN26" s="21"/>
+      <c r="SO26" s="21"/>
+      <c r="SP26" s="21"/>
+      <c r="SQ26" s="21"/>
+      <c r="SR26" s="21"/>
+      <c r="SS26" s="21"/>
+      <c r="ST26" s="21"/>
+      <c r="SU26" s="21"/>
+      <c r="SV26" s="21"/>
+      <c r="SW26" s="21"/>
+      <c r="SX26" s="21"/>
+      <c r="SY26" s="21"/>
+      <c r="SZ26" s="21"/>
+      <c r="TA26" s="21"/>
+      <c r="TB26" s="21"/>
+      <c r="TC26" s="21"/>
+      <c r="TD26" s="21"/>
+      <c r="TE26" s="21"/>
+      <c r="TF26" s="21"/>
+      <c r="TG26" s="21"/>
+      <c r="TH26" s="21"/>
+      <c r="TI26" s="21"/>
+      <c r="TJ26" s="21"/>
+      <c r="TK26" s="21"/>
+      <c r="TL26" s="21"/>
+      <c r="TM26" s="21"/>
+      <c r="TN26" s="21"/>
+      <c r="TO26" s="21"/>
+      <c r="TP26" s="21"/>
+      <c r="TQ26" s="21"/>
+      <c r="TR26" s="21"/>
+      <c r="TS26" s="21"/>
+      <c r="TT26" s="21"/>
+      <c r="TU26" s="21"/>
+      <c r="TV26" s="21"/>
+      <c r="TW26" s="21"/>
+      <c r="TX26" s="21"/>
+      <c r="TY26" s="21"/>
+      <c r="TZ26" s="21"/>
+      <c r="UA26" s="21"/>
+      <c r="UB26" s="21"/>
+      <c r="UC26" s="21"/>
+      <c r="UD26" s="21"/>
+      <c r="UE26" s="21"/>
+      <c r="UF26" s="21"/>
+      <c r="UG26" s="21"/>
+      <c r="UH26" s="21"/>
+      <c r="UI26" s="21"/>
+      <c r="UJ26" s="21"/>
+      <c r="UK26" s="21"/>
+      <c r="UL26" s="21"/>
+      <c r="UM26" s="21"/>
+      <c r="UN26" s="21"/>
+      <c r="UO26" s="21"/>
+      <c r="UP26" s="21"/>
+      <c r="UQ26" s="21"/>
+      <c r="UR26" s="21"/>
+      <c r="US26" s="21"/>
+      <c r="UT26" s="21"/>
+      <c r="UU26" s="21"/>
+      <c r="UV26" s="21"/>
+      <c r="UW26" s="21"/>
+      <c r="UX26" s="21"/>
+      <c r="UY26" s="21"/>
+      <c r="UZ26" s="21"/>
+      <c r="VA26" s="21"/>
+      <c r="VB26" s="21"/>
+      <c r="VC26" s="21"/>
+      <c r="VD26" s="21"/>
+      <c r="VE26" s="21"/>
+      <c r="VF26" s="21"/>
+      <c r="VG26" s="21"/>
+      <c r="VH26" s="21"/>
+      <c r="VI26" s="21"/>
+      <c r="VJ26" s="21"/>
+      <c r="VK26" s="21"/>
+      <c r="VL26" s="21"/>
+      <c r="VM26" s="21"/>
+      <c r="VN26" s="21"/>
+      <c r="VO26" s="21"/>
+      <c r="VP26" s="21"/>
+      <c r="VQ26" s="21"/>
+      <c r="VR26" s="21"/>
+      <c r="VS26" s="21"/>
+      <c r="VT26" s="21"/>
+      <c r="VU26" s="21"/>
+      <c r="VV26" s="21"/>
+      <c r="VW26" s="21"/>
+      <c r="VX26" s="21"/>
+      <c r="VY26" s="21"/>
+      <c r="VZ26" s="21"/>
+      <c r="WA26" s="21"/>
+      <c r="WB26" s="21"/>
+      <c r="WC26" s="21"/>
+      <c r="WD26" s="21"/>
+      <c r="WE26" s="21"/>
+      <c r="WF26" s="21"/>
+      <c r="WG26" s="21"/>
+      <c r="WH26" s="21"/>
+      <c r="WI26" s="21"/>
+      <c r="WJ26" s="21"/>
+      <c r="WK26" s="21"/>
+      <c r="WL26" s="21"/>
+      <c r="WM26" s="21"/>
+      <c r="WN26" s="21"/>
+      <c r="WO26" s="21"/>
+      <c r="WP26" s="21"/>
+      <c r="WQ26" s="21"/>
+      <c r="WR26" s="21"/>
+      <c r="WS26" s="21"/>
+      <c r="WT26" s="21"/>
+      <c r="WU26" s="21"/>
+      <c r="WV26" s="21"/>
+      <c r="WW26" s="21"/>
+      <c r="WX26" s="21"/>
+      <c r="WY26" s="21"/>
+      <c r="WZ26" s="21"/>
+      <c r="XA26" s="21"/>
+      <c r="XB26" s="21"/>
+      <c r="XC26" s="21"/>
+      <c r="XD26" s="21"/>
+      <c r="XE26" s="21"/>
+      <c r="XF26" s="21"/>
+      <c r="XG26" s="21"/>
+      <c r="XH26" s="21"/>
+      <c r="XI26" s="21"/>
+      <c r="XJ26" s="21"/>
+      <c r="XK26" s="21"/>
+      <c r="XL26" s="21"/>
+      <c r="XM26" s="21"/>
+      <c r="XN26" s="21"/>
+      <c r="XO26" s="21"/>
+      <c r="XP26" s="21"/>
+      <c r="XQ26" s="21"/>
+      <c r="XR26" s="21"/>
+      <c r="XS26" s="21"/>
+      <c r="XT26" s="21"/>
+      <c r="XU26" s="21"/>
+      <c r="XV26" s="21"/>
+      <c r="XW26" s="21"/>
+      <c r="XX26" s="21"/>
+      <c r="XY26" s="21"/>
+      <c r="XZ26" s="21"/>
+      <c r="YA26" s="21"/>
+      <c r="YB26" s="21"/>
+      <c r="YC26" s="21"/>
+      <c r="YD26" s="21"/>
+      <c r="YE26" s="21"/>
+      <c r="YF26" s="21"/>
+      <c r="YG26" s="21"/>
+      <c r="YH26" s="21"/>
+      <c r="YI26" s="21"/>
+      <c r="YJ26" s="21"/>
+      <c r="YK26" s="21"/>
+      <c r="YL26" s="21"/>
+      <c r="YM26" s="21"/>
+      <c r="YN26" s="21"/>
+      <c r="YO26" s="21"/>
+      <c r="YP26" s="21"/>
+      <c r="YQ26" s="21"/>
+      <c r="YR26" s="21"/>
+      <c r="YS26" s="21"/>
+      <c r="YT26" s="21"/>
+      <c r="YU26" s="21"/>
+      <c r="YV26" s="21"/>
+      <c r="YW26" s="21"/>
+      <c r="YX26" s="21"/>
+      <c r="YY26" s="21"/>
+      <c r="YZ26" s="21"/>
+      <c r="ZA26" s="21"/>
+      <c r="ZB26" s="21"/>
+      <c r="ZC26" s="21"/>
+      <c r="ZD26" s="21"/>
+      <c r="ZE26" s="21"/>
+      <c r="ZF26" s="21"/>
+      <c r="ZG26" s="21"/>
+      <c r="ZH26" s="21"/>
+      <c r="ZI26" s="21"/>
+      <c r="ZJ26" s="21"/>
+      <c r="ZK26" s="21"/>
+      <c r="ZL26" s="21"/>
+      <c r="ZM26" s="21"/>
+      <c r="ZN26" s="21"/>
+      <c r="ZO26" s="21"/>
+      <c r="ZP26" s="21"/>
+      <c r="ZQ26" s="21"/>
+      <c r="ZR26" s="21"/>
+      <c r="ZS26" s="21"/>
+      <c r="ZT26" s="21"/>
+      <c r="ZU26" s="21"/>
+      <c r="ZV26" s="21"/>
+      <c r="ZW26" s="21"/>
+      <c r="ZX26" s="21"/>
+      <c r="ZY26" s="21"/>
+      <c r="ZZ26" s="21"/>
+      <c r="AAA26" s="21"/>
+      <c r="AAB26" s="21"/>
+      <c r="AAC26" s="21"/>
+      <c r="AAD26" s="21"/>
+      <c r="AAE26" s="21"/>
+      <c r="AAF26" s="21"/>
+      <c r="AAG26" s="21"/>
+      <c r="AAH26" s="21"/>
+      <c r="AAI26" s="21"/>
+      <c r="AAJ26" s="21"/>
+      <c r="AAK26" s="21"/>
+      <c r="AAL26" s="21"/>
+      <c r="AAM26" s="21"/>
+      <c r="AAN26" s="21"/>
+      <c r="AAO26" s="21"/>
+      <c r="AAP26" s="21"/>
+      <c r="AAQ26" s="21"/>
+      <c r="AAR26" s="21"/>
+      <c r="AAS26" s="21"/>
+      <c r="AAT26" s="21"/>
+      <c r="AAU26" s="21"/>
+      <c r="AAV26" s="21"/>
+      <c r="AAW26" s="21"/>
+      <c r="AAX26" s="21"/>
+      <c r="AAY26" s="21"/>
+      <c r="AAZ26" s="21"/>
+      <c r="ABA26" s="21"/>
+      <c r="ABB26" s="21"/>
+      <c r="ABC26" s="21"/>
+      <c r="ABD26" s="21"/>
+      <c r="ABE26" s="21"/>
+      <c r="ABF26" s="21"/>
+      <c r="ABG26" s="21"/>
+      <c r="ABH26" s="21"/>
+      <c r="ABI26" s="21"/>
+      <c r="ABJ26" s="21"/>
+      <c r="ABK26" s="21"/>
+      <c r="ABL26" s="21"/>
+      <c r="ABM26" s="21"/>
+      <c r="ABN26" s="21"/>
+      <c r="ABO26" s="21"/>
+      <c r="ABP26" s="21"/>
+      <c r="ABQ26" s="21"/>
+      <c r="ABR26" s="21"/>
+      <c r="ABS26" s="21"/>
+      <c r="ABT26" s="21"/>
+      <c r="ABU26" s="21"/>
+      <c r="ABV26" s="21"/>
+      <c r="ABW26" s="21"/>
+      <c r="ABX26" s="21"/>
+      <c r="ABY26" s="21"/>
+      <c r="ABZ26" s="21"/>
+      <c r="ACA26" s="21"/>
+      <c r="ACB26" s="21"/>
+      <c r="ACC26" s="21"/>
+      <c r="ACD26" s="21"/>
+      <c r="ACE26" s="21"/>
+      <c r="ACF26" s="21"/>
+      <c r="ACG26" s="21"/>
+      <c r="ACH26" s="21"/>
+      <c r="ACI26" s="21"/>
+      <c r="ACJ26" s="21"/>
+      <c r="ACK26" s="21"/>
+      <c r="ACL26" s="21"/>
+      <c r="ACM26" s="21"/>
+      <c r="ACN26" s="21"/>
+      <c r="ACO26" s="21"/>
+      <c r="ACP26" s="21"/>
+      <c r="ACQ26" s="21"/>
+      <c r="ACR26" s="21"/>
+      <c r="ACS26" s="21"/>
+      <c r="ACT26" s="21"/>
+      <c r="ACU26" s="21"/>
+      <c r="ACV26" s="21"/>
+      <c r="ACW26" s="21"/>
+      <c r="ACX26" s="21"/>
+      <c r="ACY26" s="21"/>
+      <c r="ACZ26" s="21"/>
+      <c r="ADA26" s="21"/>
+      <c r="ADB26" s="21"/>
+      <c r="ADC26" s="21"/>
+      <c r="ADD26" s="21"/>
+      <c r="ADE26" s="21"/>
+      <c r="ADF26" s="21"/>
+      <c r="ADG26" s="21"/>
+      <c r="ADH26" s="21"/>
+      <c r="ADI26" s="21"/>
+      <c r="ADJ26" s="21"/>
+      <c r="ADK26" s="21"/>
+      <c r="ADL26" s="21"/>
+      <c r="ADM26" s="21"/>
+      <c r="ADN26" s="21"/>
+      <c r="ADO26" s="21"/>
+      <c r="ADP26" s="21"/>
+      <c r="ADQ26" s="21"/>
+      <c r="ADR26" s="21"/>
+      <c r="ADS26" s="21"/>
+      <c r="ADT26" s="21"/>
+      <c r="ADU26" s="21"/>
+      <c r="ADV26" s="21"/>
+      <c r="ADW26" s="21"/>
+      <c r="ADX26" s="21"/>
+      <c r="ADY26" s="21"/>
+      <c r="ADZ26" s="21"/>
+      <c r="AEA26" s="21"/>
+      <c r="AEB26" s="21"/>
+      <c r="AEC26" s="21"/>
+      <c r="AED26" s="21"/>
+      <c r="AEE26" s="21"/>
+      <c r="AEF26" s="21"/>
+      <c r="AEG26" s="21"/>
+      <c r="AEH26" s="21"/>
+      <c r="AEI26" s="21"/>
+      <c r="AEJ26" s="21"/>
+      <c r="AEK26" s="21"/>
+      <c r="AEL26" s="21"/>
+      <c r="AEM26" s="21"/>
+      <c r="AEN26" s="21"/>
+      <c r="AEO26" s="21"/>
+      <c r="AEP26" s="21"/>
+      <c r="AEQ26" s="21"/>
+      <c r="AER26" s="21"/>
+      <c r="AES26" s="21"/>
+      <c r="AET26" s="21"/>
+      <c r="AEU26" s="21"/>
+      <c r="AEV26" s="21"/>
+      <c r="AEW26" s="21"/>
+      <c r="AEX26" s="21"/>
+      <c r="AEY26" s="21"/>
+      <c r="AEZ26" s="21"/>
+      <c r="AFA26" s="21"/>
+      <c r="AFB26" s="21"/>
+      <c r="AFC26" s="21"/>
+      <c r="AFD26" s="21"/>
+      <c r="AFE26" s="21"/>
+      <c r="AFF26" s="21"/>
+      <c r="AFG26" s="21"/>
+      <c r="AFH26" s="21"/>
+      <c r="AFI26" s="21"/>
+      <c r="AFJ26" s="21"/>
+      <c r="AFK26" s="21"/>
+      <c r="AFL26" s="21"/>
+      <c r="AFM26" s="21"/>
+      <c r="AFN26" s="21"/>
+      <c r="AFO26" s="21"/>
+      <c r="AFP26" s="21"/>
+      <c r="AFQ26" s="21"/>
+      <c r="AFR26" s="21"/>
+      <c r="AFS26" s="21"/>
+      <c r="AFT26" s="21"/>
+      <c r="AFU26" s="21"/>
+      <c r="AFV26" s="21"/>
+      <c r="AFW26" s="21"/>
+      <c r="AFX26" s="21"/>
+      <c r="AFY26" s="21"/>
+      <c r="AFZ26" s="21"/>
+      <c r="AGA26" s="21"/>
+      <c r="AGB26" s="21"/>
+      <c r="AGC26" s="21"/>
+      <c r="AGD26" s="21"/>
+      <c r="AGE26" s="21"/>
+      <c r="AGF26" s="21"/>
+      <c r="AGG26" s="21"/>
+      <c r="AGH26" s="21"/>
+      <c r="AGI26" s="21"/>
+      <c r="AGJ26" s="21"/>
+      <c r="AGK26" s="21"/>
+      <c r="AGL26" s="21"/>
+      <c r="AGM26" s="21"/>
+      <c r="AGN26" s="21"/>
+      <c r="AGO26" s="21"/>
+      <c r="AGP26" s="21"/>
+      <c r="AGQ26" s="21"/>
+      <c r="AGR26" s="21"/>
+      <c r="AGS26" s="21"/>
+      <c r="AGT26" s="21"/>
+      <c r="AGU26" s="21"/>
+      <c r="AGV26" s="21"/>
+      <c r="AGW26" s="21"/>
+      <c r="AGX26" s="21"/>
+      <c r="AGY26" s="21"/>
+      <c r="AGZ26" s="21"/>
+      <c r="AHA26" s="21"/>
+      <c r="AHB26" s="21"/>
+      <c r="AHC26" s="21"/>
+      <c r="AHD26" s="21"/>
+      <c r="AHE26" s="21"/>
+      <c r="AHF26" s="21"/>
+      <c r="AHG26" s="21"/>
+      <c r="AHH26" s="21"/>
+      <c r="AHI26" s="21"/>
+      <c r="AHJ26" s="21"/>
+      <c r="AHK26" s="21"/>
+      <c r="AHL26" s="21"/>
+      <c r="AHM26" s="21"/>
+      <c r="AHN26" s="21"/>
+      <c r="AHO26" s="21"/>
+      <c r="AHP26" s="21"/>
+      <c r="AHQ26" s="21"/>
+      <c r="AHR26" s="21"/>
+      <c r="AHS26" s="21"/>
+      <c r="AHT26" s="21"/>
+      <c r="AHU26" s="21"/>
+      <c r="AHV26" s="21"/>
+      <c r="AHW26" s="21"/>
+      <c r="AHX26" s="21"/>
+      <c r="AHY26" s="21"/>
+      <c r="AHZ26" s="21"/>
+      <c r="AIA26" s="21"/>
+      <c r="AIB26" s="21"/>
+      <c r="AIC26" s="21"/>
+      <c r="AID26" s="21"/>
+      <c r="AIE26" s="21"/>
+      <c r="AIF26" s="21"/>
+      <c r="AIG26" s="21"/>
+      <c r="AIH26" s="21"/>
+      <c r="AII26" s="21"/>
+      <c r="AIJ26" s="21"/>
+      <c r="AIK26" s="21"/>
+      <c r="AIL26" s="21"/>
+      <c r="AIM26" s="21"/>
+      <c r="AIN26" s="21"/>
+      <c r="AIO26" s="21"/>
+      <c r="AIP26" s="21"/>
+      <c r="AIQ26" s="21"/>
+      <c r="AIR26" s="21"/>
+      <c r="AIS26" s="21"/>
+      <c r="AIT26" s="21"/>
+      <c r="AIU26" s="21"/>
+      <c r="AIV26" s="21"/>
+      <c r="AIW26" s="21"/>
+      <c r="AIX26" s="21"/>
+      <c r="AIY26" s="21"/>
+      <c r="AIZ26" s="21"/>
+      <c r="AJA26" s="21"/>
+      <c r="AJB26" s="21"/>
+      <c r="AJC26" s="21"/>
+      <c r="AJD26" s="21"/>
+      <c r="AJE26" s="21"/>
+      <c r="AJF26" s="21"/>
+      <c r="AJG26" s="21"/>
+      <c r="AJH26" s="21"/>
+      <c r="AJI26" s="21"/>
+      <c r="AJJ26" s="21"/>
+      <c r="AJK26" s="21"/>
+      <c r="AJL26" s="21"/>
+      <c r="AJM26" s="21"/>
+      <c r="AJN26" s="21"/>
+      <c r="AJO26" s="21"/>
+      <c r="AJP26" s="21"/>
+      <c r="AJQ26" s="21"/>
+      <c r="AJR26" s="21"/>
+      <c r="AJS26" s="21"/>
+      <c r="AJT26" s="21"/>
+      <c r="AJU26" s="21"/>
+      <c r="AJV26" s="21"/>
+      <c r="AJW26" s="21"/>
+      <c r="AJX26" s="21"/>
+      <c r="AJY26" s="21"/>
+      <c r="AJZ26" s="21"/>
+      <c r="AKA26" s="21"/>
+      <c r="AKB26" s="21"/>
+      <c r="AKC26" s="21"/>
+      <c r="AKD26" s="21"/>
+      <c r="AKE26" s="21"/>
+      <c r="AKF26" s="21"/>
+      <c r="AKG26" s="21"/>
+      <c r="AKH26" s="21"/>
+      <c r="AKI26" s="21"/>
+      <c r="AKJ26" s="21"/>
+      <c r="AKK26" s="21"/>
+      <c r="AKL26" s="21"/>
+      <c r="AKM26" s="21"/>
+      <c r="AKN26" s="21"/>
+      <c r="AKO26" s="21"/>
+      <c r="AKP26" s="21"/>
+      <c r="AKQ26" s="21"/>
+      <c r="AKR26" s="21"/>
+      <c r="AKS26" s="21"/>
+      <c r="AKT26" s="21"/>
+      <c r="AKU26" s="21"/>
+      <c r="AKV26" s="21"/>
+      <c r="AKW26" s="21"/>
+      <c r="AKX26" s="21"/>
+      <c r="AKY26" s="21"/>
+      <c r="AKZ26" s="21"/>
+      <c r="ALA26" s="21"/>
+      <c r="ALB26" s="21"/>
+      <c r="ALC26" s="21"/>
+      <c r="ALD26" s="21"/>
+      <c r="ALE26" s="21"/>
+      <c r="ALF26" s="21"/>
+      <c r="ALG26" s="21"/>
+      <c r="ALH26" s="21"/>
+      <c r="ALI26" s="21"/>
+      <c r="ALJ26" s="21"/>
+      <c r="ALK26" s="21"/>
+      <c r="ALL26" s="21"/>
+      <c r="ALM26" s="21"/>
+      <c r="ALN26" s="21"/>
+      <c r="ALO26" s="21"/>
+      <c r="ALP26" s="21"/>
+      <c r="ALQ26" s="21"/>
+      <c r="ALR26" s="21"/>
+      <c r="ALS26" s="21"/>
+      <c r="ALT26" s="21"/>
+      <c r="ALU26" s="21"/>
+      <c r="ALV26" s="21"/>
+      <c r="ALW26" s="21"/>
+      <c r="ALX26" s="21"/>
+      <c r="ALY26" s="21"/>
+      <c r="ALZ26" s="21"/>
+      <c r="AMA26" s="21"/>
+      <c r="AMB26" s="21"/>
+      <c r="AMC26" s="21"/>
+      <c r="AMD26" s="21"/>
+      <c r="AME26" s="21"/>
+      <c r="AMF26" s="21"/>
+      <c r="AMG26" s="21"/>
+      <c r="AMH26" s="21"/>
+      <c r="AMI26" s="21"/>
+      <c r="AMJ26" s="22"/>
+    </row>
+    <row r="27" customFormat="false" ht="258.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="15" t="s">
         <v>250</v>
       </c>
-      <c r="I26" s="16"/>
-      <c r="J26" s="16"/>
-    </row>
-    <row r="27" customFormat="false" ht="247.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="15" t="s">
+      <c r="E27" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="F27" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="G27" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="H27" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="I27" s="15"/>
+      <c r="J27" s="15"/>
+    </row>
+    <row r="28" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="14"/>
+      <c r="B28" s="14"/>
+      <c r="C28" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="E28" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="F28" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="G28" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="H28" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="I28" s="15"/>
+      <c r="J28" s="15"/>
+    </row>
+    <row r="29" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="16" t="s">
-        <v>251</v>
-      </c>
-      <c r="E27" s="16" t="s">
-        <v>252</v>
-      </c>
-      <c r="F27" s="16" t="s">
-        <v>253</v>
-      </c>
-      <c r="G27" s="16" t="s">
-        <v>254</v>
-      </c>
-      <c r="H27" s="16" t="s">
-        <v>255</v>
-      </c>
-      <c r="I27" s="16"/>
-      <c r="J27" s="16"/>
-    </row>
-    <row r="28" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="15"/>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15" t="s">
-        <v>256</v>
-      </c>
-      <c r="D28" s="16" t="s">
-        <v>257</v>
-      </c>
-      <c r="E28" s="16" t="s">
-        <v>258</v>
-      </c>
-      <c r="F28" s="16" t="s">
-        <v>259</v>
-      </c>
-      <c r="G28" s="16" t="s">
+      <c r="B29" s="14"/>
+      <c r="C29" s="14"/>
+      <c r="D29" s="15" t="s">
         <v>260</v>
       </c>
-      <c r="H28" s="16" t="s">
-        <v>223</v>
-      </c>
-      <c r="I28" s="16"/>
-      <c r="J28" s="16"/>
-    </row>
-    <row r="29" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="15" t="s">
+      <c r="E29" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="F29" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="G29" s="15" t="s">
+        <v>263</v>
+      </c>
+      <c r="H29" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="I29" s="15"/>
+      <c r="J29" s="15"/>
+    </row>
+    <row r="30" customFormat="false" ht="169.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
-      <c r="D29" s="16" t="s">
-        <v>261</v>
-      </c>
-      <c r="E29" s="16" t="s">
-        <v>262</v>
-      </c>
-      <c r="F29" s="16" t="s">
-        <v>263</v>
-      </c>
-      <c r="G29" s="16" t="s">
-        <v>264</v>
-      </c>
-      <c r="H29" s="16" t="s">
+      <c r="B30" s="14"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="15" t="s">
         <v>265</v>
       </c>
-      <c r="I29" s="16"/>
-      <c r="J29" s="16"/>
-    </row>
-    <row r="30" customFormat="false" ht="169.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="15" t="s">
+      <c r="E30" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="F30" s="15" t="s">
+        <v>267</v>
+      </c>
+      <c r="G30" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="H30" s="15" t="s">
+        <v>269</v>
+      </c>
+      <c r="I30" s="15"/>
+      <c r="J30" s="15"/>
+    </row>
+    <row r="31" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="16" t="s">
-        <v>266</v>
-      </c>
-      <c r="E30" s="16" t="s">
-        <v>267</v>
-      </c>
-      <c r="F30" s="16" t="s">
-        <v>268</v>
-      </c>
-      <c r="G30" s="16" t="s">
+      <c r="B31" s="14"/>
+      <c r="C31" s="14"/>
+      <c r="D31" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="E31" s="15" t="s">
+        <v>271</v>
+      </c>
+      <c r="F31" s="15" t="s">
+        <v>272</v>
+      </c>
+      <c r="G31" s="15" t="s">
+        <v>273</v>
+      </c>
+      <c r="H31" s="15" t="s">
         <v>269</v>
       </c>
-      <c r="H30" s="16" t="s">
-        <v>270</v>
-      </c>
-      <c r="I30" s="16"/>
-      <c r="J30" s="16"/>
-    </row>
-    <row r="31" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="15" t="s">
+      <c r="I31" s="15"/>
+      <c r="J31" s="15"/>
+    </row>
+    <row r="32" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="B31" s="15"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="16" t="s">
-        <v>271</v>
-      </c>
-      <c r="E31" s="16" t="s">
-        <v>272</v>
-      </c>
-      <c r="F31" s="16" t="s">
-        <v>273</v>
-      </c>
-      <c r="G31" s="16" t="s">
+      <c r="B32" s="14"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="15" t="s">
         <v>274</v>
       </c>
-      <c r="H31" s="16" t="s">
-        <v>270</v>
-      </c>
-      <c r="I31" s="16"/>
-      <c r="J31" s="16"/>
-    </row>
-    <row r="32" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="15" t="s">
+      <c r="E32" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="F32" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="G32" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="H32" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="I32" s="15"/>
+      <c r="J32" s="15"/>
+    </row>
+    <row r="33" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="B32" s="15"/>
-      <c r="C32" s="15"/>
-      <c r="D32" s="16" t="s">
-        <v>275</v>
-      </c>
-      <c r="E32" s="16" t="s">
-        <v>276</v>
-      </c>
-      <c r="F32" s="16" t="s">
-        <v>277</v>
-      </c>
-      <c r="G32" s="16" t="s">
+      <c r="B33" s="14"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="15" t="s">
         <v>278</v>
       </c>
-      <c r="H32" s="16" t="s">
+      <c r="E33" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="F33" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="G33" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="H33" s="15" t="s">
         <v>213</v>
       </c>
-      <c r="I32" s="16"/>
-      <c r="J32" s="16"/>
-    </row>
-    <row r="33" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="15" t="s">
+      <c r="I33" s="15"/>
+      <c r="J33" s="15"/>
+    </row>
+    <row r="34" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="B33" s="15"/>
-      <c r="C33" s="15"/>
-      <c r="D33" s="16" t="s">
-        <v>279</v>
-      </c>
-      <c r="E33" s="16" t="s">
-        <v>280</v>
-      </c>
-      <c r="F33" s="16" t="s">
-        <v>281</v>
-      </c>
-      <c r="G33" s="16" t="s">
+      <c r="B34" s="14"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="15" t="s">
         <v>282</v>
       </c>
-      <c r="H33" s="16" t="s">
-        <v>213</v>
-      </c>
-      <c r="I33" s="16"/>
-      <c r="J33" s="16"/>
-    </row>
-    <row r="34" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="B34" s="15"/>
-      <c r="C34" s="15"/>
-      <c r="D34" s="16" t="s">
+      <c r="E34" s="15" t="s">
         <v>283</v>
       </c>
-      <c r="E34" s="16" t="s">
+      <c r="F34" s="15" t="s">
         <v>284</v>
       </c>
-      <c r="F34" s="16" t="s">
+      <c r="G34" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="G34" s="16" t="s">
+      <c r="H34" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="H34" s="16" t="s">
+      <c r="I34" s="15"/>
+      <c r="J34" s="15"/>
+    </row>
+    <row r="35" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="14"/>
+      <c r="B35" s="14"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="I34" s="16"/>
-      <c r="J34" s="16"/>
-    </row>
-    <row r="35" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="15"/>
-      <c r="B35" s="15"/>
-      <c r="C35" s="15"/>
-      <c r="D35" s="16" t="s">
+      <c r="E35" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="E35" s="16" t="s">
+      <c r="F35" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="F35" s="16" t="s">
+      <c r="G35" s="15" t="s">
         <v>290</v>
       </c>
-      <c r="G35" s="16" t="s">
+      <c r="H35" s="15" t="s">
         <v>291</v>
       </c>
-      <c r="H35" s="16" t="s">
+      <c r="I35" s="15"/>
+      <c r="J35" s="15"/>
+    </row>
+    <row r="36" customFormat="false" ht="68.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="14"/>
+      <c r="B36" s="14"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="15" t="s">
         <v>292</v>
       </c>
-      <c r="I35" s="16"/>
-      <c r="J35" s="16"/>
-    </row>
-    <row r="36" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="15"/>
-      <c r="B36" s="15"/>
-      <c r="C36" s="15"/>
-      <c r="D36" s="16" t="s">
+      <c r="E36" s="15" t="s">
         <v>293</v>
       </c>
-      <c r="E36" s="16" t="s">
+      <c r="F36" s="15" t="s">
         <v>294</v>
       </c>
-      <c r="F36" s="16" t="s">
+      <c r="G36" s="15" t="s">
         <v>295</v>
       </c>
-      <c r="G36" s="16" t="s">
+      <c r="H36" s="15" t="s">
         <v>296</v>
       </c>
-      <c r="H36" s="16" t="s">
+      <c r="I36" s="15"/>
+      <c r="J36" s="15"/>
+    </row>
+    <row r="37" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="14"/>
+      <c r="B37" s="14"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="15" t="s">
         <v>297</v>
       </c>
-      <c r="I36" s="16"/>
-      <c r="J36" s="16"/>
-    </row>
-    <row r="37" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="15"/>
-      <c r="B37" s="15"/>
-      <c r="C37" s="15"/>
-      <c r="D37" s="16" t="s">
+      <c r="E37" s="15" t="s">
         <v>298</v>
       </c>
-      <c r="E37" s="16" t="s">
+      <c r="F37" s="15" t="s">
         <v>299</v>
       </c>
-      <c r="F37" s="16" t="s">
+      <c r="G37" s="15" t="s">
         <v>300</v>
       </c>
-      <c r="G37" s="16" t="s">
+      <c r="H37" s="15" t="s">
         <v>301</v>
       </c>
-      <c r="H37" s="16" t="s">
+      <c r="I37" s="15"/>
+      <c r="J37" s="15"/>
+    </row>
+    <row r="38" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="14"/>
+      <c r="B38" s="14"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="15" t="s">
         <v>302</v>
       </c>
-      <c r="I37" s="16"/>
-      <c r="J37" s="16"/>
-    </row>
-    <row r="38" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="15"/>
-      <c r="B38" s="15"/>
-      <c r="C38" s="15"/>
-      <c r="D38" s="16" t="s">
+      <c r="E38" s="15" t="s">
         <v>303</v>
       </c>
-      <c r="E38" s="16" t="s">
+      <c r="F38" s="15" t="s">
         <v>304</v>
       </c>
-      <c r="F38" s="16" t="s">
+      <c r="G38" s="15" t="s">
         <v>305</v>
       </c>
-      <c r="G38" s="16" t="s">
+      <c r="H38" s="15" t="s">
         <v>306</v>
       </c>
-      <c r="H38" s="16" t="s">
+      <c r="I38" s="15"/>
+      <c r="J38" s="15"/>
+    </row>
+    <row r="39" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="14"/>
+      <c r="B39" s="14"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="15" t="s">
         <v>307</v>
       </c>
-      <c r="I38" s="16"/>
-      <c r="J38" s="16"/>
-    </row>
-    <row r="39" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="15"/>
-      <c r="B39" s="15"/>
-      <c r="C39" s="15"/>
-      <c r="D39" s="16" t="s">
+      <c r="E39" s="15" t="s">
         <v>308</v>
       </c>
-      <c r="E39" s="16" t="s">
+      <c r="F39" s="15" t="s">
         <v>309</v>
       </c>
-      <c r="F39" s="16" t="s">
+      <c r="G39" s="15" t="s">
         <v>310</v>
       </c>
-      <c r="G39" s="16" t="s">
+      <c r="H39" s="15" t="s">
         <v>311</v>
       </c>
-      <c r="H39" s="16" t="s">
+      <c r="I39" s="15"/>
+      <c r="J39" s="15"/>
+    </row>
+    <row r="40" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="14"/>
+      <c r="B40" s="14"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="15" t="s">
         <v>312</v>
       </c>
-      <c r="I39" s="16"/>
-      <c r="J39" s="16"/>
-    </row>
-    <row r="40" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="15"/>
-      <c r="B40" s="15"/>
-      <c r="C40" s="15"/>
-      <c r="D40" s="16" t="s">
+      <c r="E40" s="15" t="s">
         <v>313</v>
       </c>
-      <c r="E40" s="16" t="s">
+      <c r="F40" s="15" t="s">
         <v>314</v>
       </c>
-      <c r="F40" s="16" t="s">
+      <c r="G40" s="15" t="s">
         <v>315</v>
       </c>
-      <c r="G40" s="16" t="s">
+      <c r="H40" s="15" t="s">
         <v>316</v>
       </c>
-      <c r="H40" s="16" t="s">
+      <c r="I40" s="15"/>
+      <c r="J40" s="15"/>
+    </row>
+    <row r="41" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="14"/>
+      <c r="B41" s="14"/>
+      <c r="C41" s="14"/>
+      <c r="D41" s="15" t="s">
         <v>317</v>
       </c>
-      <c r="I40" s="16"/>
-      <c r="J40" s="16"/>
-    </row>
-    <row r="41" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="15"/>
-      <c r="B41" s="15"/>
-      <c r="C41" s="15"/>
-      <c r="D41" s="16" t="s">
+      <c r="E41" s="15" t="s">
         <v>318</v>
       </c>
-      <c r="E41" s="16" t="s">
+      <c r="F41" s="15" t="s">
         <v>319</v>
       </c>
-      <c r="F41" s="16" t="s">
+      <c r="G41" s="15" t="s">
         <v>320</v>
       </c>
-      <c r="G41" s="16" t="s">
+      <c r="H41" s="15" t="s">
         <v>321</v>
       </c>
-      <c r="H41" s="16" t="s">
+      <c r="I41" s="15"/>
+      <c r="J41" s="15"/>
+    </row>
+    <row r="42" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="14"/>
+      <c r="B42" s="14"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="15" t="s">
         <v>322</v>
       </c>
-      <c r="I41" s="16"/>
-      <c r="J41" s="16"/>
-    </row>
-    <row r="42" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="15"/>
-      <c r="B42" s="15"/>
-      <c r="C42" s="15"/>
-      <c r="D42" s="16" t="s">
+      <c r="E42" s="15" t="s">
         <v>323</v>
       </c>
-      <c r="E42" s="16" t="s">
+      <c r="F42" s="15" t="s">
         <v>324</v>
       </c>
-      <c r="F42" s="16" t="s">
+      <c r="G42" s="15" t="s">
         <v>325</v>
       </c>
-      <c r="G42" s="16" t="s">
+      <c r="H42" s="15" t="s">
         <v>326</v>
       </c>
-      <c r="H42" s="16" t="s">
+      <c r="I42" s="15"/>
+      <c r="J42" s="15"/>
+    </row>
+    <row r="43" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="14"/>
+      <c r="B43" s="14"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="15" t="s">
         <v>327</v>
       </c>
-      <c r="I42" s="16"/>
-      <c r="J42" s="16"/>
-    </row>
-    <row r="43" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="15"/>
-      <c r="B43" s="15"/>
-      <c r="C43" s="15"/>
-      <c r="D43" s="16" t="s">
+      <c r="E43" s="15" t="s">
         <v>328</v>
       </c>
-      <c r="E43" s="16" t="s">
+      <c r="F43" s="15" t="s">
         <v>329</v>
       </c>
-      <c r="F43" s="16" t="s">
+      <c r="G43" s="15" t="s">
         <v>330</v>
       </c>
-      <c r="G43" s="16" t="s">
+      <c r="H43" s="15" t="s">
         <v>331</v>
       </c>
-      <c r="H43" s="16" t="s">
+      <c r="I43" s="15"/>
+      <c r="J43" s="15"/>
+    </row>
+    <row r="44" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="14"/>
+      <c r="B44" s="14"/>
+      <c r="C44" s="14"/>
+      <c r="D44" s="15" t="s">
         <v>332</v>
       </c>
-      <c r="I43" s="16"/>
-      <c r="J43" s="16"/>
-    </row>
-    <row r="44" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="15"/>
-      <c r="B44" s="15"/>
-      <c r="C44" s="15"/>
-      <c r="D44" s="16" t="s">
+      <c r="E44" s="15" t="s">
         <v>333</v>
       </c>
-      <c r="E44" s="16" t="s">
+      <c r="F44" s="15" t="s">
         <v>334</v>
       </c>
-      <c r="F44" s="16" t="s">
+      <c r="G44" s="15" t="s">
         <v>335</v>
       </c>
-      <c r="G44" s="16" t="s">
+      <c r="H44" s="15" t="s">
         <v>336</v>
       </c>
-      <c r="H44" s="16" t="s">
+      <c r="I44" s="15"/>
+      <c r="J44" s="15"/>
+    </row>
+    <row r="45" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="14"/>
+      <c r="B45" s="14"/>
+      <c r="C45" s="14"/>
+      <c r="D45" s="15" t="s">
         <v>337</v>
       </c>
-      <c r="I44" s="16"/>
-      <c r="J44" s="16"/>
-    </row>
-    <row r="45" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="15"/>
-      <c r="B45" s="15"/>
-      <c r="C45" s="15"/>
-      <c r="D45" s="16" t="s">
+      <c r="E45" s="15" t="s">
         <v>338</v>
       </c>
-      <c r="E45" s="16" t="s">
+      <c r="F45" s="15" t="s">
         <v>339</v>
       </c>
-      <c r="F45" s="16" t="s">
+      <c r="G45" s="15" t="s">
         <v>340</v>
       </c>
-      <c r="G45" s="16" t="s">
+      <c r="H45" s="15" t="s">
         <v>341</v>
       </c>
-      <c r="H45" s="16" t="s">
-        <v>342</v>
-      </c>
-      <c r="I45" s="16"/>
-      <c r="J45" s="16"/>
+      <c r="I45" s="15"/>
+      <c r="J45" s="15"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J42"/>
-  <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="I2:I45" type="list">
+  <autoFilter ref="A1:J45"/>
+  <dataValidations count="2">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="I2:I25" type="list">
+      <formula1>$S$1:$S$3</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="equal" showDropDown="false" showErrorMessage="true" showInputMessage="true" sqref="I26:I45" type="list">
       <formula1>$R$1:$R$3</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -3936,10 +8059,4 @@
   <drawing r:id="rId2"/>
   <legacyDrawing r:id="rId3"/>
 </worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{b27ac744-d744-4b94-baa9-948b89b4017a}" enabled="1" method="Standard" siteId="{e3333e00-c877-4b87-b6ad-45e942de1750}" contentBits="0" removed="0"/>
-</clbl:labelList>
 </file>